--- a/05 dependency and cleanup reports/scuc_dependency_scan_and_cleanup_plan.xlsx
+++ b/05 dependency and cleanup reports/scuc_dependency_scan_and_cleanup_plan.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="254">
   <si>
     <t xml:space="preserve">classification</t>
   </si>
@@ -30,6 +30,9 @@
     <t xml:space="preserve">source_exists_now</t>
   </si>
   <si>
+    <t xml:space="preserve">is_separate_non_snapshot_dataset</t>
+  </si>
+  <si>
     <t xml:space="preserve">proposed_destination</t>
   </si>
   <si>
@@ -81,306 +84,306 @@
     <t xml:space="preserve">08 datasets prior to pre-canonical set matches</t>
   </si>
   <si>
+    <t xml:space="preserve">/Users/D/R Working Directory/SCUC Data Analysis/TEST-Plotting Data From TEA Reports/data/TEST SCUC 2004 TEA TAKS Data Grades 3-11.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEST SCUC 2004 TEA TAKS Data Grades 3-11.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCUC Data Analysis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Users/D/R Working Directory/SCUC Data Recovery/08 datasets prior to pre-canonical set matches/SCUC Data Analysis/TEST-Plotting Data From TEA Reports/data/TEST SCUC 2004 TEA TAKS Data Grades 3-11.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RETAIN: owner confirmed this is a separate dataset outside the canonical Snapshot cleanup</t>
+  </si>
+  <si>
+    <t xml:space="preserve">retain as a separate dataset; no canonical Snapshot replacement required</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pending</t>
+  </si>
+  <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
+    <t xml:space="preserve">/Users/D/R Working Directory/SCUC Data Analysis/Various Scripts for Book Examples/scuc-tea-5yr-snapshot-df.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">scuc-tea-5yr-snapshot-df.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Users/D/R Working Directory/SCUC Data Recovery/08 datasets prior to pre-canonical set matches/SCUC Data Analysis/Various Scripts for Book Examples/scuc-tea-5yr-snapshot-df.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Users/D/R Working Directory/SCUC-Book---28-Years-of-Data/data/TEST SCUC 2004 TEA TAKS Data Grades 3-11.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCUC-Book---28-Years-of-Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Users/D/R Working Directory/SCUC Data Recovery/08 datasets prior to pre-canonical set matches/SCUC-Book---28-Years-of-Data/data/TEST SCUC 2004 TEA TAKS Data Grades 3-11.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06 canonical data set matches</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Users/D/R Working Directory/Master Data Bank/CANONICAL DATA SETS/SCUC Canonical Data Sets/Became_Canonical_20250808_FINALIZED_man_standardized_resectioned_decimals_SCUC_Snapshots_1995_to_2023-LONG (SUPERSEDED).csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Became_Canonical_20250808_FINALIZED_man_standardized_resectioned_decimals_SCUC_Snapshots_1995_to_2023-LONG (SUPERSEDED).csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Master Data Bank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Users/D/R Working Directory/SCUC Data Recovery/06 canonical data set matches/Master Data Bank/CANONICAL DATA SETS/SCUC Canonical Data Sets/Became_Canonical_20250808_FINALIZED_man_standardized_resectioned_decimals_SCUC_Snapshots_1995_to_2023-LONG (SUPERSEDED).csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Users/D/R Working Directory/SCUC Data Recovery/01 reference canonical/SCUC_Snapshots_1995_to_2023_LONG_CANONICAL.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">READY FOR ARCHIVE after backup approval; exact canonical replacement exists</t>
+  </si>
+  <si>
+    <t xml:space="preserve">archive original after backup approval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Users/D/R Working Directory/Master Data Bank/CANONICAL DATA SETS/SCUC Canonical Data Sets/Became_Canonical_man_standardized_20250808_resectioned_decimals_SCUC_Snapshots_1995_to_2023-LONG-FINAL (SUPERCEDED).xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Became_Canonical_man_standardized_20250808_resectioned_decimals_SCUC_Snapshots_1995_to_2023-LONG-FINAL (SUPERCEDED).xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Users/D/R Working Directory/SCUC Data Recovery/06 canonical data set matches/Master Data Bank/CANONICAL DATA SETS/SCUC Canonical Data Sets/Became_Canonical_man_standardized_20250808_resectioned_decimals_SCUC_Snapshots_1995_to_2023-LONG-FINAL (SUPERCEDED).xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Users/D/R Working Directory/Master Data Bank/CANONICAL DATA SETS/SCUC Canonical Data Sets/SCUC_Snapshots_1995_to_2022_LONG_CANONICAL.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCUC_Snapshots_1995_to_2022_LONG_CANONICAL.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Users/D/R Working Directory/SCUC Data Recovery/06 canonical data set matches/Master Data Bank/CANONICAL DATA SETS/SCUC Canonical Data Sets/SCUC_Snapshots_1995_to_2022_LONG_CANONICAL.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Users/D/R Working Directory/SCUC Data Recovery/01 reference canonical/SCUC_Snapshots_1995_to_2022_LONG_CANONICAL.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Users/D/R Working Directory/Master Data Bank/CANONICAL DATA SETS/SCUC Canonical Data Sets/SCUC_Snapshots_1995_to_2022_LONG_CANONICAL.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCUC_Snapshots_1995_to_2022_LONG_CANONICAL.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Users/D/R Working Directory/SCUC Data Recovery/06 canonical data set matches/Master Data Bank/CANONICAL DATA SETS/SCUC Canonical Data Sets/SCUC_Snapshots_1995_to_2022_LONG_CANONICAL.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Users/D/R Working Directory/SCUC Data Recovery/01 reference canonical/SCUC_Snapshots_1995_to_2022_LONG_CANONICAL.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Users/D/R Working Directory/Master Data Bank/CANONICAL DATA SETS/SCUC Canonical Data Sets/SCUC_Snapshots_1995_to_2022_LONG_metric_registry_CANONICAL.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCUC_Snapshots_1995_to_2022_LONG_metric_registry_CANONICAL.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Users/D/R Working Directory/SCUC Data Recovery/06 canonical data set matches/Master Data Bank/CANONICAL DATA SETS/SCUC Canonical Data Sets/SCUC_Snapshots_1995_to_2022_LONG_metric_registry_CANONICAL.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Users/D/R Working Directory/SCUC Data Recovery/01 reference canonical/SCUC_Snapshots_1995_to_2022_LONG_metric_registry_CANONICAL.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Users/D/R Working Directory/Master Data Bank/CANONICAL DATA SETS/SCUC Canonical Data Sets/SCUC_Snapshots_1995_to_2022_WIDE_CANONICAL.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCUC_Snapshots_1995_to_2022_WIDE_CANONICAL.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Users/D/R Working Directory/SCUC Data Recovery/06 canonical data set matches/Master Data Bank/CANONICAL DATA SETS/SCUC Canonical Data Sets/SCUC_Snapshots_1995_to_2022_WIDE_CANONICAL.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Users/D/R Working Directory/SCUC Data Recovery/01 reference canonical/SCUC_Snapshots_1995_to_2022_WIDE_CANONICAL.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Users/D/R Working Directory/Master Data Bank/CANONICAL DATA SETS/SCUC Canonical Data Sets/SCUC_Snapshots_1995_to_2023_LONG_CANONICAL.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCUC_Snapshots_1995_to_2023_LONG_CANONICAL.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Users/D/R Working Directory/SCUC Data Recovery/06 canonical data set matches/Master Data Bank/CANONICAL DATA SETS/SCUC Canonical Data Sets/SCUC_Snapshots_1995_to_2023_LONG_CANONICAL.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Users/D/R Working Directory/Master Data Bank/CANONICAL DATA SETS/SCUC Canonical Data Sets/SCUC_Snapshots_1995_to_2023_LONG_CANONICAL.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCUC_Snapshots_1995_to_2023_LONG_CANONICAL.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Users/D/R Working Directory/SCUC Data Recovery/06 canonical data set matches/Master Data Bank/CANONICAL DATA SETS/SCUC Canonical Data Sets/SCUC_Snapshots_1995_to_2023_LONG_CANONICAL.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Users/D/R Working Directory/SCUC Data Recovery/01 reference canonical/SCUC_Snapshots_1995_to_2023_LONG_CANONICAL.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Users/D/R Working Directory/Master Data Bank/CANONICAL DATA SETS/SCUC Canonical Data Sets/SCUC_Snapshots_1995_to_2023_LONG_metric_registry_CANONICAL.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCUC_Snapshots_1995_to_2023_LONG_metric_registry_CANONICAL.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Users/D/R Working Directory/SCUC Data Recovery/06 canonical data set matches/Master Data Bank/CANONICAL DATA SETS/SCUC Canonical Data Sets/SCUC_Snapshots_1995_to_2023_LONG_metric_registry_CANONICAL.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Users/D/R Working Directory/SCUC Data Recovery/01 reference canonical/SCUC_Snapshots_1995_to_2023_LONG_metric_registry_CANONICAL.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Users/D/R Working Directory/Master Data Bank/CANONICAL DATA SETS/SCUC Canonical Data Sets/SCUC_Snapshots_1995_to_2023_WIDE_CANONICAL.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCUC_Snapshots_1995_to_2023_WIDE_CANONICAL.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Users/D/R Working Directory/SCUC Data Recovery/06 canonical data set matches/Master Data Bank/CANONICAL DATA SETS/SCUC Canonical Data Sets/SCUC_Snapshots_1995_to_2023_WIDE_CANONICAL.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Users/D/R Working Directory/SCUC Data Recovery/01 reference canonical/SCUC_Snapshots_1995_to_2023_WIDE_CANONICAL.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Users/D/R Working Directory/SCUC-Book---28-Years-of-Data/data/SCUC Snapshots 1995 to 2022-LONG.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCUC Snapshots 1995 to 2022-LONG.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Users/D/R Working Directory/SCUC Data Recovery/06 canonical data set matches/SCUC-Book---28-Years-of-Data/data/SCUC Snapshots 1995 to 2022-LONG.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07 pre-canonical set matches</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Users/D/R Working Directory/29-Years-of-Data-SCUC/data/20250227 SCUC Snapshots 1995 to 2022-LONG.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20250227 SCUC Snapshots 1995 to 2022-LONG.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29-Years-of-Data-SCUC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Users/D/R Working Directory/SCUC Data Recovery/07 pre-canonical set matches/29-Years-of-Data-SCUC/data/20250227 SCUC Snapshots 1995 to 2022-LONG.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">READY FOR ARCHIVE after backup approval; reference predecessor remains in folder 02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Users/D/R Working Directory/Data Analysis - SCUC Flexdashboard/data/20250227 SCUC Snapshots 1995 to 2022-LONG.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Analysis - SCUC Flexdashboard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Users/D/R Working Directory/SCUC Data Recovery/07 pre-canonical set matches/Data Analysis - SCUC Flexdashboard/data/20250227 SCUC Snapshots 1995 to 2022-LONG.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Users/D/R Working Directory/Master Data Bank/CANONICAL DATA SETS/SCUC Canonical Data Sets/Became_Canonical_20250329 SCUC Snapshots 1995 to 2022-LONG (SUPERSEDED).csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Became_Canonical_20250329 SCUC Snapshots 1995 to 2022-LONG (SUPERSEDED).csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Users/D/R Working Directory/SCUC Data Recovery/07 pre-canonical set matches/Master Data Bank/CANONICAL DATA SETS/SCUC Canonical Data Sets/Became_Canonical_20250329 SCUC Snapshots 1995 to 2022-LONG (SUPERSEDED).csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Users/D/R Working Directory/SCUC Data Wrangling/SCUC 1995-2022 TEA Snapshots MASTER WORKING COPIES/20250329 SCUC Snapshots 1995 to 2022-LONG.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20250329 SCUC Snapshots 1995 to 2022-LONG.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCUC Data Wrangling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Users/D/R Working Directory/SCUC Data Recovery/07 pre-canonical set matches/SCUC Data Wrangling/SCUC 1995-2022 TEA Snapshots MASTER WORKING COPIES/20250329 SCUC Snapshots 1995 to 2022-LONG.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Users/D/R Working Directory/29-Years-of-Data-SCUC/data/20250227 SCUC Snapshots 1995 to 2023-LONG-ONLY-WITH-SORT.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20250227 SCUC Snapshots 1995 to 2023-LONG-ONLY-WITH-SORT.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Users/D/R Working Directory/SCUC Data Recovery/08 datasets prior to pre-canonical set matches/29-Years-of-Data-SCUC/data/20250227 SCUC Snapshots 1995 to 2023-LONG-ONLY-WITH-SORT.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARCHIVE CANDIDATE: unmatched historical variant; manual approval required; do not delete</t>
+  </si>
+  <si>
+    <t xml:space="preserve">archive for historical review; no deletion authorized</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Users/D/R Working Directory/29-Years-of-Data-SCUC/data/TEST SCUC 2004 TEA TAKS Data Grades 3-11.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Users/D/R Working Directory/SCUC Data Recovery/08 datasets prior to pre-canonical set matches/29-Years-of-Data-SCUC/data/TEST SCUC 2004 TEA TAKS Data Grades 3-11.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Users/D/R Working Directory/Data Analysis - SCUC Flexdashboard/data/20250227 SCUC Snapshots 1995 to 2023-LONG-ONLY-WITH-SORT.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Users/D/R Working Directory/SCUC Data Recovery/08 datasets prior to pre-canonical set matches/Data Analysis - SCUC Flexdashboard/data/20250227 SCUC Snapshots 1995 to 2023-LONG-ONLY-WITH-SORT.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Users/D/R Working Directory/Master Data Bank/WIDE data/CANONIZE_THIS_SCUC_Snapshots_1995_to_2023_WIDE_ONLY-NO-SORT-COL-20250717-FINAL.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CANONIZE_THIS_SCUC_Snapshots_1995_to_2023_WIDE_ONLY-NO-SORT-COL-20250717-FINAL.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Users/D/R Working Directory/SCUC Data Recovery/08 datasets prior to pre-canonical set matches/Master Data Bank/WIDE data/CANONIZE_THIS_SCUC_Snapshots_1995_to_2023_WIDE_ONLY-NO-SORT-COL-20250717-FINAL.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Users/D/R Working Directory/SCUC Data Analysis/data/BACKUP-SCUC Snapshots 1994 - 2022.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BACKUP-SCUC Snapshots 1994 - 2022.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Users/D/R Working Directory/SCUC Data Recovery/08 datasets prior to pre-canonical set matches/SCUC Data Analysis/data/BACKUP-SCUC Snapshots 1994 - 2022.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Users/D/R Working Directory/SCUC Data Analysis/TEST-Plotting Data From TEA Reports/data/OLD-SCUC Snapshots 1995 to 2022-LONG.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OLD-SCUC Snapshots 1995 to 2022-LONG.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Users/D/R Working Directory/SCUC Data Recovery/08 datasets prior to pre-canonical set matches/SCUC Data Analysis/TEST-Plotting Data From TEA Reports/data/OLD-SCUC Snapshots 1995 to 2022-LONG.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Users/D/R Working Directory/SCUC Data Analysis/data/SCUC Snapshots 1994 - 2022.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCUC Snapshots 1994 - 2022.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Users/D/R Working Directory/SCUC Data Recovery/08 datasets prior to pre-canonical set matches/SCUC Data Analysis/data/SCUC Snapshots 1994 - 2022.xlsx</t>
+  </si>
+  <si>
     <t xml:space="preserve">/Users/D/R Working Directory/SCUC Data Analysis/TEST-Plotting Data From TEA Reports/data/SCUC Snapshots 1995 to 2022-LONG.csv</t>
   </si>
   <si>
-    <t xml:space="preserve">SCUC Snapshots 1995 to 2022-LONG.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SCUC Data Analysis</t>
-  </si>
-  <si>
     <t xml:space="preserve">/Users/D/R Working Directory/SCUC Data Recovery/08 datasets prior to pre-canonical set matches/SCUC Data Analysis/TEST-Plotting Data From TEA Reports/data/SCUC Snapshots 1995 to 2022-LONG.csv</t>
   </si>
   <si>
-    <t xml:space="preserve">RETAIN AND INVESTIGATE: active dependency exists; do not archive or delete</t>
-  </si>
-  <si>
-    <t xml:space="preserve">retain and investigate; no canonical replacement assumed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pending</t>
-  </si>
-  <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
     <t xml:space="preserve">/Users/D/R Working Directory/SCUC Data Analysis/data/SCUC Snapshots 1995 to 2022-LONG.csv</t>
   </si>
   <si>
     <t xml:space="preserve">/Users/D/R Working Directory/SCUC Data Recovery/08 datasets prior to pre-canonical set matches/SCUC Data Analysis/data/SCUC Snapshots 1995 to 2022-LONG.csv</t>
   </si>
   <si>
-    <t xml:space="preserve">/Users/D/R Working Directory/SCUC Data Analysis/TEST-Plotting Data From TEA Reports/data/TEST SCUC 2004 TEA TAKS Data Grades 3-11.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TEST SCUC 2004 TEA TAKS Data Grades 3-11.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/Users/D/R Working Directory/SCUC Data Recovery/08 datasets prior to pre-canonical set matches/SCUC Data Analysis/TEST-Plotting Data From TEA Reports/data/TEST SCUC 2004 TEA TAKS Data Grades 3-11.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/Users/D/R Working Directory/SCUC Data Analysis/Various Scripts for Book Examples/scuc-tea-5yr-snapshot-df.xlsx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">scuc-tea-5yr-snapshot-df.xlsx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/Users/D/R Working Directory/SCUC Data Recovery/08 datasets prior to pre-canonical set matches/SCUC Data Analysis/Various Scripts for Book Examples/scuc-tea-5yr-snapshot-df.xlsx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/Users/D/R Working Directory/SCUC-Book---28-Years-of-Data/data/TEST SCUC 2004 TEA TAKS Data Grades 3-11.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SCUC-Book---28-Years-of-Data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/Users/D/R Working Directory/SCUC Data Recovery/08 datasets prior to pre-canonical set matches/SCUC-Book---28-Years-of-Data/data/TEST SCUC 2004 TEA TAKS Data Grades 3-11.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06 canonical data set matches</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/Users/D/R Working Directory/Master Data Bank/CANONICAL DATA SETS/SCUC Canonical Data Sets/Became_Canonical_20250808_FINALIZED_man_standardized_resectioned_decimals_SCUC_Snapshots_1995_to_2023-LONG (SUPERSEDED).csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Became_Canonical_20250808_FINALIZED_man_standardized_resectioned_decimals_SCUC_Snapshots_1995_to_2023-LONG (SUPERSEDED).csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Master Data Bank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/Users/D/R Working Directory/SCUC Data Recovery/06 canonical data set matches/Master Data Bank/CANONICAL DATA SETS/SCUC Canonical Data Sets/Became_Canonical_20250808_FINALIZED_man_standardized_resectioned_decimals_SCUC_Snapshots_1995_to_2023-LONG (SUPERSEDED).csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/Users/D/R Working Directory/SCUC Data Recovery/01 reference canonical/SCUC_Snapshots_1995_to_2023_LONG_CANONICAL.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">READY FOR ARCHIVE after backup approval; exact canonical replacement exists</t>
-  </si>
-  <si>
-    <t xml:space="preserve">archive original after backup approval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/Users/D/R Working Directory/Master Data Bank/CANONICAL DATA SETS/SCUC Canonical Data Sets/Became_Canonical_man_standardized_20250808_resectioned_decimals_SCUC_Snapshots_1995_to_2023-LONG-FINAL (SUPERCEDED).xlsx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Became_Canonical_man_standardized_20250808_resectioned_decimals_SCUC_Snapshots_1995_to_2023-LONG-FINAL (SUPERCEDED).xlsx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/Users/D/R Working Directory/SCUC Data Recovery/06 canonical data set matches/Master Data Bank/CANONICAL DATA SETS/SCUC Canonical Data Sets/Became_Canonical_man_standardized_20250808_resectioned_decimals_SCUC_Snapshots_1995_to_2023-LONG-FINAL (SUPERCEDED).xlsx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/Users/D/R Working Directory/Master Data Bank/CANONICAL DATA SETS/SCUC Canonical Data Sets/SCUC_Snapshots_1995_to_2022_LONG_CANONICAL.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SCUC_Snapshots_1995_to_2022_LONG_CANONICAL.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/Users/D/R Working Directory/SCUC Data Recovery/06 canonical data set matches/Master Data Bank/CANONICAL DATA SETS/SCUC Canonical Data Sets/SCUC_Snapshots_1995_to_2022_LONG_CANONICAL.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/Users/D/R Working Directory/SCUC Data Recovery/01 reference canonical/SCUC_Snapshots_1995_to_2022_LONG_CANONICAL.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/Users/D/R Working Directory/Master Data Bank/CANONICAL DATA SETS/SCUC Canonical Data Sets/SCUC_Snapshots_1995_to_2022_LONG_CANONICAL.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SCUC_Snapshots_1995_to_2022_LONG_CANONICAL.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/Users/D/R Working Directory/SCUC Data Recovery/06 canonical data set matches/Master Data Bank/CANONICAL DATA SETS/SCUC Canonical Data Sets/SCUC_Snapshots_1995_to_2022_LONG_CANONICAL.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/Users/D/R Working Directory/SCUC Data Recovery/01 reference canonical/SCUC_Snapshots_1995_to_2022_LONG_CANONICAL.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/Users/D/R Working Directory/Master Data Bank/CANONICAL DATA SETS/SCUC Canonical Data Sets/SCUC_Snapshots_1995_to_2022_LONG_metric_registry_CANONICAL.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SCUC_Snapshots_1995_to_2022_LONG_metric_registry_CANONICAL.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/Users/D/R Working Directory/SCUC Data Recovery/06 canonical data set matches/Master Data Bank/CANONICAL DATA SETS/SCUC Canonical Data Sets/SCUC_Snapshots_1995_to_2022_LONG_metric_registry_CANONICAL.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/Users/D/R Working Directory/SCUC Data Recovery/01 reference canonical/SCUC_Snapshots_1995_to_2022_LONG_metric_registry_CANONICAL.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/Users/D/R Working Directory/Master Data Bank/CANONICAL DATA SETS/SCUC Canonical Data Sets/SCUC_Snapshots_1995_to_2022_WIDE_CANONICAL.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SCUC_Snapshots_1995_to_2022_WIDE_CANONICAL.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/Users/D/R Working Directory/SCUC Data Recovery/06 canonical data set matches/Master Data Bank/CANONICAL DATA SETS/SCUC Canonical Data Sets/SCUC_Snapshots_1995_to_2022_WIDE_CANONICAL.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/Users/D/R Working Directory/SCUC Data Recovery/01 reference canonical/SCUC_Snapshots_1995_to_2022_WIDE_CANONICAL.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/Users/D/R Working Directory/Master Data Bank/CANONICAL DATA SETS/SCUC Canonical Data Sets/SCUC_Snapshots_1995_to_2023_LONG_CANONICAL.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SCUC_Snapshots_1995_to_2023_LONG_CANONICAL.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/Users/D/R Working Directory/SCUC Data Recovery/06 canonical data set matches/Master Data Bank/CANONICAL DATA SETS/SCUC Canonical Data Sets/SCUC_Snapshots_1995_to_2023_LONG_CANONICAL.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/Users/D/R Working Directory/Master Data Bank/CANONICAL DATA SETS/SCUC Canonical Data Sets/SCUC_Snapshots_1995_to_2023_LONG_CANONICAL.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SCUC_Snapshots_1995_to_2023_LONG_CANONICAL.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/Users/D/R Working Directory/SCUC Data Recovery/06 canonical data set matches/Master Data Bank/CANONICAL DATA SETS/SCUC Canonical Data Sets/SCUC_Snapshots_1995_to_2023_LONG_CANONICAL.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/Users/D/R Working Directory/SCUC Data Recovery/01 reference canonical/SCUC_Snapshots_1995_to_2023_LONG_CANONICAL.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/Users/D/R Working Directory/Master Data Bank/CANONICAL DATA SETS/SCUC Canonical Data Sets/SCUC_Snapshots_1995_to_2023_LONG_metric_registry_CANONICAL.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SCUC_Snapshots_1995_to_2023_LONG_metric_registry_CANONICAL.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/Users/D/R Working Directory/SCUC Data Recovery/06 canonical data set matches/Master Data Bank/CANONICAL DATA SETS/SCUC Canonical Data Sets/SCUC_Snapshots_1995_to_2023_LONG_metric_registry_CANONICAL.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/Users/D/R Working Directory/SCUC Data Recovery/01 reference canonical/SCUC_Snapshots_1995_to_2023_LONG_metric_registry_CANONICAL.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/Users/D/R Working Directory/Master Data Bank/CANONICAL DATA SETS/SCUC Canonical Data Sets/SCUC_Snapshots_1995_to_2023_WIDE_CANONICAL.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SCUC_Snapshots_1995_to_2023_WIDE_CANONICAL.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/Users/D/R Working Directory/SCUC Data Recovery/06 canonical data set matches/Master Data Bank/CANONICAL DATA SETS/SCUC Canonical Data Sets/SCUC_Snapshots_1995_to_2023_WIDE_CANONICAL.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/Users/D/R Working Directory/SCUC Data Recovery/01 reference canonical/SCUC_Snapshots_1995_to_2023_WIDE_CANONICAL.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/Users/D/R Working Directory/SCUC-Book---28-Years-of-Data/data/SCUC Snapshots 1995 to 2022-LONG.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/Users/D/R Working Directory/SCUC Data Recovery/06 canonical data set matches/SCUC-Book---28-Years-of-Data/data/SCUC Snapshots 1995 to 2022-LONG.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">07 pre-canonical set matches</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/Users/D/R Working Directory/29-Years-of-Data-SCUC/data/20250227 SCUC Snapshots 1995 to 2022-LONG.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20250227 SCUC Snapshots 1995 to 2022-LONG.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29-Years-of-Data-SCUC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/Users/D/R Working Directory/SCUC Data Recovery/07 pre-canonical set matches/29-Years-of-Data-SCUC/data/20250227 SCUC Snapshots 1995 to 2022-LONG.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">READY FOR ARCHIVE after backup approval; reference predecessor remains in folder 02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/Users/D/R Working Directory/Data Analysis - SCUC Flexdashboard/data/20250227 SCUC Snapshots 1995 to 2022-LONG.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Analysis - SCUC Flexdashboard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/Users/D/R Working Directory/SCUC Data Recovery/07 pre-canonical set matches/Data Analysis - SCUC Flexdashboard/data/20250227 SCUC Snapshots 1995 to 2022-LONG.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/Users/D/R Working Directory/Master Data Bank/CANONICAL DATA SETS/SCUC Canonical Data Sets/Became_Canonical_20250329 SCUC Snapshots 1995 to 2022-LONG (SUPERSEDED).csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Became_Canonical_20250329 SCUC Snapshots 1995 to 2022-LONG (SUPERSEDED).csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/Users/D/R Working Directory/SCUC Data Recovery/07 pre-canonical set matches/Master Data Bank/CANONICAL DATA SETS/SCUC Canonical Data Sets/Became_Canonical_20250329 SCUC Snapshots 1995 to 2022-LONG (SUPERSEDED).csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/Users/D/R Working Directory/SCUC Data Wrangling/SCUC 1995-2022 TEA Snapshots MASTER WORKING COPIES/20250329 SCUC Snapshots 1995 to 2022-LONG.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20250329 SCUC Snapshots 1995 to 2022-LONG.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SCUC Data Wrangling</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/Users/D/R Working Directory/SCUC Data Recovery/07 pre-canonical set matches/SCUC Data Wrangling/SCUC 1995-2022 TEA Snapshots MASTER WORKING COPIES/20250329 SCUC Snapshots 1995 to 2022-LONG.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/Users/D/R Working Directory/29-Years-of-Data-SCUC/data/20250227 SCUC Snapshots 1995 to 2023-LONG-ONLY-WITH-SORT.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20250227 SCUC Snapshots 1995 to 2023-LONG-ONLY-WITH-SORT.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/Users/D/R Working Directory/SCUC Data Recovery/08 datasets prior to pre-canonical set matches/29-Years-of-Data-SCUC/data/20250227 SCUC Snapshots 1995 to 2023-LONG-ONLY-WITH-SORT.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARCHIVE CANDIDATE: unmatched historical variant; manual approval required; do not delete</t>
-  </si>
-  <si>
-    <t xml:space="preserve">archive for historical review; no deletion authorized</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/Users/D/R Working Directory/29-Years-of-Data-SCUC/data/TEST SCUC 2004 TEA TAKS Data Grades 3-11.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/Users/D/R Working Directory/SCUC Data Recovery/08 datasets prior to pre-canonical set matches/29-Years-of-Data-SCUC/data/TEST SCUC 2004 TEA TAKS Data Grades 3-11.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/Users/D/R Working Directory/Data Analysis - SCUC Flexdashboard/data/20250227 SCUC Snapshots 1995 to 2023-LONG-ONLY-WITH-SORT.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/Users/D/R Working Directory/SCUC Data Recovery/08 datasets prior to pre-canonical set matches/Data Analysis - SCUC Flexdashboard/data/20250227 SCUC Snapshots 1995 to 2023-LONG-ONLY-WITH-SORT.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/Users/D/R Working Directory/Master Data Bank/WIDE data/CANONIZE_THIS_SCUC_Snapshots_1995_to_2023_WIDE_ONLY-NO-SORT-COL-20250717-FINAL.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CANONIZE_THIS_SCUC_Snapshots_1995_to_2023_WIDE_ONLY-NO-SORT-COL-20250717-FINAL.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/Users/D/R Working Directory/SCUC Data Recovery/08 datasets prior to pre-canonical set matches/Master Data Bank/WIDE data/CANONIZE_THIS_SCUC_Snapshots_1995_to_2023_WIDE_ONLY-NO-SORT-COL-20250717-FINAL.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/Users/D/R Working Directory/SCUC Data Analysis/data/BACKUP-SCUC Snapshots 1994 - 2022.xlsx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BACKUP-SCUC Snapshots 1994 - 2022.xlsx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/Users/D/R Working Directory/SCUC Data Recovery/08 datasets prior to pre-canonical set matches/SCUC Data Analysis/data/BACKUP-SCUC Snapshots 1994 - 2022.xlsx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/Users/D/R Working Directory/SCUC Data Analysis/TEST-Plotting Data From TEA Reports/data/OLD-SCUC Snapshots 1995 to 2022-LONG.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OLD-SCUC Snapshots 1995 to 2022-LONG.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/Users/D/R Working Directory/SCUC Data Recovery/08 datasets prior to pre-canonical set matches/SCUC Data Analysis/TEST-Plotting Data From TEA Reports/data/OLD-SCUC Snapshots 1995 to 2022-LONG.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/Users/D/R Working Directory/SCUC Data Analysis/data/SCUC Snapshots 1994 - 2022.xlsx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SCUC Snapshots 1994 - 2022.xlsx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/Users/D/R Working Directory/SCUC Data Recovery/08 datasets prior to pre-canonical set matches/SCUC Data Analysis/data/SCUC Snapshots 1994 - 2022.xlsx</t>
-  </si>
-  <si>
     <t xml:space="preserve">/Users/D/R Working Directory/SCUC Data Analysis/data/SCUC TEA Snapshots 2017-2021.xlsx</t>
   </si>
   <si>
@@ -540,7 +543,7 @@
     <t xml:space="preserve">SCUC Data Analysis/TEST-Plotting Data From TEA Reports/Exploratory Data Analysis-Kelsey Gonzalez.qmd</t>
   </si>
   <si>
-    <t xml:space="preserve">df2 &lt;- read_csv(file = here::here("data","SCUC Snapshots 1995 to 2022-LONG.csv"))</t>
+    <t xml:space="preserve">df2 &lt;- read_csv(file = here::here("data","SCUC_Snapshots_1995_to_2022_LONG_CANONICAL.csv")) |&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">df1 &lt;- read_csv(file = here::here("data","TEST SCUC 2004 TEA TAKS Data Grades 3-11.csv"))</t>
@@ -1105,22 +1108,23 @@
     <col min="3" max="3" width="123.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="34.71" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="17.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="250.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="22.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="20.71" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="133.71" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="23.71" hidden="0" customWidth="1"/>
-    <col min="11" max="11" width="12.71" hidden="0" customWidth="1"/>
-    <col min="12" max="12" width="11.71" hidden="0" customWidth="1"/>
-    <col min="13" max="13" width="14.71" hidden="0" customWidth="1"/>
-    <col min="14" max="14" width="17.71" hidden="0" customWidth="1"/>
-    <col min="15" max="15" width="28.71" hidden="0" customWidth="1"/>
-    <col min="16" max="16" width="21.71" hidden="0" customWidth="1"/>
-    <col min="17" max="17" width="88.71" hidden="0" customWidth="1"/>
-    <col min="18" max="18" width="56.71" hidden="0" customWidth="1"/>
-    <col min="19" max="19" width="19.71" hidden="0" customWidth="1"/>
-    <col min="20" max="20" width="14.71" hidden="0" customWidth="1"/>
-    <col min="21" max="21" width="10.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="32.71" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="250.71" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="22.71" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="20.71" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="133.71" hidden="0" customWidth="1"/>
+    <col min="11" max="11" width="23.71" hidden="0" customWidth="1"/>
+    <col min="12" max="12" width="12.71" hidden="0" customWidth="1"/>
+    <col min="13" max="13" width="11.71" hidden="0" customWidth="1"/>
+    <col min="14" max="14" width="14.71" hidden="0" customWidth="1"/>
+    <col min="15" max="15" width="17.71" hidden="0" customWidth="1"/>
+    <col min="16" max="16" width="28.71" hidden="0" customWidth="1"/>
+    <col min="17" max="17" width="21.71" hidden="0" customWidth="1"/>
+    <col min="18" max="18" width="89.71" hidden="0" customWidth="1"/>
+    <col min="19" max="19" width="72.71" hidden="0" customWidth="1"/>
+    <col min="20" max="20" width="19.71" hidden="0" customWidth="1"/>
+    <col min="21" max="21" width="14.71" hidden="0" customWidth="1"/>
+    <col min="22" max="22" width="10.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1187,1199 +1191,1258 @@
       <c r="U1" t="s">
         <v>20</v>
       </c>
+      <c r="V1" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E2" t="b">
         <v>1</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" t="b">
+        <v>1</v>
+      </c>
+      <c r="J2"/>
+      <c r="K2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>4</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P2" t="s">
         <v>25</v>
       </c>
-      <c r="G2" t="b">
-        <v>1</v>
-      </c>
-      <c r="H2" t="b">
-        <v>1</v>
-      </c>
-      <c r="I2"/>
-      <c r="J2" t="b">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="n">
-        <v>4</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N2" t="n">
-        <v>2</v>
-      </c>
-      <c r="O2" t="s">
-        <v>24</v>
-      </c>
-      <c r="P2" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>26</v>
+      <c r="Q2" t="b">
+        <v>1</v>
       </c>
       <c r="R2" t="s">
         <v>27</v>
       </c>
-      <c r="S2" t="b">
-        <v>0</v>
-      </c>
-      <c r="T2" t="s">
+      <c r="S2" t="s">
         <v>28</v>
+      </c>
+      <c r="T2" t="b">
+        <v>0</v>
       </c>
       <c r="U2" t="s">
         <v>29</v>
       </c>
+      <c r="V2" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C3" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="D3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E3" t="b">
         <v>1</v>
       </c>
-      <c r="F3" t="s">
-        <v>31</v>
-      </c>
-      <c r="G3" t="b">
-        <v>1</v>
+      <c r="F3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G3" t="s">
+        <v>33</v>
       </c>
       <c r="H3" t="b">
         <v>1</v>
       </c>
-      <c r="I3"/>
-      <c r="J3" t="b">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
+      <c r="I3" t="b">
+        <v>1</v>
+      </c>
+      <c r="J3"/>
+      <c r="K3" t="b">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N3" t="n">
-        <v>2</v>
-      </c>
-      <c r="O3" t="s">
-        <v>24</v>
-      </c>
-      <c r="P3" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>26</v>
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1</v>
+      </c>
+      <c r="P3" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q3" t="b">
+        <v>1</v>
       </c>
       <c r="R3" t="s">
         <v>27</v>
       </c>
-      <c r="S3" t="b">
-        <v>0</v>
-      </c>
-      <c r="T3" t="s">
+      <c r="S3" t="s">
         <v>28</v>
+      </c>
+      <c r="T3" t="b">
+        <v>0</v>
       </c>
       <c r="U3" t="s">
         <v>29</v>
       </c>
+      <c r="V3" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C4" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="D4" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="E4" t="b">
         <v>1</v>
       </c>
-      <c r="F4" t="s">
-        <v>34</v>
-      </c>
-      <c r="G4" t="b">
-        <v>1</v>
+      <c r="F4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G4" t="s">
+        <v>36</v>
       </c>
       <c r="H4" t="b">
         <v>1</v>
       </c>
-      <c r="I4"/>
-      <c r="J4" t="b">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
+      <c r="I4" t="b">
+        <v>1</v>
+      </c>
+      <c r="J4"/>
+      <c r="K4" t="b">
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" t="n">
         <v>4</v>
       </c>
-      <c r="M4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N4" t="n">
-        <v>2</v>
-      </c>
-      <c r="O4" t="s">
-        <v>24</v>
-      </c>
-      <c r="P4" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>26</v>
+      <c r="O4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P4" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q4" t="b">
+        <v>1</v>
       </c>
       <c r="R4" t="s">
         <v>27</v>
       </c>
-      <c r="S4" t="b">
-        <v>0</v>
-      </c>
-      <c r="T4" t="s">
+      <c r="S4" t="s">
         <v>28</v>
+      </c>
+      <c r="T4" t="b">
+        <v>0</v>
       </c>
       <c r="U4" t="s">
         <v>29</v>
       </c>
+      <c r="V4" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="B5" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C5" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D5" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="E5" t="b">
         <v>1</v>
       </c>
-      <c r="F5" t="s">
-        <v>37</v>
-      </c>
-      <c r="G5" t="b">
-        <v>1</v>
+      <c r="F5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G5" t="s">
+        <v>41</v>
       </c>
       <c r="H5" t="b">
         <v>1</v>
       </c>
-      <c r="I5"/>
-      <c r="J5" t="b">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="I5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J5" t="s">
+        <v>42</v>
+      </c>
+      <c r="K5" t="b">
+        <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>1</v>
-      </c>
-      <c r="O5" t="s">
-        <v>24</v>
-      </c>
-      <c r="P5" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>26</v>
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q5" t="b">
+        <v>0</v>
       </c>
       <c r="R5" t="s">
-        <v>27</v>
-      </c>
-      <c r="S5" t="b">
-        <v>0</v>
-      </c>
-      <c r="T5" t="s">
-        <v>28</v>
+        <v>43</v>
+      </c>
+      <c r="S5" t="s">
+        <v>44</v>
+      </c>
+      <c r="T5" t="b">
+        <v>0</v>
       </c>
       <c r="U5" t="s">
         <v>29</v>
       </c>
+      <c r="V5" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="B6" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="C6" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="D6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E6" t="b">
         <v>1</v>
       </c>
-      <c r="F6" t="s">
-        <v>40</v>
-      </c>
-      <c r="G6" t="b">
-        <v>1</v>
+      <c r="F6" t="b">
+        <v>0</v>
+      </c>
+      <c r="G6" t="s">
+        <v>47</v>
       </c>
       <c r="H6" t="b">
         <v>1</v>
       </c>
-      <c r="I6"/>
-      <c r="J6" t="b">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="I6" t="b">
+        <v>1</v>
+      </c>
+      <c r="J6" t="s">
+        <v>42</v>
+      </c>
+      <c r="K6" t="b">
+        <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O6" t="s">
-        <v>39</v>
-      </c>
-      <c r="P6" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>26</v>
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q6" t="b">
+        <v>0</v>
       </c>
       <c r="R6" t="s">
-        <v>27</v>
-      </c>
-      <c r="S6" t="b">
-        <v>0</v>
-      </c>
-      <c r="T6" t="s">
-        <v>28</v>
+        <v>43</v>
+      </c>
+      <c r="S6" t="s">
+        <v>44</v>
+      </c>
+      <c r="T6" t="b">
+        <v>0</v>
       </c>
       <c r="U6" t="s">
         <v>29</v>
       </c>
+      <c r="V6" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B7" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E7" t="b">
+        <v>1</v>
+      </c>
+      <c r="F7" t="b">
+        <v>0</v>
+      </c>
+      <c r="G7" t="s">
+        <v>50</v>
+      </c>
+      <c r="H7" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" t="b">
+        <v>1</v>
+      </c>
+      <c r="J7" t="s">
+        <v>51</v>
+      </c>
+      <c r="K7" t="b">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>70</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q7" t="b">
+        <v>0</v>
+      </c>
+      <c r="R7" t="s">
         <v>43</v>
       </c>
-      <c r="D7" t="s">
+      <c r="S7" t="s">
         <v>44</v>
       </c>
-      <c r="E7" t="b">
-        <v>1</v>
-      </c>
-      <c r="F7" t="s">
-        <v>45</v>
-      </c>
-      <c r="G7" t="b">
-        <v>1</v>
-      </c>
-      <c r="H7" t="b">
-        <v>1</v>
-      </c>
-      <c r="I7" t="s">
-        <v>46</v>
-      </c>
-      <c r="J7" t="b">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="s">
-        <v>29</v>
-      </c>
-      <c r="P7" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>47</v>
-      </c>
-      <c r="R7" t="s">
-        <v>48</v>
-      </c>
-      <c r="S7" t="b">
-        <v>0</v>
-      </c>
-      <c r="T7" t="s">
-        <v>28</v>
+      <c r="T7" t="b">
+        <v>0</v>
       </c>
       <c r="U7" t="s">
         <v>29</v>
       </c>
+      <c r="V7" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B8" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C8" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D8" t="s">
+        <v>40</v>
+      </c>
+      <c r="E8" t="b">
+        <v>1</v>
+      </c>
+      <c r="F8" t="b">
+        <v>0</v>
+      </c>
+      <c r="G8" t="s">
+        <v>54</v>
+      </c>
+      <c r="H8" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" t="b">
+        <v>1</v>
+      </c>
+      <c r="J8" t="s">
+        <v>55</v>
+      </c>
+      <c r="K8" t="b">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q8" t="b">
+        <v>0</v>
+      </c>
+      <c r="R8" t="s">
+        <v>43</v>
+      </c>
+      <c r="S8" t="s">
         <v>44</v>
       </c>
-      <c r="E8" t="b">
-        <v>1</v>
-      </c>
-      <c r="F8" t="s">
-        <v>51</v>
-      </c>
-      <c r="G8" t="b">
-        <v>1</v>
-      </c>
-      <c r="H8" t="b">
-        <v>1</v>
-      </c>
-      <c r="I8" t="s">
-        <v>46</v>
-      </c>
-      <c r="J8" t="b">
-        <v>1</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="s">
-        <v>29</v>
-      </c>
-      <c r="P8" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>47</v>
-      </c>
-      <c r="R8" t="s">
-        <v>48</v>
-      </c>
-      <c r="S8" t="b">
-        <v>0</v>
-      </c>
-      <c r="T8" t="s">
-        <v>28</v>
+      <c r="T8" t="b">
+        <v>0</v>
       </c>
       <c r="U8" t="s">
         <v>29</v>
       </c>
+      <c r="V8" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B9" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C9" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E9" t="b">
+        <v>1</v>
+      </c>
+      <c r="F9" t="b">
+        <v>0</v>
+      </c>
+      <c r="G9" t="s">
+        <v>58</v>
+      </c>
+      <c r="H9" t="b">
+        <v>1</v>
+      </c>
+      <c r="I9" t="b">
+        <v>1</v>
+      </c>
+      <c r="J9" t="s">
+        <v>59</v>
+      </c>
+      <c r="K9" t="b">
+        <v>1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q9" t="b">
+        <v>0</v>
+      </c>
+      <c r="R9" t="s">
+        <v>43</v>
+      </c>
+      <c r="S9" t="s">
         <v>44</v>
       </c>
-      <c r="E9" t="b">
-        <v>1</v>
-      </c>
-      <c r="F9" t="s">
-        <v>54</v>
-      </c>
-      <c r="G9" t="b">
-        <v>1</v>
-      </c>
-      <c r="H9" t="b">
-        <v>1</v>
-      </c>
-      <c r="I9" t="s">
-        <v>55</v>
-      </c>
-      <c r="J9" t="b">
-        <v>1</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>66</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="s">
-        <v>29</v>
-      </c>
-      <c r="P9" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>47</v>
-      </c>
-      <c r="R9" t="s">
-        <v>48</v>
-      </c>
-      <c r="S9" t="b">
-        <v>0</v>
-      </c>
-      <c r="T9" t="s">
-        <v>28</v>
+      <c r="T9" t="b">
+        <v>0</v>
       </c>
       <c r="U9" t="s">
         <v>29</v>
       </c>
+      <c r="V9" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B10" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C10" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D10" t="s">
+        <v>40</v>
+      </c>
+      <c r="E10" t="b">
+        <v>1</v>
+      </c>
+      <c r="F10" t="b">
+        <v>0</v>
+      </c>
+      <c r="G10" t="s">
+        <v>62</v>
+      </c>
+      <c r="H10" t="b">
+        <v>1</v>
+      </c>
+      <c r="I10" t="b">
+        <v>1</v>
+      </c>
+      <c r="J10" t="s">
+        <v>63</v>
+      </c>
+      <c r="K10" t="b">
+        <v>1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q10" t="b">
+        <v>0</v>
+      </c>
+      <c r="R10" t="s">
+        <v>43</v>
+      </c>
+      <c r="S10" t="s">
         <v>44</v>
       </c>
-      <c r="E10" t="b">
-        <v>1</v>
-      </c>
-      <c r="F10" t="s">
-        <v>58</v>
-      </c>
-      <c r="G10" t="b">
-        <v>1</v>
-      </c>
-      <c r="H10" t="b">
-        <v>1</v>
-      </c>
-      <c r="I10" t="s">
-        <v>59</v>
-      </c>
-      <c r="J10" t="b">
-        <v>1</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="s">
-        <v>29</v>
-      </c>
-      <c r="P10" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>47</v>
-      </c>
-      <c r="R10" t="s">
-        <v>48</v>
-      </c>
-      <c r="S10" t="b">
-        <v>0</v>
-      </c>
-      <c r="T10" t="s">
-        <v>28</v>
+      <c r="T10" t="b">
+        <v>0</v>
       </c>
       <c r="U10" t="s">
         <v>29</v>
       </c>
+      <c r="V10" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B11" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C11" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D11" t="s">
+        <v>40</v>
+      </c>
+      <c r="E11" t="b">
+        <v>1</v>
+      </c>
+      <c r="F11" t="b">
+        <v>0</v>
+      </c>
+      <c r="G11" t="s">
+        <v>66</v>
+      </c>
+      <c r="H11" t="b">
+        <v>1</v>
+      </c>
+      <c r="I11" t="b">
+        <v>1</v>
+      </c>
+      <c r="J11" t="s">
+        <v>42</v>
+      </c>
+      <c r="K11" t="b">
+        <v>1</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q11" t="b">
+        <v>0</v>
+      </c>
+      <c r="R11" t="s">
+        <v>43</v>
+      </c>
+      <c r="S11" t="s">
         <v>44</v>
       </c>
-      <c r="E11" t="b">
-        <v>1</v>
-      </c>
-      <c r="F11" t="s">
-        <v>62</v>
-      </c>
-      <c r="G11" t="b">
-        <v>1</v>
-      </c>
-      <c r="H11" t="b">
-        <v>1</v>
-      </c>
-      <c r="I11" t="s">
-        <v>63</v>
-      </c>
-      <c r="J11" t="b">
-        <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="s">
-        <v>29</v>
-      </c>
-      <c r="P11" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>47</v>
-      </c>
-      <c r="R11" t="s">
-        <v>48</v>
-      </c>
-      <c r="S11" t="b">
-        <v>0</v>
-      </c>
-      <c r="T11" t="s">
-        <v>28</v>
+      <c r="T11" t="b">
+        <v>0</v>
       </c>
       <c r="U11" t="s">
         <v>29</v>
       </c>
+      <c r="V11" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B12" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C12" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D12" t="s">
+        <v>40</v>
+      </c>
+      <c r="E12" t="b">
+        <v>1</v>
+      </c>
+      <c r="F12" t="b">
+        <v>0</v>
+      </c>
+      <c r="G12" t="s">
+        <v>69</v>
+      </c>
+      <c r="H12" t="b">
+        <v>1</v>
+      </c>
+      <c r="I12" t="b">
+        <v>1</v>
+      </c>
+      <c r="J12" t="s">
+        <v>70</v>
+      </c>
+      <c r="K12" t="b">
+        <v>1</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R12" t="s">
+        <v>43</v>
+      </c>
+      <c r="S12" t="s">
         <v>44</v>
       </c>
-      <c r="E12" t="b">
-        <v>1</v>
-      </c>
-      <c r="F12" t="s">
-        <v>66</v>
-      </c>
-      <c r="G12" t="b">
-        <v>1</v>
-      </c>
-      <c r="H12" t="b">
-        <v>1</v>
-      </c>
-      <c r="I12" t="s">
-        <v>67</v>
-      </c>
-      <c r="J12" t="b">
-        <v>1</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="s">
-        <v>29</v>
-      </c>
-      <c r="P12" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>47</v>
-      </c>
-      <c r="R12" t="s">
-        <v>48</v>
-      </c>
-      <c r="S12" t="b">
-        <v>0</v>
-      </c>
-      <c r="T12" t="s">
-        <v>28</v>
+      <c r="T12" t="b">
+        <v>0</v>
       </c>
       <c r="U12" t="s">
         <v>29</v>
       </c>
+      <c r="V12" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B13" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C13" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D13" t="s">
+        <v>40</v>
+      </c>
+      <c r="E13" t="b">
+        <v>1</v>
+      </c>
+      <c r="F13" t="b">
+        <v>0</v>
+      </c>
+      <c r="G13" t="s">
+        <v>73</v>
+      </c>
+      <c r="H13" t="b">
+        <v>1</v>
+      </c>
+      <c r="I13" t="b">
+        <v>1</v>
+      </c>
+      <c r="J13" t="s">
+        <v>74</v>
+      </c>
+      <c r="K13" t="b">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q13" t="b">
+        <v>0</v>
+      </c>
+      <c r="R13" t="s">
+        <v>43</v>
+      </c>
+      <c r="S13" t="s">
         <v>44</v>
       </c>
-      <c r="E13" t="b">
-        <v>1</v>
-      </c>
-      <c r="F13" t="s">
-        <v>70</v>
-      </c>
-      <c r="G13" t="b">
-        <v>1</v>
-      </c>
-      <c r="H13" t="b">
-        <v>1</v>
-      </c>
-      <c r="I13" t="s">
-        <v>46</v>
-      </c>
-      <c r="J13" t="b">
-        <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="s">
-        <v>29</v>
-      </c>
-      <c r="P13" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>47</v>
-      </c>
-      <c r="R13" t="s">
-        <v>48</v>
-      </c>
-      <c r="S13" t="b">
-        <v>0</v>
-      </c>
-      <c r="T13" t="s">
-        <v>28</v>
+      <c r="T13" t="b">
+        <v>0</v>
       </c>
       <c r="U13" t="s">
         <v>29</v>
       </c>
+      <c r="V13" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B14" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C14" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D14" t="s">
+        <v>40</v>
+      </c>
+      <c r="E14" t="b">
+        <v>1</v>
+      </c>
+      <c r="F14" t="b">
+        <v>0</v>
+      </c>
+      <c r="G14" t="s">
+        <v>77</v>
+      </c>
+      <c r="H14" t="b">
+        <v>1</v>
+      </c>
+      <c r="I14" t="b">
+        <v>1</v>
+      </c>
+      <c r="J14" t="s">
+        <v>78</v>
+      </c>
+      <c r="K14" t="b">
+        <v>1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q14" t="b">
+        <v>0</v>
+      </c>
+      <c r="R14" t="s">
+        <v>43</v>
+      </c>
+      <c r="S14" t="s">
         <v>44</v>
       </c>
-      <c r="E14" t="b">
-        <v>1</v>
-      </c>
-      <c r="F14" t="s">
-        <v>73</v>
-      </c>
-      <c r="G14" t="b">
-        <v>1</v>
-      </c>
-      <c r="H14" t="b">
-        <v>1</v>
-      </c>
-      <c r="I14" t="s">
-        <v>74</v>
-      </c>
-      <c r="J14" t="b">
-        <v>1</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="s">
-        <v>29</v>
-      </c>
-      <c r="P14" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>47</v>
-      </c>
-      <c r="R14" t="s">
-        <v>48</v>
-      </c>
-      <c r="S14" t="b">
-        <v>0</v>
-      </c>
-      <c r="T14" t="s">
-        <v>28</v>
+      <c r="T14" t="b">
+        <v>0</v>
       </c>
       <c r="U14" t="s">
         <v>29</v>
       </c>
+      <c r="V14" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B15" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C15" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="D15" t="s">
+        <v>35</v>
+      </c>
+      <c r="E15" t="b">
+        <v>0</v>
+      </c>
+      <c r="F15" t="b">
+        <v>0</v>
+      </c>
+      <c r="G15" t="s">
+        <v>81</v>
+      </c>
+      <c r="H15" t="b">
+        <v>1</v>
+      </c>
+      <c r="I15" t="b">
+        <v>1</v>
+      </c>
+      <c r="J15" t="s">
+        <v>51</v>
+      </c>
+      <c r="K15" t="b">
+        <v>1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q15" t="b">
+        <v>0</v>
+      </c>
+      <c r="R15" t="s">
+        <v>43</v>
+      </c>
+      <c r="S15" t="s">
         <v>44</v>
       </c>
-      <c r="E15" t="b">
-        <v>1</v>
-      </c>
-      <c r="F15" t="s">
-        <v>77</v>
-      </c>
-      <c r="G15" t="b">
-        <v>1</v>
-      </c>
-      <c r="H15" t="b">
-        <v>1</v>
-      </c>
-      <c r="I15" t="s">
-        <v>78</v>
-      </c>
-      <c r="J15" t="b">
-        <v>1</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="s">
-        <v>29</v>
-      </c>
-      <c r="P15" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>47</v>
-      </c>
-      <c r="R15" t="s">
-        <v>48</v>
-      </c>
-      <c r="S15" t="b">
-        <v>0</v>
-      </c>
-      <c r="T15" t="s">
-        <v>28</v>
+      <c r="T15" t="b">
+        <v>0</v>
       </c>
       <c r="U15" t="s">
         <v>29</v>
       </c>
+      <c r="V15" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>41</v>
+        <v>82</v>
       </c>
       <c r="B16" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C16" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="D16" t="s">
+        <v>85</v>
+      </c>
+      <c r="E16" t="b">
+        <v>1</v>
+      </c>
+      <c r="F16" t="b">
+        <v>0</v>
+      </c>
+      <c r="G16" t="s">
+        <v>86</v>
+      </c>
+      <c r="H16" t="b">
+        <v>1</v>
+      </c>
+      <c r="I16" t="b">
+        <v>1</v>
+      </c>
+      <c r="J16" t="s">
+        <v>51</v>
+      </c>
+      <c r="K16" t="b">
+        <v>1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q16" t="b">
+        <v>0</v>
+      </c>
+      <c r="R16" t="s">
+        <v>87</v>
+      </c>
+      <c r="S16" t="s">
         <v>44</v>
       </c>
-      <c r="E16" t="b">
-        <v>1</v>
-      </c>
-      <c r="F16" t="s">
-        <v>81</v>
-      </c>
-      <c r="G16" t="b">
-        <v>1</v>
-      </c>
-      <c r="H16" t="b">
-        <v>1</v>
-      </c>
-      <c r="I16" t="s">
-        <v>82</v>
-      </c>
-      <c r="J16" t="b">
-        <v>1</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="s">
-        <v>29</v>
-      </c>
-      <c r="P16" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>47</v>
-      </c>
-      <c r="R16" t="s">
-        <v>48</v>
-      </c>
-      <c r="S16" t="b">
-        <v>0</v>
-      </c>
-      <c r="T16" t="s">
-        <v>28</v>
+      <c r="T16" t="b">
+        <v>0</v>
       </c>
       <c r="U16" t="s">
         <v>29</v>
       </c>
+      <c r="V16" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>41</v>
+        <v>82</v>
       </c>
       <c r="B17" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C17" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="D17" t="s">
-        <v>39</v>
+        <v>89</v>
       </c>
       <c r="E17" t="b">
-        <v>0</v>
-      </c>
-      <c r="F17" t="s">
-        <v>84</v>
-      </c>
-      <c r="G17" t="b">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="F17" t="b">
+        <v>0</v>
+      </c>
+      <c r="G17" t="s">
+        <v>90</v>
       </c>
       <c r="H17" t="b">
         <v>1</v>
       </c>
-      <c r="I17" t="s">
-        <v>55</v>
-      </c>
-      <c r="J17" t="b">
-        <v>1</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
+      <c r="I17" t="b">
+        <v>1</v>
+      </c>
+      <c r="J17" t="s">
+        <v>51</v>
+      </c>
+      <c r="K17" t="b">
+        <v>1</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
       </c>
-      <c r="O17" t="s">
-        <v>29</v>
-      </c>
-      <c r="P17" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>47</v>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q17" t="b">
+        <v>0</v>
       </c>
       <c r="R17" t="s">
-        <v>48</v>
-      </c>
-      <c r="S17" t="b">
-        <v>0</v>
-      </c>
-      <c r="T17" t="s">
-        <v>28</v>
+        <v>87</v>
+      </c>
+      <c r="S17" t="s">
+        <v>44</v>
+      </c>
+      <c r="T17" t="b">
+        <v>0</v>
       </c>
       <c r="U17" t="s">
         <v>29</v>
       </c>
+      <c r="V17" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B18" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C18" t="s">
+        <v>92</v>
+      </c>
+      <c r="D18" t="s">
+        <v>40</v>
+      </c>
+      <c r="E18" t="b">
+        <v>1</v>
+      </c>
+      <c r="F18" t="b">
+        <v>0</v>
+      </c>
+      <c r="G18" t="s">
+        <v>93</v>
+      </c>
+      <c r="H18" t="b">
+        <v>1</v>
+      </c>
+      <c r="I18" t="b">
+        <v>1</v>
+      </c>
+      <c r="J18" t="s">
+        <v>51</v>
+      </c>
+      <c r="K18" t="b">
+        <v>1</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q18" t="b">
+        <v>0</v>
+      </c>
+      <c r="R18" t="s">
         <v>87</v>
       </c>
-      <c r="D18" t="s">
-        <v>88</v>
-      </c>
-      <c r="E18" t="b">
-        <v>1</v>
-      </c>
-      <c r="F18" t="s">
-        <v>89</v>
-      </c>
-      <c r="G18" t="b">
-        <v>1</v>
-      </c>
-      <c r="H18" t="b">
-        <v>1</v>
-      </c>
-      <c r="I18" t="s">
-        <v>55</v>
-      </c>
-      <c r="J18" t="b">
-        <v>1</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="s">
-        <v>29</v>
-      </c>
-      <c r="P18" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="s">
-        <v>90</v>
-      </c>
-      <c r="R18" t="s">
-        <v>48</v>
-      </c>
-      <c r="S18" t="b">
-        <v>0</v>
-      </c>
-      <c r="T18" t="s">
-        <v>28</v>
+      <c r="S18" t="s">
+        <v>44</v>
+      </c>
+      <c r="T18" t="b">
+        <v>0</v>
       </c>
       <c r="U18" t="s">
         <v>29</v>
       </c>
+      <c r="V18" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B19" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C19" t="s">
+        <v>95</v>
+      </c>
+      <c r="D19" t="s">
+        <v>96</v>
+      </c>
+      <c r="E19" t="b">
+        <v>1</v>
+      </c>
+      <c r="F19" t="b">
+        <v>0</v>
+      </c>
+      <c r="G19" t="s">
+        <v>97</v>
+      </c>
+      <c r="H19" t="b">
+        <v>1</v>
+      </c>
+      <c r="I19" t="b">
+        <v>1</v>
+      </c>
+      <c r="J19" t="s">
+        <v>51</v>
+      </c>
+      <c r="K19" t="b">
+        <v>1</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q19" t="b">
+        <v>0</v>
+      </c>
+      <c r="R19" t="s">
         <v>87</v>
       </c>
-      <c r="D19" t="s">
-        <v>92</v>
-      </c>
-      <c r="E19" t="b">
-        <v>1</v>
-      </c>
-      <c r="F19" t="s">
-        <v>93</v>
-      </c>
-      <c r="G19" t="b">
-        <v>1</v>
-      </c>
-      <c r="H19" t="b">
-        <v>1</v>
-      </c>
-      <c r="I19" t="s">
-        <v>55</v>
-      </c>
-      <c r="J19" t="b">
-        <v>1</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="s">
-        <v>29</v>
-      </c>
-      <c r="P19" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="s">
-        <v>90</v>
-      </c>
-      <c r="R19" t="s">
-        <v>48</v>
-      </c>
-      <c r="S19" t="b">
-        <v>0</v>
-      </c>
-      <c r="T19" t="s">
-        <v>28</v>
+      <c r="S19" t="s">
+        <v>44</v>
+      </c>
+      <c r="T19" t="b">
+        <v>0</v>
       </c>
       <c r="U19" t="s">
         <v>29</v>
       </c>
+      <c r="V19" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
+        <v>22</v>
+      </c>
+      <c r="B20" t="s">
+        <v>98</v>
+      </c>
+      <c r="C20" t="s">
+        <v>99</v>
+      </c>
+      <c r="D20" t="s">
         <v>85</v>
       </c>
-      <c r="B20" t="s">
-        <v>94</v>
-      </c>
-      <c r="C20" t="s">
-        <v>95</v>
-      </c>
-      <c r="D20" t="s">
-        <v>44</v>
-      </c>
       <c r="E20" t="b">
         <v>1</v>
       </c>
-      <c r="F20" t="s">
-        <v>96</v>
-      </c>
-      <c r="G20" t="b">
-        <v>1</v>
+      <c r="F20" t="b">
+        <v>0</v>
+      </c>
+      <c r="G20" t="s">
+        <v>100</v>
       </c>
       <c r="H20" t="b">
         <v>1</v>
       </c>
-      <c r="I20" t="s">
-        <v>55</v>
-      </c>
-      <c r="J20" t="b">
-        <v>1</v>
-      </c>
-      <c r="K20" t="n">
+      <c r="I20" t="b">
+        <v>1</v>
+      </c>
+      <c r="J20"/>
+      <c r="K20" t="b">
         <v>0</v>
       </c>
       <c r="L20" t="n">
@@ -2391,60 +2454,61 @@
       <c r="N20" t="n">
         <v>0</v>
       </c>
-      <c r="O20" t="s">
-        <v>29</v>
-      </c>
-      <c r="P20" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="s">
-        <v>90</v>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q20" t="b">
+        <v>0</v>
       </c>
       <c r="R20" t="s">
-        <v>48</v>
-      </c>
-      <c r="S20" t="b">
-        <v>0</v>
-      </c>
-      <c r="T20" t="s">
-        <v>28</v>
+        <v>101</v>
+      </c>
+      <c r="S20" t="s">
+        <v>102</v>
+      </c>
+      <c r="T20" t="b">
+        <v>0</v>
       </c>
       <c r="U20" t="s">
         <v>29</v>
       </c>
+      <c r="V20" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
+        <v>22</v>
+      </c>
+      <c r="B21" t="s">
+        <v>103</v>
+      </c>
+      <c r="C21" t="s">
+        <v>24</v>
+      </c>
+      <c r="D21" t="s">
         <v>85</v>
       </c>
-      <c r="B21" t="s">
-        <v>97</v>
-      </c>
-      <c r="C21" t="s">
-        <v>98</v>
-      </c>
-      <c r="D21" t="s">
-        <v>99</v>
-      </c>
       <c r="E21" t="b">
         <v>1</v>
       </c>
-      <c r="F21" t="s">
-        <v>100</v>
-      </c>
-      <c r="G21" t="b">
-        <v>1</v>
+      <c r="F21" t="b">
+        <v>1</v>
+      </c>
+      <c r="G21" t="s">
+        <v>104</v>
       </c>
       <c r="H21" t="b">
         <v>1</v>
       </c>
-      <c r="I21" t="s">
-        <v>55</v>
-      </c>
-      <c r="J21" t="b">
-        <v>1</v>
-      </c>
-      <c r="K21" t="n">
+      <c r="I21" t="b">
+        <v>1</v>
+      </c>
+      <c r="J21"/>
+      <c r="K21" t="b">
         <v>0</v>
       </c>
       <c r="L21" t="n">
@@ -2454,249 +2518,261 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="s">
-        <v>29</v>
-      </c>
-      <c r="P21" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>90</v>
+        <v>5</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q21" t="b">
+        <v>0</v>
       </c>
       <c r="R21" t="s">
-        <v>48</v>
-      </c>
-      <c r="S21" t="b">
-        <v>0</v>
-      </c>
-      <c r="T21" t="s">
+        <v>27</v>
+      </c>
+      <c r="S21" t="s">
         <v>28</v>
+      </c>
+      <c r="T21" t="b">
+        <v>0</v>
       </c>
       <c r="U21" t="s">
         <v>29</v>
       </c>
+      <c r="V21" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B22" t="s">
+        <v>105</v>
+      </c>
+      <c r="C22" t="s">
+        <v>99</v>
+      </c>
+      <c r="D22" t="s">
+        <v>89</v>
+      </c>
+      <c r="E22" t="b">
+        <v>1</v>
+      </c>
+      <c r="F22" t="b">
+        <v>0</v>
+      </c>
+      <c r="G22" t="s">
+        <v>106</v>
+      </c>
+      <c r="H22" t="b">
+        <v>1</v>
+      </c>
+      <c r="I22" t="b">
+        <v>1</v>
+      </c>
+      <c r="J22"/>
+      <c r="K22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q22" t="b">
+        <v>0</v>
+      </c>
+      <c r="R22" t="s">
         <v>101</v>
       </c>
-      <c r="C22" t="s">
+      <c r="S22" t="s">
         <v>102</v>
       </c>
-      <c r="D22" t="s">
-        <v>88</v>
-      </c>
-      <c r="E22" t="b">
-        <v>1</v>
-      </c>
-      <c r="F22" t="s">
-        <v>103</v>
-      </c>
-      <c r="G22" t="b">
-        <v>1</v>
-      </c>
-      <c r="H22" t="b">
-        <v>1</v>
-      </c>
-      <c r="I22"/>
-      <c r="J22" t="b">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="s">
-        <v>29</v>
-      </c>
-      <c r="P22" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="s">
-        <v>104</v>
-      </c>
-      <c r="R22" t="s">
-        <v>105</v>
-      </c>
-      <c r="S22" t="b">
-        <v>0</v>
-      </c>
-      <c r="T22" t="s">
-        <v>28</v>
+      <c r="T22" t="b">
+        <v>0</v>
       </c>
       <c r="U22" t="s">
         <v>29</v>
       </c>
+      <c r="V22" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C23" t="s">
-        <v>33</v>
+        <v>108</v>
       </c>
       <c r="D23" t="s">
-        <v>88</v>
+        <v>40</v>
       </c>
       <c r="E23" t="b">
         <v>1</v>
       </c>
-      <c r="F23" t="s">
-        <v>107</v>
-      </c>
-      <c r="G23" t="b">
-        <v>1</v>
+      <c r="F23" t="b">
+        <v>0</v>
+      </c>
+      <c r="G23" t="s">
+        <v>109</v>
       </c>
       <c r="H23" t="b">
         <v>1</v>
       </c>
-      <c r="I23"/>
-      <c r="J23" t="b">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
+      <c r="I23" t="b">
+        <v>1</v>
+      </c>
+      <c r="J23"/>
+      <c r="K23" t="b">
         <v>0</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
       </c>
-      <c r="O23" t="s">
-        <v>29</v>
-      </c>
-      <c r="P23" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="s">
-        <v>104</v>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q23" t="b">
+        <v>0</v>
       </c>
       <c r="R23" t="s">
-        <v>105</v>
-      </c>
-      <c r="S23" t="b">
-        <v>0</v>
-      </c>
-      <c r="T23" t="s">
-        <v>28</v>
+        <v>101</v>
+      </c>
+      <c r="S23" t="s">
+        <v>102</v>
+      </c>
+      <c r="T23" t="b">
+        <v>0</v>
       </c>
       <c r="U23" t="s">
         <v>29</v>
       </c>
+      <c r="V23" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C24" t="s">
+        <v>111</v>
+      </c>
+      <c r="D24" t="s">
+        <v>25</v>
+      </c>
+      <c r="E24" t="b">
+        <v>1</v>
+      </c>
+      <c r="F24" t="b">
+        <v>0</v>
+      </c>
+      <c r="G24" t="s">
+        <v>112</v>
+      </c>
+      <c r="H24" t="b">
+        <v>1</v>
+      </c>
+      <c r="I24" t="b">
+        <v>1</v>
+      </c>
+      <c r="J24"/>
+      <c r="K24" t="b">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q24" t="b">
+        <v>0</v>
+      </c>
+      <c r="R24" t="s">
+        <v>101</v>
+      </c>
+      <c r="S24" t="s">
         <v>102</v>
       </c>
-      <c r="D24" t="s">
-        <v>92</v>
-      </c>
-      <c r="E24" t="b">
-        <v>1</v>
-      </c>
-      <c r="F24" t="s">
-        <v>109</v>
-      </c>
-      <c r="G24" t="b">
-        <v>1</v>
-      </c>
-      <c r="H24" t="b">
-        <v>1</v>
-      </c>
-      <c r="I24"/>
-      <c r="J24" t="b">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="s">
-        <v>29</v>
-      </c>
-      <c r="P24" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="s">
-        <v>104</v>
-      </c>
-      <c r="R24" t="s">
-        <v>105</v>
-      </c>
-      <c r="S24" t="b">
-        <v>0</v>
-      </c>
-      <c r="T24" t="s">
-        <v>28</v>
+      <c r="T24" t="b">
+        <v>0</v>
       </c>
       <c r="U24" t="s">
         <v>29</v>
       </c>
+      <c r="V24" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C25" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D25" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="E25" t="b">
         <v>1</v>
       </c>
-      <c r="F25" t="s">
-        <v>112</v>
-      </c>
-      <c r="G25" t="b">
-        <v>1</v>
+      <c r="F25" t="b">
+        <v>0</v>
+      </c>
+      <c r="G25" t="s">
+        <v>115</v>
       </c>
       <c r="H25" t="b">
         <v>1</v>
       </c>
-      <c r="I25"/>
-      <c r="J25" t="b">
-        <v>0</v>
-      </c>
-      <c r="K25" t="n">
+      <c r="I25" t="b">
+        <v>1</v>
+      </c>
+      <c r="J25"/>
+      <c r="K25" t="b">
         <v>0</v>
       </c>
       <c r="L25" t="n">
@@ -2708,58 +2784,61 @@
       <c r="N25" t="n">
         <v>0</v>
       </c>
-      <c r="O25" t="s">
-        <v>29</v>
-      </c>
-      <c r="P25" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="s">
-        <v>104</v>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q25" t="b">
+        <v>0</v>
       </c>
       <c r="R25" t="s">
-        <v>105</v>
-      </c>
-      <c r="S25" t="b">
-        <v>0</v>
-      </c>
-      <c r="T25" t="s">
-        <v>28</v>
+        <v>101</v>
+      </c>
+      <c r="S25" t="s">
+        <v>102</v>
+      </c>
+      <c r="T25" t="b">
+        <v>0</v>
       </c>
       <c r="U25" t="s">
         <v>29</v>
       </c>
+      <c r="V25" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B26" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C26" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D26" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E26" t="b">
         <v>1</v>
       </c>
-      <c r="F26" t="s">
-        <v>115</v>
-      </c>
-      <c r="G26" t="b">
-        <v>1</v>
+      <c r="F26" t="b">
+        <v>0</v>
+      </c>
+      <c r="G26" t="s">
+        <v>118</v>
       </c>
       <c r="H26" t="b">
         <v>1</v>
       </c>
-      <c r="I26"/>
-      <c r="J26" t="b">
-        <v>0</v>
-      </c>
-      <c r="K26" t="n">
+      <c r="I26" t="b">
+        <v>1</v>
+      </c>
+      <c r="J26"/>
+      <c r="K26" t="b">
         <v>0</v>
       </c>
       <c r="L26" t="n">
@@ -2771,58 +2850,61 @@
       <c r="N26" t="n">
         <v>0</v>
       </c>
-      <c r="O26" t="s">
-        <v>29</v>
-      </c>
-      <c r="P26" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="s">
-        <v>104</v>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q26" t="b">
+        <v>0</v>
       </c>
       <c r="R26" t="s">
-        <v>105</v>
-      </c>
-      <c r="S26" t="b">
-        <v>0</v>
-      </c>
-      <c r="T26" t="s">
-        <v>28</v>
+        <v>101</v>
+      </c>
+      <c r="S26" t="s">
+        <v>102</v>
+      </c>
+      <c r="T26" t="b">
+        <v>0</v>
       </c>
       <c r="U26" t="s">
         <v>29</v>
       </c>
+      <c r="V26" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B27" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C27" t="s">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="D27" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E27" t="b">
-        <v>1</v>
-      </c>
-      <c r="F27" t="s">
-        <v>118</v>
-      </c>
-      <c r="G27" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="F27" t="b">
+        <v>0</v>
+      </c>
+      <c r="G27" t="s">
+        <v>120</v>
       </c>
       <c r="H27" t="b">
         <v>1</v>
       </c>
-      <c r="I27"/>
-      <c r="J27" t="b">
-        <v>0</v>
-      </c>
-      <c r="K27" t="n">
+      <c r="I27" t="b">
+        <v>1</v>
+      </c>
+      <c r="J27"/>
+      <c r="K27" t="b">
         <v>0</v>
       </c>
       <c r="L27" t="n">
@@ -2832,60 +2914,63 @@
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="s">
-        <v>29</v>
-      </c>
-      <c r="P27" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="s">
-        <v>104</v>
+        <v>1</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q27" t="b">
+        <v>0</v>
       </c>
       <c r="R27" t="s">
-        <v>105</v>
-      </c>
-      <c r="S27" t="b">
-        <v>0</v>
-      </c>
-      <c r="T27" t="s">
-        <v>28</v>
+        <v>101</v>
+      </c>
+      <c r="S27" t="s">
+        <v>102</v>
+      </c>
+      <c r="T27" t="b">
+        <v>0</v>
       </c>
       <c r="U27" t="s">
         <v>29</v>
       </c>
+      <c r="V27" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B28" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C28" t="s">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="D28" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E28" t="b">
         <v>1</v>
       </c>
-      <c r="F28" t="s">
-        <v>121</v>
-      </c>
-      <c r="G28" t="b">
-        <v>1</v>
+      <c r="F28" t="b">
+        <v>0</v>
+      </c>
+      <c r="G28" t="s">
+        <v>122</v>
       </c>
       <c r="H28" t="b">
         <v>1</v>
       </c>
-      <c r="I28"/>
-      <c r="J28" t="b">
-        <v>0</v>
-      </c>
-      <c r="K28" t="n">
+      <c r="I28" t="b">
+        <v>1</v>
+      </c>
+      <c r="J28"/>
+      <c r="K28" t="b">
         <v>0</v>
       </c>
       <c r="L28" t="n">
@@ -2895,60 +2980,63 @@
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="s">
-        <v>29</v>
-      </c>
-      <c r="P28" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="s">
-        <v>104</v>
+        <v>1</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q28" t="b">
+        <v>0</v>
       </c>
       <c r="R28" t="s">
-        <v>105</v>
-      </c>
-      <c r="S28" t="b">
-        <v>0</v>
-      </c>
-      <c r="T28" t="s">
-        <v>28</v>
+        <v>101</v>
+      </c>
+      <c r="S28" t="s">
+        <v>102</v>
+      </c>
+      <c r="T28" t="b">
+        <v>0</v>
       </c>
       <c r="U28" t="s">
         <v>29</v>
       </c>
+      <c r="V28" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B29" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C29" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D29" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E29" t="b">
         <v>1</v>
       </c>
-      <c r="F29" t="s">
-        <v>124</v>
-      </c>
-      <c r="G29" t="b">
-        <v>1</v>
+      <c r="F29" t="b">
+        <v>0</v>
+      </c>
+      <c r="G29" t="s">
+        <v>125</v>
       </c>
       <c r="H29" t="b">
         <v>1</v>
       </c>
-      <c r="I29"/>
-      <c r="J29" t="b">
-        <v>0</v>
-      </c>
-      <c r="K29" t="n">
+      <c r="I29" t="b">
+        <v>1</v>
+      </c>
+      <c r="J29"/>
+      <c r="K29" t="b">
         <v>0</v>
       </c>
       <c r="L29" t="n">
@@ -2960,58 +3048,61 @@
       <c r="N29" t="n">
         <v>0</v>
       </c>
-      <c r="O29" t="s">
-        <v>29</v>
-      </c>
-      <c r="P29" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="s">
-        <v>104</v>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q29" t="b">
+        <v>0</v>
       </c>
       <c r="R29" t="s">
-        <v>105</v>
-      </c>
-      <c r="S29" t="b">
-        <v>0</v>
-      </c>
-      <c r="T29" t="s">
-        <v>28</v>
+        <v>101</v>
+      </c>
+      <c r="S29" t="s">
+        <v>102</v>
+      </c>
+      <c r="T29" t="b">
+        <v>0</v>
       </c>
       <c r="U29" t="s">
         <v>29</v>
       </c>
+      <c r="V29" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B30" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C30" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D30" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E30" t="b">
         <v>1</v>
       </c>
-      <c r="F30" t="s">
-        <v>127</v>
-      </c>
-      <c r="G30" t="b">
-        <v>1</v>
+      <c r="F30" t="b">
+        <v>0</v>
+      </c>
+      <c r="G30" t="s">
+        <v>128</v>
       </c>
       <c r="H30" t="b">
         <v>1</v>
       </c>
-      <c r="I30"/>
-      <c r="J30" t="b">
-        <v>0</v>
-      </c>
-      <c r="K30" t="n">
+      <c r="I30" t="b">
+        <v>1</v>
+      </c>
+      <c r="J30"/>
+      <c r="K30" t="b">
         <v>0</v>
       </c>
       <c r="L30" t="n">
@@ -3023,58 +3114,61 @@
       <c r="N30" t="n">
         <v>0</v>
       </c>
-      <c r="O30" t="s">
-        <v>29</v>
-      </c>
-      <c r="P30" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="s">
-        <v>104</v>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q30" t="b">
+        <v>0</v>
       </c>
       <c r="R30" t="s">
-        <v>105</v>
-      </c>
-      <c r="S30" t="b">
-        <v>0</v>
-      </c>
-      <c r="T30" t="s">
-        <v>28</v>
+        <v>101</v>
+      </c>
+      <c r="S30" t="s">
+        <v>102</v>
+      </c>
+      <c r="T30" t="b">
+        <v>0</v>
       </c>
       <c r="U30" t="s">
         <v>29</v>
       </c>
+      <c r="V30" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B31" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C31" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D31" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E31" t="b">
         <v>1</v>
       </c>
-      <c r="F31" t="s">
-        <v>130</v>
-      </c>
-      <c r="G31" t="b">
-        <v>1</v>
+      <c r="F31" t="b">
+        <v>0</v>
+      </c>
+      <c r="G31" t="s">
+        <v>131</v>
       </c>
       <c r="H31" t="b">
         <v>1</v>
       </c>
-      <c r="I31"/>
-      <c r="J31" t="b">
-        <v>0</v>
-      </c>
-      <c r="K31" t="n">
+      <c r="I31" t="b">
+        <v>1</v>
+      </c>
+      <c r="J31"/>
+      <c r="K31" t="b">
         <v>0</v>
       </c>
       <c r="L31" t="n">
@@ -3086,58 +3180,61 @@
       <c r="N31" t="n">
         <v>0</v>
       </c>
-      <c r="O31" t="s">
-        <v>29</v>
-      </c>
-      <c r="P31" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="s">
-        <v>104</v>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q31" t="b">
+        <v>0</v>
       </c>
       <c r="R31" t="s">
-        <v>105</v>
-      </c>
-      <c r="S31" t="b">
-        <v>0</v>
-      </c>
-      <c r="T31" t="s">
-        <v>28</v>
+        <v>101</v>
+      </c>
+      <c r="S31" t="s">
+        <v>102</v>
+      </c>
+      <c r="T31" t="b">
+        <v>0</v>
       </c>
       <c r="U31" t="s">
         <v>29</v>
       </c>
+      <c r="V31" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B32" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C32" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D32" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E32" t="b">
         <v>1</v>
       </c>
-      <c r="F32" t="s">
-        <v>133</v>
-      </c>
-      <c r="G32" t="b">
-        <v>1</v>
+      <c r="F32" t="b">
+        <v>0</v>
+      </c>
+      <c r="G32" t="s">
+        <v>134</v>
       </c>
       <c r="H32" t="b">
         <v>1</v>
       </c>
-      <c r="I32"/>
-      <c r="J32" t="b">
-        <v>0</v>
-      </c>
-      <c r="K32" t="n">
+      <c r="I32" t="b">
+        <v>1</v>
+      </c>
+      <c r="J32"/>
+      <c r="K32" t="b">
         <v>0</v>
       </c>
       <c r="L32" t="n">
@@ -3149,58 +3246,61 @@
       <c r="N32" t="n">
         <v>0</v>
       </c>
-      <c r="O32" t="s">
-        <v>29</v>
-      </c>
-      <c r="P32" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q32" t="s">
-        <v>104</v>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q32" t="b">
+        <v>0</v>
       </c>
       <c r="R32" t="s">
-        <v>105</v>
-      </c>
-      <c r="S32" t="b">
-        <v>0</v>
-      </c>
-      <c r="T32" t="s">
-        <v>28</v>
+        <v>101</v>
+      </c>
+      <c r="S32" t="s">
+        <v>102</v>
+      </c>
+      <c r="T32" t="b">
+        <v>0</v>
       </c>
       <c r="U32" t="s">
         <v>29</v>
       </c>
+      <c r="V32" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B33" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C33" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D33" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E33" t="b">
         <v>1</v>
       </c>
-      <c r="F33" t="s">
-        <v>137</v>
-      </c>
-      <c r="G33" t="b">
-        <v>1</v>
+      <c r="F33" t="b">
+        <v>0</v>
+      </c>
+      <c r="G33" t="s">
+        <v>138</v>
       </c>
       <c r="H33" t="b">
         <v>1</v>
       </c>
-      <c r="I33"/>
-      <c r="J33" t="b">
-        <v>0</v>
-      </c>
-      <c r="K33" t="n">
+      <c r="I33" t="b">
+        <v>1</v>
+      </c>
+      <c r="J33"/>
+      <c r="K33" t="b">
         <v>0</v>
       </c>
       <c r="L33" t="n">
@@ -3212,58 +3312,61 @@
       <c r="N33" t="n">
         <v>0</v>
       </c>
-      <c r="O33" t="s">
-        <v>29</v>
-      </c>
-      <c r="P33" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="s">
-        <v>104</v>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q33" t="b">
+        <v>0</v>
       </c>
       <c r="R33" t="s">
-        <v>105</v>
-      </c>
-      <c r="S33" t="b">
-        <v>0</v>
-      </c>
-      <c r="T33" t="s">
-        <v>28</v>
+        <v>101</v>
+      </c>
+      <c r="S33" t="s">
+        <v>102</v>
+      </c>
+      <c r="T33" t="b">
+        <v>0</v>
       </c>
       <c r="U33" t="s">
         <v>29</v>
       </c>
+      <c r="V33" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B34" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C34" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D34" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E34" t="b">
         <v>1</v>
       </c>
-      <c r="F34" t="s">
-        <v>140</v>
-      </c>
-      <c r="G34" t="b">
-        <v>1</v>
+      <c r="F34" t="b">
+        <v>0</v>
+      </c>
+      <c r="G34" t="s">
+        <v>141</v>
       </c>
       <c r="H34" t="b">
         <v>1</v>
       </c>
-      <c r="I34"/>
-      <c r="J34" t="b">
-        <v>0</v>
-      </c>
-      <c r="K34" t="n">
+      <c r="I34" t="b">
+        <v>1</v>
+      </c>
+      <c r="J34"/>
+      <c r="K34" t="b">
         <v>0</v>
       </c>
       <c r="L34" t="n">
@@ -3275,58 +3378,61 @@
       <c r="N34" t="n">
         <v>0</v>
       </c>
-      <c r="O34" t="s">
-        <v>29</v>
-      </c>
-      <c r="P34" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q34" t="s">
-        <v>104</v>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q34" t="b">
+        <v>0</v>
       </c>
       <c r="R34" t="s">
-        <v>105</v>
-      </c>
-      <c r="S34" t="b">
-        <v>0</v>
-      </c>
-      <c r="T34" t="s">
-        <v>28</v>
+        <v>101</v>
+      </c>
+      <c r="S34" t="s">
+        <v>102</v>
+      </c>
+      <c r="T34" t="b">
+        <v>0</v>
       </c>
       <c r="U34" t="s">
         <v>29</v>
       </c>
+      <c r="V34" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B35" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C35" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D35" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E35" t="b">
         <v>1</v>
       </c>
-      <c r="F35" t="s">
-        <v>143</v>
-      </c>
-      <c r="G35" t="b">
-        <v>1</v>
+      <c r="F35" t="b">
+        <v>0</v>
+      </c>
+      <c r="G35" t="s">
+        <v>144</v>
       </c>
       <c r="H35" t="b">
         <v>1</v>
       </c>
-      <c r="I35"/>
-      <c r="J35" t="b">
-        <v>0</v>
-      </c>
-      <c r="K35" t="n">
+      <c r="I35" t="b">
+        <v>1</v>
+      </c>
+      <c r="J35"/>
+      <c r="K35" t="b">
         <v>0</v>
       </c>
       <c r="L35" t="n">
@@ -3338,58 +3444,61 @@
       <c r="N35" t="n">
         <v>0</v>
       </c>
-      <c r="O35" t="s">
-        <v>29</v>
-      </c>
-      <c r="P35" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q35" t="s">
-        <v>104</v>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q35" t="b">
+        <v>0</v>
       </c>
       <c r="R35" t="s">
-        <v>105</v>
-      </c>
-      <c r="S35" t="b">
-        <v>0</v>
-      </c>
-      <c r="T35" t="s">
-        <v>28</v>
+        <v>101</v>
+      </c>
+      <c r="S35" t="s">
+        <v>102</v>
+      </c>
+      <c r="T35" t="b">
+        <v>0</v>
       </c>
       <c r="U35" t="s">
         <v>29</v>
       </c>
+      <c r="V35" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B36" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C36" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D36" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E36" t="b">
         <v>1</v>
       </c>
-      <c r="F36" t="s">
-        <v>146</v>
-      </c>
-      <c r="G36" t="b">
-        <v>1</v>
+      <c r="F36" t="b">
+        <v>0</v>
+      </c>
+      <c r="G36" t="s">
+        <v>147</v>
       </c>
       <c r="H36" t="b">
         <v>1</v>
       </c>
-      <c r="I36"/>
-      <c r="J36" t="b">
-        <v>0</v>
-      </c>
-      <c r="K36" t="n">
+      <c r="I36" t="b">
+        <v>1</v>
+      </c>
+      <c r="J36"/>
+      <c r="K36" t="b">
         <v>0</v>
       </c>
       <c r="L36" t="n">
@@ -3401,58 +3510,61 @@
       <c r="N36" t="n">
         <v>0</v>
       </c>
-      <c r="O36" t="s">
-        <v>29</v>
-      </c>
-      <c r="P36" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q36" t="s">
-        <v>104</v>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q36" t="b">
+        <v>0</v>
       </c>
       <c r="R36" t="s">
-        <v>105</v>
-      </c>
-      <c r="S36" t="b">
-        <v>0</v>
-      </c>
-      <c r="T36" t="s">
-        <v>28</v>
+        <v>101</v>
+      </c>
+      <c r="S36" t="s">
+        <v>102</v>
+      </c>
+      <c r="T36" t="b">
+        <v>0</v>
       </c>
       <c r="U36" t="s">
         <v>29</v>
       </c>
+      <c r="V36" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B37" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C37" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D37" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E37" t="b">
         <v>1</v>
       </c>
-      <c r="F37" t="s">
-        <v>149</v>
-      </c>
-      <c r="G37" t="b">
-        <v>1</v>
+      <c r="F37" t="b">
+        <v>0</v>
+      </c>
+      <c r="G37" t="s">
+        <v>150</v>
       </c>
       <c r="H37" t="b">
         <v>1</v>
       </c>
-      <c r="I37"/>
-      <c r="J37" t="b">
-        <v>0</v>
-      </c>
-      <c r="K37" t="n">
+      <c r="I37" t="b">
+        <v>1</v>
+      </c>
+      <c r="J37"/>
+      <c r="K37" t="b">
         <v>0</v>
       </c>
       <c r="L37" t="n">
@@ -3464,58 +3576,61 @@
       <c r="N37" t="n">
         <v>0</v>
       </c>
-      <c r="O37" t="s">
-        <v>29</v>
-      </c>
-      <c r="P37" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q37" t="s">
-        <v>104</v>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q37" t="b">
+        <v>0</v>
       </c>
       <c r="R37" t="s">
-        <v>105</v>
-      </c>
-      <c r="S37" t="b">
-        <v>0</v>
-      </c>
-      <c r="T37" t="s">
-        <v>28</v>
+        <v>101</v>
+      </c>
+      <c r="S37" t="s">
+        <v>102</v>
+      </c>
+      <c r="T37" t="b">
+        <v>0</v>
       </c>
       <c r="U37" t="s">
         <v>29</v>
       </c>
+      <c r="V37" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B38" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C38" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D38" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E38" t="b">
         <v>1</v>
       </c>
-      <c r="F38" t="s">
-        <v>152</v>
-      </c>
-      <c r="G38" t="b">
-        <v>1</v>
+      <c r="F38" t="b">
+        <v>0</v>
+      </c>
+      <c r="G38" t="s">
+        <v>153</v>
       </c>
       <c r="H38" t="b">
         <v>1</v>
       </c>
-      <c r="I38"/>
-      <c r="J38" t="b">
-        <v>0</v>
-      </c>
-      <c r="K38" t="n">
+      <c r="I38" t="b">
+        <v>1</v>
+      </c>
+      <c r="J38"/>
+      <c r="K38" t="b">
         <v>0</v>
       </c>
       <c r="L38" t="n">
@@ -3527,58 +3642,61 @@
       <c r="N38" t="n">
         <v>0</v>
       </c>
-      <c r="O38" t="s">
-        <v>29</v>
-      </c>
-      <c r="P38" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q38" t="s">
-        <v>104</v>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q38" t="b">
+        <v>0</v>
       </c>
       <c r="R38" t="s">
-        <v>105</v>
-      </c>
-      <c r="S38" t="b">
-        <v>0</v>
-      </c>
-      <c r="T38" t="s">
-        <v>28</v>
+        <v>101</v>
+      </c>
+      <c r="S38" t="s">
+        <v>102</v>
+      </c>
+      <c r="T38" t="b">
+        <v>0</v>
       </c>
       <c r="U38" t="s">
         <v>29</v>
       </c>
+      <c r="V38" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B39" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C39" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D39" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E39" t="b">
         <v>1</v>
       </c>
-      <c r="F39" t="s">
-        <v>155</v>
-      </c>
-      <c r="G39" t="b">
-        <v>1</v>
+      <c r="F39" t="b">
+        <v>0</v>
+      </c>
+      <c r="G39" t="s">
+        <v>156</v>
       </c>
       <c r="H39" t="b">
         <v>1</v>
       </c>
-      <c r="I39"/>
-      <c r="J39" t="b">
-        <v>0</v>
-      </c>
-      <c r="K39" t="n">
+      <c r="I39" t="b">
+        <v>1</v>
+      </c>
+      <c r="J39"/>
+      <c r="K39" t="b">
         <v>0</v>
       </c>
       <c r="L39" t="n">
@@ -3590,58 +3708,61 @@
       <c r="N39" t="n">
         <v>0</v>
       </c>
-      <c r="O39" t="s">
-        <v>29</v>
-      </c>
-      <c r="P39" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q39" t="s">
-        <v>104</v>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q39" t="b">
+        <v>0</v>
       </c>
       <c r="R39" t="s">
-        <v>105</v>
-      </c>
-      <c r="S39" t="b">
-        <v>0</v>
-      </c>
-      <c r="T39" t="s">
-        <v>28</v>
+        <v>101</v>
+      </c>
+      <c r="S39" t="s">
+        <v>102</v>
+      </c>
+      <c r="T39" t="b">
+        <v>0</v>
       </c>
       <c r="U39" t="s">
         <v>29</v>
       </c>
+      <c r="V39" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B40" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C40" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D40" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="E40" t="b">
         <v>1</v>
       </c>
-      <c r="F40" t="s">
-        <v>158</v>
-      </c>
-      <c r="G40" t="b">
-        <v>1</v>
+      <c r="F40" t="b">
+        <v>0</v>
+      </c>
+      <c r="G40" t="s">
+        <v>159</v>
       </c>
       <c r="H40" t="b">
         <v>1</v>
       </c>
-      <c r="I40"/>
-      <c r="J40" t="b">
-        <v>0</v>
-      </c>
-      <c r="K40" t="n">
+      <c r="I40" t="b">
+        <v>1</v>
+      </c>
+      <c r="J40"/>
+      <c r="K40" t="b">
         <v>0</v>
       </c>
       <c r="L40" t="n">
@@ -3653,26 +3774,29 @@
       <c r="N40" t="n">
         <v>0</v>
       </c>
-      <c r="O40" t="s">
-        <v>29</v>
-      </c>
-      <c r="P40" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q40" t="s">
-        <v>104</v>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q40" t="b">
+        <v>0</v>
       </c>
       <c r="R40" t="s">
-        <v>105</v>
-      </c>
-      <c r="S40" t="b">
-        <v>0</v>
-      </c>
-      <c r="T40" t="s">
-        <v>28</v>
+        <v>101</v>
+      </c>
+      <c r="S40" t="s">
+        <v>102</v>
+      </c>
+      <c r="T40" t="b">
+        <v>0</v>
       </c>
       <c r="U40" t="s">
         <v>29</v>
+      </c>
+      <c r="V40" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -3700,353 +3824,357 @@
         <v>0</v>
       </c>
       <c r="E1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="J1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="K1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="L1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>80</v>
       </c>
       <c r="C2" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="G2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K2" t="n">
         <v>38</v>
       </c>
       <c r="L2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" t="s">
         <v>22</v>
-      </c>
-      <c r="B3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D3" t="s">
-        <v>21</v>
       </c>
       <c r="E3"/>
       <c r="F3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="G3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K3" t="n">
         <v>38</v>
       </c>
       <c r="L3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>30</v>
+        <v>121</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>80</v>
       </c>
       <c r="C4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E4"/>
       <c r="F4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="G4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K4" t="n">
         <v>38</v>
       </c>
       <c r="L4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>83</v>
+        <v>48</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="C5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D5" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E5" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F5" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G5" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J5" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K5" t="n">
         <v>61</v>
       </c>
       <c r="L5" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B6" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E6"/>
       <c r="F6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K6" t="n">
         <v>59</v>
       </c>
       <c r="L6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" t="s">
         <v>22</v>
-      </c>
-      <c r="B7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" t="s">
-        <v>21</v>
       </c>
       <c r="E7"/>
       <c r="F7" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G7" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I7" t="s">
+        <v>178</v>
+      </c>
+      <c r="J7" t="s">
+        <v>172</v>
+      </c>
+      <c r="K7" t="n">
+        <v>59</v>
+      </c>
+      <c r="L7" t="s">
         <v>177</v>
-      </c>
-      <c r="J7" t="s">
-        <v>171</v>
-      </c>
-      <c r="K7" t="n">
-        <v>61</v>
-      </c>
-      <c r="L7" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B8" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="C8" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="D8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E8"/>
       <c r="F8" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G8" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I8" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="J8" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K8" t="n">
         <v>59</v>
       </c>
       <c r="L8" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="B9" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="C9" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="D9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E9"/>
+        <v>37</v>
+      </c>
+      <c r="E9" t="s">
+        <v>49</v>
+      </c>
       <c r="F9" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="G9" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="H9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I9" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="J9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K9" t="n">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="L9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="B10" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="C10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D10" t="s">
-        <v>21</v>
-      </c>
-      <c r="E10"/>
+        <v>37</v>
+      </c>
+      <c r="E10" t="s">
+        <v>49</v>
+      </c>
       <c r="F10" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="G10" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="H10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K10" t="n">
-        <v>59</v>
+        <v>261</v>
       </c>
       <c r="L10" t="s">
         <v>176</v>
@@ -4054,3344 +4182,3052 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>83</v>
+        <v>48</v>
       </c>
       <c r="B11" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="C11" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D11" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E11" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F11" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="G11" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H11" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I11" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J11" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K11" t="n">
-        <v>50</v>
+        <v>418</v>
       </c>
       <c r="L11" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>83</v>
+        <v>103</v>
       </c>
       <c r="B12" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C12" t="s">
-        <v>39</v>
+        <v>85</v>
       </c>
       <c r="D12" t="s">
-        <v>41</v>
-      </c>
-      <c r="E12" t="s">
-        <v>53</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="E12"/>
       <c r="F12" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="G12" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H12" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I12" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J12" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K12" t="n">
-        <v>260</v>
+        <v>48</v>
       </c>
       <c r="L12" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>83</v>
+        <v>103</v>
       </c>
       <c r="B13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C13" t="s">
-        <v>39</v>
+        <v>85</v>
       </c>
       <c r="D13" t="s">
-        <v>41</v>
-      </c>
-      <c r="E13" t="s">
-        <v>53</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="E13"/>
       <c r="F13" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="G13" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I13" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J13" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K13" t="n">
-        <v>416</v>
+        <v>75</v>
       </c>
       <c r="L13" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B14" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="C14" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D14" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E14"/>
       <c r="F14" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="G14" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H14" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I14" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J14" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K14" t="n">
-        <v>48</v>
+        <v>108</v>
       </c>
       <c r="L14" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>106</v>
+        <v>23</v>
       </c>
       <c r="B15" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="C15" t="s">
-        <v>88</v>
+        <v>25</v>
       </c>
       <c r="D15" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E15"/>
       <c r="F15" t="s">
+        <v>179</v>
+      </c>
+      <c r="G15" t="s">
+        <v>180</v>
+      </c>
+      <c r="H15" t="s">
+        <v>25</v>
+      </c>
+      <c r="I15" t="s">
         <v>178</v>
       </c>
-      <c r="G15" t="s">
-        <v>179</v>
-      </c>
-      <c r="H15" t="s">
-        <v>24</v>
-      </c>
-      <c r="I15" t="s">
-        <v>170</v>
-      </c>
       <c r="J15" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K15" t="n">
-        <v>74</v>
+        <v>48</v>
       </c>
       <c r="L15" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>106</v>
+        <v>23</v>
       </c>
       <c r="B16" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="C16" t="s">
-        <v>88</v>
+        <v>25</v>
       </c>
       <c r="D16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E16"/>
       <c r="F16" t="s">
+        <v>179</v>
+      </c>
+      <c r="G16" t="s">
+        <v>180</v>
+      </c>
+      <c r="H16" t="s">
+        <v>25</v>
+      </c>
+      <c r="I16" t="s">
         <v>178</v>
       </c>
-      <c r="G16" t="s">
-        <v>179</v>
-      </c>
-      <c r="H16" t="s">
-        <v>24</v>
-      </c>
-      <c r="I16" t="s">
-        <v>170</v>
-      </c>
       <c r="J16" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K16" t="n">
-        <v>107</v>
+        <v>75</v>
       </c>
       <c r="L16" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C17" t="s">
+        <v>25</v>
+      </c>
+      <c r="D17" t="s">
         <v>22</v>
-      </c>
-      <c r="B17" t="s">
-        <v>23</v>
-      </c>
-      <c r="C17" t="s">
-        <v>24</v>
-      </c>
-      <c r="D17" t="s">
-        <v>21</v>
       </c>
       <c r="E17"/>
       <c r="F17" t="s">
+        <v>179</v>
+      </c>
+      <c r="G17" t="s">
+        <v>180</v>
+      </c>
+      <c r="H17" t="s">
+        <v>25</v>
+      </c>
+      <c r="I17" t="s">
         <v>178</v>
       </c>
-      <c r="G17" t="s">
-        <v>179</v>
-      </c>
-      <c r="H17" t="s">
-        <v>24</v>
-      </c>
-      <c r="I17" t="s">
+      <c r="J17" t="s">
+        <v>172</v>
+      </c>
+      <c r="K17" t="n">
+        <v>108</v>
+      </c>
+      <c r="L17" t="s">
         <v>177</v>
-      </c>
-      <c r="J17" t="s">
-        <v>171</v>
-      </c>
-      <c r="K17" t="n">
-        <v>50</v>
-      </c>
-      <c r="L17" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C18" t="s">
+        <v>35</v>
+      </c>
+      <c r="D18" t="s">
         <v>22</v>
-      </c>
-      <c r="B18" t="s">
-        <v>23</v>
-      </c>
-      <c r="C18" t="s">
-        <v>24</v>
-      </c>
-      <c r="D18" t="s">
-        <v>21</v>
       </c>
       <c r="E18"/>
       <c r="F18" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="G18" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H18" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I18" t="s">
+        <v>171</v>
+      </c>
+      <c r="J18" t="s">
+        <v>172</v>
+      </c>
+      <c r="K18" t="n">
+        <v>48</v>
+      </c>
+      <c r="L18" t="s">
         <v>177</v>
-      </c>
-      <c r="J18" t="s">
-        <v>171</v>
-      </c>
-      <c r="K18" t="n">
-        <v>260</v>
-      </c>
-      <c r="L18" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
+        <v>34</v>
+      </c>
+      <c r="B19" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19" t="s">
+        <v>35</v>
+      </c>
+      <c r="D19" t="s">
         <v>22</v>
-      </c>
-      <c r="B19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C19" t="s">
-        <v>24</v>
-      </c>
-      <c r="D19" t="s">
-        <v>21</v>
       </c>
       <c r="E19"/>
       <c r="F19" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="G19" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H19" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I19" t="s">
+        <v>171</v>
+      </c>
+      <c r="J19" t="s">
+        <v>172</v>
+      </c>
+      <c r="K19" t="n">
+        <v>75</v>
+      </c>
+      <c r="L19" t="s">
         <v>177</v>
-      </c>
-      <c r="J19" t="s">
-        <v>171</v>
-      </c>
-      <c r="K19" t="n">
-        <v>416</v>
-      </c>
-      <c r="L19" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B20" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="C20" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="D20" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E20"/>
       <c r="F20" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="G20" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H20" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I20" t="s">
+        <v>171</v>
+      </c>
+      <c r="J20" t="s">
+        <v>172</v>
+      </c>
+      <c r="K20" t="n">
+        <v>108</v>
+      </c>
+      <c r="L20" t="s">
         <v>177</v>
-      </c>
-      <c r="J20" t="s">
-        <v>171</v>
-      </c>
-      <c r="K20" t="n">
-        <v>48</v>
-      </c>
-      <c r="L20" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
+        <v>31</v>
+      </c>
+      <c r="B21" t="s">
         <v>32</v>
       </c>
-      <c r="B21" t="s">
-        <v>33</v>
-      </c>
       <c r="C21" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D21" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E21"/>
       <c r="F21" t="s">
+        <v>181</v>
+      </c>
+      <c r="G21" t="s">
+        <v>182</v>
+      </c>
+      <c r="H21" t="s">
+        <v>25</v>
+      </c>
+      <c r="I21" t="s">
         <v>178</v>
       </c>
-      <c r="G21" t="s">
-        <v>179</v>
-      </c>
-      <c r="H21" t="s">
-        <v>24</v>
-      </c>
-      <c r="I21" t="s">
-        <v>177</v>
-      </c>
       <c r="J21" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K21" t="n">
-        <v>74</v>
+        <v>39</v>
       </c>
       <c r="L21" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
+        <v>31</v>
+      </c>
+      <c r="B22" t="s">
         <v>32</v>
       </c>
-      <c r="B22" t="s">
-        <v>33</v>
-      </c>
       <c r="C22" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D22" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E22"/>
       <c r="F22" t="s">
+        <v>181</v>
+      </c>
+      <c r="G22" t="s">
+        <v>182</v>
+      </c>
+      <c r="H22" t="s">
+        <v>25</v>
+      </c>
+      <c r="I22" t="s">
         <v>178</v>
       </c>
-      <c r="G22" t="s">
-        <v>179</v>
-      </c>
-      <c r="H22" t="s">
-        <v>24</v>
-      </c>
-      <c r="I22" t="s">
-        <v>177</v>
-      </c>
       <c r="J22" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K22" t="n">
-        <v>107</v>
+        <v>176</v>
       </c>
       <c r="L22" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="B23" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="C23" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="D23" t="s">
-        <v>21</v>
-      </c>
-      <c r="E23"/>
+        <v>37</v>
+      </c>
+      <c r="E23" t="s">
+        <v>49</v>
+      </c>
       <c r="F23" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="G23" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="H23" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="I23" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="J23" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K23" t="n">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="L23" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="B24" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="C24" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="D24" t="s">
-        <v>21</v>
-      </c>
-      <c r="E24"/>
+        <v>37</v>
+      </c>
+      <c r="E24" t="s">
+        <v>49</v>
+      </c>
       <c r="F24" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="G24" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="H24" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="I24" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="J24" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K24" t="n">
-        <v>260</v>
+        <v>374</v>
       </c>
       <c r="L24" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="B25" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="C25" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="D25" t="s">
-        <v>21</v>
-      </c>
-      <c r="E25"/>
+        <v>37</v>
+      </c>
+      <c r="E25" t="s">
+        <v>49</v>
+      </c>
       <c r="F25" t="s">
-        <v>178</v>
+        <v>189</v>
       </c>
       <c r="G25" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="H25" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="I25" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="J25" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K25" t="n">
-        <v>416</v>
+        <v>85</v>
       </c>
       <c r="L25" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="B26" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="C26" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D26" t="s">
-        <v>21</v>
-      </c>
-      <c r="E26"/>
+        <v>37</v>
+      </c>
+      <c r="E26" t="s">
+        <v>49</v>
+      </c>
       <c r="F26" t="s">
-        <v>178</v>
+        <v>189</v>
       </c>
       <c r="G26" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="H26" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="I26" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J26" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K26" t="n">
-        <v>48</v>
+        <v>370</v>
       </c>
       <c r="L26" t="s">
-        <v>176</v>
+        <v>188</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="B27" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="C27" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D27" t="s">
-        <v>21</v>
-      </c>
-      <c r="E27"/>
+        <v>37</v>
+      </c>
+      <c r="E27" t="s">
+        <v>49</v>
+      </c>
       <c r="F27" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="G27" t="s">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="H27" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="I27" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J27" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K27" t="n">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="L27" t="s">
-        <v>176</v>
+        <v>193</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="B28" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="C28" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D28" t="s">
-        <v>21</v>
-      </c>
-      <c r="E28"/>
+        <v>37</v>
+      </c>
+      <c r="E28" t="s">
+        <v>49</v>
+      </c>
       <c r="F28" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="G28" t="s">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="H28" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="I28" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J28" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K28" t="n">
-        <v>107</v>
+        <v>381</v>
       </c>
       <c r="L28" t="s">
-        <v>176</v>
+        <v>188</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="B29" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="C29" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="D29" t="s">
-        <v>21</v>
-      </c>
-      <c r="E29"/>
+        <v>37</v>
+      </c>
+      <c r="E29" t="s">
+        <v>49</v>
+      </c>
       <c r="F29" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G29" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
       <c r="H29" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="I29" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="J29" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K29" t="n">
-        <v>39</v>
+        <v>90</v>
       </c>
       <c r="L29" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="B30" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="C30" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="D30" t="s">
-        <v>21</v>
-      </c>
-      <c r="E30"/>
+        <v>37</v>
+      </c>
+      <c r="E30" t="s">
+        <v>49</v>
+      </c>
       <c r="F30" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G30" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
       <c r="H30" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="I30" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="J30" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K30" t="n">
-        <v>176</v>
+        <v>374</v>
       </c>
       <c r="L30" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B31" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C31" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D31" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E31" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F31" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="G31" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="H31" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="I31" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J31" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K31" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="L31" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B32" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C32" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D32" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E32" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F32" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="G32" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="H32" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="I32" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J32" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K32" t="n">
-        <v>374</v>
+        <v>387</v>
       </c>
       <c r="L32" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B33" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C33" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D33" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E33" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F33" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="G33" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="H33" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="I33" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J33" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K33" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="L33" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B34" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C34" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D34" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E34" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F34" t="s">
+        <v>198</v>
+      </c>
+      <c r="G34" t="s">
+        <v>199</v>
+      </c>
+      <c r="H34" t="s">
+        <v>35</v>
+      </c>
+      <c r="I34" t="s">
+        <v>171</v>
+      </c>
+      <c r="J34" t="s">
+        <v>172</v>
+      </c>
+      <c r="K34" t="n">
+        <v>375</v>
+      </c>
+      <c r="L34" t="s">
         <v>188</v>
-      </c>
-      <c r="G34" t="s">
-        <v>189</v>
-      </c>
-      <c r="H34" t="s">
-        <v>39</v>
-      </c>
-      <c r="I34" t="s">
-        <v>170</v>
-      </c>
-      <c r="J34" t="s">
-        <v>171</v>
-      </c>
-      <c r="K34" t="n">
-        <v>370</v>
-      </c>
-      <c r="L34" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B35" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C35" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D35" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E35" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F35" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="G35" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="H35" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="I35" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J35" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K35" t="n">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="L35" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B36" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C36" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D36" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E36" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F36" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="G36" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="H36" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="I36" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J36" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K36" t="n">
-        <v>381</v>
+        <v>370</v>
       </c>
       <c r="L36" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B37" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C37" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D37" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E37" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F37" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="G37" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="H37" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="I37" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J37" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K37" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="L37" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B38" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C38" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D38" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E38" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F38" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="G38" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="H38" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="I38" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J38" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K38" t="n">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="L38" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B39" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C39" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D39" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E39" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F39" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="G39" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="H39" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="I39" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J39" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K39" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="L39" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B40" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C40" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D40" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E40" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F40" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="G40" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="H40" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="I40" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J40" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K40" t="n">
-        <v>387</v>
+        <v>369</v>
       </c>
       <c r="L40" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B41" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C41" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D41" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E41" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F41" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="G41" t="s">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="H41" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="I41" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J41" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K41" t="n">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="L41" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B42" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C42" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D42" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E42" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F42" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="G42" t="s">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="H42" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="I42" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J42" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K42" t="n">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="L42" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B43" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C43" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D43" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E43" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F43" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="G43" t="s">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="H43" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="I43" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J43" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K43" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="L43" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B44" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C44" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D44" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E44" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F44" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="G44" t="s">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="H44" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="I44" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J44" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K44" t="n">
         <v>370</v>
       </c>
       <c r="L44" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B45" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C45" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D45" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E45" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F45" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="G45" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="H45" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="I45" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J45" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K45" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="L45" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B46" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C46" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D46" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E46" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F46" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="G46" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="H46" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="I46" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J46" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K46" t="n">
         <v>370</v>
       </c>
       <c r="L46" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B47" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C47" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D47" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E47" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F47" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="G47" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="H47" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="I47" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J47" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K47" t="n">
-        <v>84</v>
+        <v>55</v>
       </c>
       <c r="L47" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B48" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C48" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D48" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E48" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F48" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="G48" t="s">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="H48" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="I48" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J48" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K48" t="n">
-        <v>369</v>
+        <v>73</v>
       </c>
       <c r="L48" t="s">
-        <v>187</v>
+        <v>216</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C49" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D49" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E49" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F49" t="s">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="G49" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="H49" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="I49" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J49" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K49" t="n">
-        <v>84</v>
+        <v>322</v>
       </c>
       <c r="L49" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C50" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D50" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E50" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F50" t="s">
-        <v>205</v>
+        <v>217</v>
       </c>
       <c r="G50" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="H50" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="I50" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J50" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K50" t="n">
-        <v>370</v>
+        <v>38</v>
       </c>
       <c r="L50" t="s">
-        <v>187</v>
+        <v>219</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B51" t="s">
+        <v>49</v>
+      </c>
+      <c r="C51" t="s">
+        <v>40</v>
+      </c>
+      <c r="D51" t="s">
+        <v>37</v>
+      </c>
+      <c r="E51" t="s">
+        <v>49</v>
+      </c>
+      <c r="F51" t="s">
+        <v>220</v>
+      </c>
+      <c r="G51" t="s">
+        <v>221</v>
+      </c>
+      <c r="H51" t="s">
+        <v>35</v>
+      </c>
+      <c r="I51" t="s">
+        <v>171</v>
+      </c>
+      <c r="J51" t="s">
+        <v>172</v>
+      </c>
+      <c r="K51" t="n">
         <v>53</v>
       </c>
-      <c r="C51" t="s">
-        <v>44</v>
-      </c>
-      <c r="D51" t="s">
-        <v>41</v>
-      </c>
-      <c r="E51" t="s">
-        <v>53</v>
-      </c>
-      <c r="F51" t="s">
-        <v>207</v>
-      </c>
-      <c r="G51" t="s">
-        <v>208</v>
-      </c>
-      <c r="H51" t="s">
-        <v>39</v>
-      </c>
-      <c r="I51" t="s">
-        <v>170</v>
-      </c>
-      <c r="J51" t="s">
-        <v>171</v>
-      </c>
-      <c r="K51" t="n">
-        <v>84</v>
-      </c>
       <c r="L51" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B52" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C52" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D52" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E52" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F52" t="s">
-        <v>207</v>
+        <v>220</v>
       </c>
       <c r="G52" t="s">
-        <v>208</v>
+        <v>221</v>
       </c>
       <c r="H52" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="I52" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J52" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K52" t="n">
-        <v>370</v>
+        <v>247</v>
       </c>
       <c r="L52" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B53" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C53" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D53" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E53" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F53" t="s">
-        <v>209</v>
+        <v>220</v>
       </c>
       <c r="G53" t="s">
-        <v>210</v>
+        <v>221</v>
       </c>
       <c r="H53" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="I53" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J53" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K53" t="n">
-        <v>84</v>
+        <v>427</v>
       </c>
       <c r="L53" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B54" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C54" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D54" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E54" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F54" t="s">
-        <v>209</v>
+        <v>220</v>
       </c>
       <c r="G54" t="s">
-        <v>210</v>
+        <v>221</v>
       </c>
       <c r="H54" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="I54" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J54" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K54" t="n">
-        <v>370</v>
+        <v>603</v>
       </c>
       <c r="L54" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B55" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C55" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D55" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E55" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F55" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="G55" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="H55" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="I55" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J55" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K55" t="n">
-        <v>55</v>
+        <v>787</v>
       </c>
       <c r="L55" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B56" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C56" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D56" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E56" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F56" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="G56" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="H56" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="I56" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J56" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K56" t="n">
-        <v>73</v>
+        <v>969</v>
       </c>
       <c r="L56" t="s">
-        <v>215</v>
+        <v>193</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B57" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C57" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D57" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E57" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F57" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="G57" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="H57" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="I57" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J57" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K57" t="n">
-        <v>322</v>
+        <v>1157</v>
       </c>
       <c r="L57" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B58" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C58" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D58" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E58" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F58" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="G58" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="H58" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="I58" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J58" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K58" t="n">
-        <v>38</v>
+        <v>1302</v>
       </c>
       <c r="L58" t="s">
-        <v>218</v>
+        <v>193</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B59" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C59" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D59" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E59" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F59" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G59" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H59" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="I59" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J59" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K59" t="n">
-        <v>53</v>
+        <v>1447</v>
       </c>
       <c r="L59" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B60" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C60" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D60" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E60" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F60" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G60" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H60" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="I60" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J60" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K60" t="n">
-        <v>247</v>
+        <v>1594</v>
       </c>
       <c r="L60" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B61" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C61" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D61" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E61" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F61" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G61" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H61" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="I61" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J61" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K61" t="n">
-        <v>427</v>
+        <v>1739</v>
       </c>
       <c r="L61" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B62" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C62" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D62" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E62" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F62" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G62" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H62" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="I62" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J62" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K62" t="n">
-        <v>603</v>
+        <v>1888</v>
       </c>
       <c r="L62" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B63" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C63" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D63" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E63" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F63" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G63" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H63" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="I63" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J63" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K63" t="n">
-        <v>787</v>
+        <v>2029</v>
       </c>
       <c r="L63" t="s">
-        <v>192</v>
+        <v>222</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B64" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C64" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D64" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E64" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F64" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="G64" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="H64" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="I64" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J64" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K64" t="n">
-        <v>969</v>
+        <v>47</v>
       </c>
       <c r="L64" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>52</v>
+        <v>103</v>
       </c>
       <c r="B65" t="s">
-        <v>53</v>
+        <v>24</v>
       </c>
       <c r="C65" t="s">
-        <v>44</v>
+        <v>85</v>
       </c>
       <c r="D65" t="s">
-        <v>41</v>
-      </c>
-      <c r="E65" t="s">
-        <v>53</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="E65"/>
       <c r="F65" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="G65" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="H65" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="I65" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J65" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K65" t="n">
-        <v>1157</v>
+        <v>186</v>
       </c>
       <c r="L65" t="s">
-        <v>192</v>
+        <v>225</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>52</v>
+        <v>23</v>
       </c>
       <c r="B66" t="s">
-        <v>53</v>
+        <v>24</v>
       </c>
       <c r="C66" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="D66" t="s">
-        <v>41</v>
-      </c>
-      <c r="E66" t="s">
-        <v>53</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="E66"/>
       <c r="F66" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="G66" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="H66" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="I66" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J66" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K66" t="n">
-        <v>1302</v>
+        <v>186</v>
       </c>
       <c r="L66" t="s">
-        <v>192</v>
+        <v>225</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="B67" t="s">
-        <v>53</v>
+        <v>24</v>
       </c>
       <c r="C67" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="D67" t="s">
-        <v>41</v>
-      </c>
-      <c r="E67" t="s">
-        <v>53</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="E67"/>
       <c r="F67" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="G67" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="H67" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="I67" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="J67" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K67" t="n">
-        <v>1447</v>
+        <v>186</v>
       </c>
       <c r="L67" t="s">
-        <v>192</v>
+        <v>225</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B68" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C68" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D68" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E68" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F68" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="G68" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="H68" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="I68" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J68" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K68" t="n">
-        <v>1594</v>
+        <v>180</v>
       </c>
       <c r="L68" t="s">
-        <v>192</v>
+        <v>228</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B69" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C69" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D69" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E69" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F69" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="G69" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="H69" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="I69" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J69" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K69" t="n">
-        <v>1739</v>
+        <v>331</v>
       </c>
       <c r="L69" t="s">
-        <v>192</v>
+        <v>229</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B70" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C70" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D70" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E70" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F70" t="s">
-        <v>219</v>
+        <v>230</v>
       </c>
       <c r="G70" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="H70" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="I70" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J70" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K70" t="n">
-        <v>1888</v>
+        <v>68</v>
       </c>
       <c r="L70" t="s">
-        <v>192</v>
+        <v>232</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B71" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C71" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D71" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E71" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F71" t="s">
-        <v>219</v>
+        <v>230</v>
       </c>
       <c r="G71" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="H71" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="I71" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J71" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K71" t="n">
-        <v>2029</v>
+        <v>241</v>
       </c>
       <c r="L71" t="s">
-        <v>221</v>
+        <v>188</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B72" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C72" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D72" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E72" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F72" t="s">
-        <v>222</v>
+        <v>233</v>
       </c>
       <c r="G72" t="s">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="H72" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="I72" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J72" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K72" t="n">
-        <v>47</v>
+        <v>84</v>
       </c>
       <c r="L72" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>106</v>
+        <v>48</v>
       </c>
       <c r="B73" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="C73" t="s">
-        <v>88</v>
+        <v>40</v>
       </c>
       <c r="D73" t="s">
-        <v>21</v>
-      </c>
-      <c r="E73"/>
+        <v>37</v>
+      </c>
+      <c r="E73" t="s">
+        <v>49</v>
+      </c>
       <c r="F73" t="s">
-        <v>222</v>
+        <v>233</v>
       </c>
       <c r="G73" t="s">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="H73" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="I73" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J73" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K73" t="n">
-        <v>186</v>
+        <v>100</v>
       </c>
       <c r="L73" t="s">
-        <v>224</v>
+        <v>235</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="B74" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="C74" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="D74" t="s">
-        <v>21</v>
-      </c>
-      <c r="E74"/>
+        <v>37</v>
+      </c>
+      <c r="E74" t="s">
+        <v>49</v>
+      </c>
       <c r="F74" t="s">
-        <v>222</v>
+        <v>233</v>
       </c>
       <c r="G74" t="s">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="H74" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="I74" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J74" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K74" t="n">
-        <v>186</v>
+        <v>393</v>
       </c>
       <c r="L74" t="s">
-        <v>224</v>
+        <v>193</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="B75" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="C75" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D75" t="s">
-        <v>21</v>
-      </c>
-      <c r="E75"/>
+        <v>37</v>
+      </c>
+      <c r="E75" t="s">
+        <v>49</v>
+      </c>
       <c r="F75" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="G75" t="s">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="H75" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="I75" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="J75" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K75" t="n">
-        <v>186</v>
+        <v>76</v>
       </c>
       <c r="L75" t="s">
-        <v>224</v>
+        <v>193</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B76" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C76" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D76" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E76" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F76" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="G76" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="H76" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="I76" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J76" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K76" t="n">
-        <v>180</v>
+        <v>370</v>
       </c>
       <c r="L76" t="s">
-        <v>227</v>
+        <v>193</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B77" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C77" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D77" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E77" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F77" t="s">
-        <v>225</v>
+        <v>238</v>
       </c>
       <c r="G77" t="s">
-        <v>226</v>
+        <v>239</v>
       </c>
       <c r="H77" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="I77" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J77" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K77" t="n">
-        <v>331</v>
+        <v>69</v>
       </c>
       <c r="L77" t="s">
-        <v>228</v>
+        <v>193</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B78" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C78" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D78" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E78" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F78" t="s">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="G78" t="s">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="H78" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="I78" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J78" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K78" t="n">
-        <v>68</v>
+        <v>363</v>
       </c>
       <c r="L78" t="s">
-        <v>231</v>
+        <v>193</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B79" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C79" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D79" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E79" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F79" t="s">
-        <v>229</v>
+        <v>240</v>
       </c>
       <c r="G79" t="s">
-        <v>230</v>
+        <v>241</v>
       </c>
       <c r="H79" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="I79" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J79" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K79" t="n">
-        <v>241</v>
+        <v>77</v>
       </c>
       <c r="L79" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B80" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C80" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D80" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E80" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F80" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="G80" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="H80" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="I80" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J80" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K80" t="n">
-        <v>84</v>
+        <v>376</v>
       </c>
       <c r="L80" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B81" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C81" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D81" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E81" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F81" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="G81" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="H81" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="I81" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J81" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K81" t="n">
-        <v>100</v>
+        <v>49</v>
       </c>
       <c r="L81" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B82" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C82" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D82" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E82" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F82" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="G82" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="H82" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="I82" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J82" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K82" t="n">
-        <v>393</v>
+        <v>357</v>
       </c>
       <c r="L82" t="s">
-        <v>192</v>
+        <v>245</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B83" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C83" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D83" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E83" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F83" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="G83" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="H83" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="I83" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J83" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K83" t="n">
-        <v>76</v>
+        <v>522</v>
       </c>
       <c r="L83" t="s">
-        <v>192</v>
+        <v>245</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B84" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C84" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D84" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E84" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F84" t="s">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="G84" t="s">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="H84" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="I84" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J84" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K84" t="n">
-        <v>370</v>
+        <v>37</v>
       </c>
       <c r="L84" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B85" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C85" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D85" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E85" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F85" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="G85" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="H85" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="I85" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J85" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K85" t="n">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="L85" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B86" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C86" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D86" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E86" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F86" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="G86" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="H86" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="I86" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J86" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K86" t="n">
-        <v>363</v>
+        <v>77</v>
       </c>
       <c r="L86" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B87" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C87" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D87" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E87" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F87" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="G87" t="s">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="H87" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="I87" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J87" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K87" t="n">
-        <v>77</v>
+        <v>371</v>
       </c>
       <c r="L87" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B88" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C88" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D88" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E88" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F88" t="s">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="G88" t="s">
-        <v>240</v>
+        <v>251</v>
       </c>
       <c r="H88" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="I88" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J88" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K88" t="n">
-        <v>376</v>
+        <v>77</v>
       </c>
       <c r="L88" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B89" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C89" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D89" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E89" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F89" t="s">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="G89" t="s">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="H89" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="I89" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J89" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K89" t="n">
-        <v>49</v>
+        <v>371</v>
       </c>
       <c r="L89" t="s">
-        <v>243</v>
+        <v>193</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B90" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C90" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D90" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E90" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F90" t="s">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="G90" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="H90" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="I90" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J90" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K90" t="n">
-        <v>357</v>
+        <v>85</v>
       </c>
       <c r="L90" t="s">
-        <v>244</v>
+        <v>216</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B91" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C91" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D91" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E91" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F91" t="s">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="G91" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="H91" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="I91" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J91" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K91" t="n">
-        <v>522</v>
+        <v>360</v>
       </c>
       <c r="L91" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="s">
-        <v>52</v>
-      </c>
-      <c r="B92" t="s">
-        <v>53</v>
-      </c>
-      <c r="C92" t="s">
-        <v>44</v>
-      </c>
-      <c r="D92" t="s">
-        <v>41</v>
-      </c>
-      <c r="E92" t="s">
-        <v>53</v>
-      </c>
-      <c r="F92" t="s">
-        <v>245</v>
-      </c>
-      <c r="G92" t="s">
-        <v>246</v>
-      </c>
-      <c r="H92" t="s">
-        <v>39</v>
-      </c>
-      <c r="I92" t="s">
-        <v>170</v>
-      </c>
-      <c r="J92" t="s">
-        <v>171</v>
-      </c>
-      <c r="K92" t="n">
-        <v>37</v>
-      </c>
-      <c r="L92" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="s">
-        <v>52</v>
-      </c>
-      <c r="B93" t="s">
-        <v>53</v>
-      </c>
-      <c r="C93" t="s">
-        <v>44</v>
-      </c>
-      <c r="D93" t="s">
-        <v>41</v>
-      </c>
-      <c r="E93" t="s">
-        <v>53</v>
-      </c>
-      <c r="F93" t="s">
-        <v>245</v>
-      </c>
-      <c r="G93" t="s">
-        <v>246</v>
-      </c>
-      <c r="H93" t="s">
-        <v>39</v>
-      </c>
-      <c r="I93" t="s">
-        <v>170</v>
-      </c>
-      <c r="J93" t="s">
-        <v>171</v>
-      </c>
-      <c r="K93" t="n">
-        <v>87</v>
-      </c>
-      <c r="L93" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="s">
-        <v>52</v>
-      </c>
-      <c r="B94" t="s">
-        <v>53</v>
-      </c>
-      <c r="C94" t="s">
-        <v>44</v>
-      </c>
-      <c r="D94" t="s">
-        <v>41</v>
-      </c>
-      <c r="E94" t="s">
-        <v>53</v>
-      </c>
-      <c r="F94" t="s">
-        <v>247</v>
-      </c>
-      <c r="G94" t="s">
-        <v>248</v>
-      </c>
-      <c r="H94" t="s">
-        <v>39</v>
-      </c>
-      <c r="I94" t="s">
-        <v>170</v>
-      </c>
-      <c r="J94" t="s">
-        <v>171</v>
-      </c>
-      <c r="K94" t="n">
-        <v>77</v>
-      </c>
-      <c r="L94" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="s">
-        <v>52</v>
-      </c>
-      <c r="B95" t="s">
-        <v>53</v>
-      </c>
-      <c r="C95" t="s">
-        <v>44</v>
-      </c>
-      <c r="D95" t="s">
-        <v>41</v>
-      </c>
-      <c r="E95" t="s">
-        <v>53</v>
-      </c>
-      <c r="F95" t="s">
-        <v>247</v>
-      </c>
-      <c r="G95" t="s">
-        <v>248</v>
-      </c>
-      <c r="H95" t="s">
-        <v>39</v>
-      </c>
-      <c r="I95" t="s">
-        <v>170</v>
-      </c>
-      <c r="J95" t="s">
-        <v>171</v>
-      </c>
-      <c r="K95" t="n">
-        <v>371</v>
-      </c>
-      <c r="L95" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="s">
-        <v>52</v>
-      </c>
-      <c r="B96" t="s">
-        <v>53</v>
-      </c>
-      <c r="C96" t="s">
-        <v>44</v>
-      </c>
-      <c r="D96" t="s">
-        <v>41</v>
-      </c>
-      <c r="E96" t="s">
-        <v>53</v>
-      </c>
-      <c r="F96" t="s">
-        <v>249</v>
-      </c>
-      <c r="G96" t="s">
-        <v>250</v>
-      </c>
-      <c r="H96" t="s">
-        <v>39</v>
-      </c>
-      <c r="I96" t="s">
-        <v>170</v>
-      </c>
-      <c r="J96" t="s">
-        <v>171</v>
-      </c>
-      <c r="K96" t="n">
-        <v>77</v>
-      </c>
-      <c r="L96" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="s">
-        <v>52</v>
-      </c>
-      <c r="B97" t="s">
-        <v>53</v>
-      </c>
-      <c r="C97" t="s">
-        <v>44</v>
-      </c>
-      <c r="D97" t="s">
-        <v>41</v>
-      </c>
-      <c r="E97" t="s">
-        <v>53</v>
-      </c>
-      <c r="F97" t="s">
-        <v>249</v>
-      </c>
-      <c r="G97" t="s">
-        <v>250</v>
-      </c>
-      <c r="H97" t="s">
-        <v>39</v>
-      </c>
-      <c r="I97" t="s">
-        <v>170</v>
-      </c>
-      <c r="J97" t="s">
-        <v>171</v>
-      </c>
-      <c r="K97" t="n">
-        <v>371</v>
-      </c>
-      <c r="L97" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="s">
-        <v>52</v>
-      </c>
-      <c r="B98" t="s">
-        <v>53</v>
-      </c>
-      <c r="C98" t="s">
-        <v>44</v>
-      </c>
-      <c r="D98" t="s">
-        <v>41</v>
-      </c>
-      <c r="E98" t="s">
-        <v>53</v>
-      </c>
-      <c r="F98" t="s">
-        <v>251</v>
-      </c>
-      <c r="G98" t="s">
-        <v>252</v>
-      </c>
-      <c r="H98" t="s">
-        <v>39</v>
-      </c>
-      <c r="I98" t="s">
-        <v>170</v>
-      </c>
-      <c r="J98" t="s">
-        <v>171</v>
-      </c>
-      <c r="K98" t="n">
-        <v>85</v>
-      </c>
-      <c r="L98" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="s">
-        <v>52</v>
-      </c>
-      <c r="B99" t="s">
-        <v>53</v>
-      </c>
-      <c r="C99" t="s">
-        <v>44</v>
-      </c>
-      <c r="D99" t="s">
-        <v>41</v>
-      </c>
-      <c r="E99" t="s">
-        <v>53</v>
-      </c>
-      <c r="F99" t="s">
-        <v>251</v>
-      </c>
-      <c r="G99" t="s">
-        <v>252</v>
-      </c>
-      <c r="H99" t="s">
-        <v>39</v>
-      </c>
-      <c r="I99" t="s">
-        <v>170</v>
-      </c>
-      <c r="J99" t="s">
-        <v>171</v>
-      </c>
-      <c r="K99" t="n">
-        <v>360</v>
-      </c>
-      <c r="L99" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
   </sheetData>

--- a/05 dependency and cleanup reports/scuc_dependency_scan_and_cleanup_plan.xlsx
+++ b/05 dependency and cleanup reports/scuc_dependency_scan_and_cleanup_plan.xlsx
@@ -1407,7 +1407,7 @@
         <v>40</v>
       </c>
       <c r="E5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" t="b">
         <v>0</v>
@@ -1475,7 +1475,7 @@
         <v>40</v>
       </c>
       <c r="E6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" t="b">
         <v>0</v>
@@ -1543,7 +1543,7 @@
         <v>40</v>
       </c>
       <c r="E7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" t="b">
         <v>0</v>
@@ -1611,7 +1611,7 @@
         <v>40</v>
       </c>
       <c r="E8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8" t="b">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>40</v>
       </c>
       <c r="E9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" t="b">
         <v>0</v>
@@ -1747,7 +1747,7 @@
         <v>40</v>
       </c>
       <c r="E10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F10" t="b">
         <v>0</v>
@@ -1815,7 +1815,7 @@
         <v>40</v>
       </c>
       <c r="E11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F11" t="b">
         <v>0</v>
@@ -1883,7 +1883,7 @@
         <v>40</v>
       </c>
       <c r="E12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F12" t="b">
         <v>0</v>
@@ -1951,7 +1951,7 @@
         <v>40</v>
       </c>
       <c r="E13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F13" t="b">
         <v>0</v>
@@ -2019,7 +2019,7 @@
         <v>40</v>
       </c>
       <c r="E14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14" t="b">
         <v>0</v>
@@ -2155,7 +2155,7 @@
         <v>85</v>
       </c>
       <c r="E16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F16" t="b">
         <v>0</v>
@@ -2223,7 +2223,7 @@
         <v>89</v>
       </c>
       <c r="E17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F17" t="b">
         <v>0</v>
@@ -2291,7 +2291,7 @@
         <v>40</v>
       </c>
       <c r="E18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F18" t="b">
         <v>0</v>
@@ -2359,7 +2359,7 @@
         <v>96</v>
       </c>
       <c r="E19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F19" t="b">
         <v>0</v>
@@ -2427,7 +2427,7 @@
         <v>85</v>
       </c>
       <c r="E20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F20" t="b">
         <v>0</v>
@@ -2559,7 +2559,7 @@
         <v>89</v>
       </c>
       <c r="E22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F22" t="b">
         <v>0</v>
@@ -2625,7 +2625,7 @@
         <v>40</v>
       </c>
       <c r="E23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F23" t="b">
         <v>0</v>
@@ -2691,7 +2691,7 @@
         <v>25</v>
       </c>
       <c r="E24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F24" t="b">
         <v>0</v>
@@ -2757,7 +2757,7 @@
         <v>25</v>
       </c>
       <c r="E25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F25" t="b">
         <v>0</v>
@@ -2823,7 +2823,7 @@
         <v>25</v>
       </c>
       <c r="E26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F26" t="b">
         <v>0</v>
@@ -2955,7 +2955,7 @@
         <v>25</v>
       </c>
       <c r="E28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F28" t="b">
         <v>0</v>
@@ -3021,7 +3021,7 @@
         <v>25</v>
       </c>
       <c r="E29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F29" t="b">
         <v>0</v>
@@ -3087,7 +3087,7 @@
         <v>25</v>
       </c>
       <c r="E30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F30" t="b">
         <v>0</v>
@@ -3153,7 +3153,7 @@
         <v>25</v>
       </c>
       <c r="E31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F31" t="b">
         <v>0</v>
@@ -3222,7 +3222,7 @@
         <v>1</v>
       </c>
       <c r="F32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G32" t="s">
         <v>134</v>
@@ -3256,10 +3256,10 @@
         <v>0</v>
       </c>
       <c r="R32" t="s">
-        <v>101</v>
+        <v>27</v>
       </c>
       <c r="S32" t="s">
-        <v>102</v>
+        <v>28</v>
       </c>
       <c r="T32" t="b">
         <v>0</v>
@@ -3285,7 +3285,7 @@
         <v>137</v>
       </c>
       <c r="E33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F33" t="b">
         <v>0</v>
@@ -3351,7 +3351,7 @@
         <v>96</v>
       </c>
       <c r="E34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F34" t="b">
         <v>0</v>
@@ -3417,7 +3417,7 @@
         <v>96</v>
       </c>
       <c r="E35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F35" t="b">
         <v>0</v>
@@ -3483,7 +3483,7 @@
         <v>96</v>
       </c>
       <c r="E36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F36" t="b">
         <v>0</v>
@@ -3549,7 +3549,7 @@
         <v>96</v>
       </c>
       <c r="E37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F37" t="b">
         <v>0</v>
@@ -3615,7 +3615,7 @@
         <v>96</v>
       </c>
       <c r="E38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F38" t="b">
         <v>0</v>
@@ -3681,7 +3681,7 @@
         <v>96</v>
       </c>
       <c r="E39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F39" t="b">
         <v>0</v>
@@ -3747,7 +3747,7 @@
         <v>35</v>
       </c>
       <c r="E40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F40" t="b">
         <v>0</v>

--- a/05 dependency and cleanup reports/scuc_dependency_scan_and_cleanup_plan.xlsx
+++ b/05 dependency and cleanup reports/scuc_dependency_scan_and_cleanup_plan.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="298">
   <si>
     <t xml:space="preserve">classification</t>
   </si>
@@ -519,6 +519,144 @@
     <t xml:space="preserve">line_excerpt</t>
   </si>
   <si>
+    <t xml:space="preserve">/Users/D/R Working Directory/29-Years-of-Data-SCUC/2023 Avg STAAR Scores By Subject - All Grades - Approaches or Above - all Groups Combined.qmd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29-Years-of-Data-SCUC/2023 Avg STAAR Scores By Subject - All Grades - Approaches or Above - all Groups Combined.qmd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ambiguous</t>
+  </si>
+  <si>
+    <t xml:space="preserve">filename only</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#                                   "SCUC_Snapshots_1995_to_2023_LONG_CANONICAL.csv")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#                                   "SCUC_Snapshots_1995_to_2023_LONG_CANONICAL.csv"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Users/D/R Working Directory/29-Years-of-Data-SCUC/2023 Avg STAAR Scores By Subject - All Grades - Failing - all Groups Combined.qmd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29-Years-of-Data-SCUC/2023 Avg STAAR Scores By Subject - All Grades - Failing - all Groups Combined.qmd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"SCUC_Snapshots_1995_to_2023_LONG_CANONICAL.csv")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Users/D/R Working Directory/29-Years-of-Data-SCUC/2023 Avg STAAR Scores By Subject - All Grades - Masters - all Groups Combined.qmd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29-Years-of-Data-SCUC/2023 Avg STAAR Scores By Subject - All Grades - Masters - all Groups Combined.qmd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Users/D/R Working Directory/29-Years-of-Data-SCUC/2023 Avg STAAR Scores By Subject - All Grades - Meets or Above - all Groups Combined.qmd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29-Years-of-Data-SCUC/2023 Avg STAAR Scores By Subject - All Grades - Meets or Above - all Groups Combined.qmd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Users/D/R Working Directory/29-Years-of-Data-SCUC/2023 Avg STAAR Scores by Ethnic Classification - All Grades - Approaches or Above.qmd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29-Years-of-Data-SCUC/2023 Avg STAAR Scores by Ethnic Classification - All Grades - Approaches or Above.qmd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Users/D/R Working Directory/29-Years-of-Data-SCUC/2023 Avg STAAR Scores by Ethnic Classification - All Grades - Failing.qmd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29-Years-of-Data-SCUC/2023 Avg STAAR Scores by Ethnic Classification - All Grades - Failing.qmd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Users/D/R Working Directory/29-Years-of-Data-SCUC/2023 Avg STAAR Scores by Ethnic Classification - All Grades - Masters.qmd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29-Years-of-Data-SCUC/2023 Avg STAAR Scores by Ethnic Classification - All Grades - Masters.qmd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Users/D/R Working Directory/29-Years-of-Data-SCUC/2023 Avg STAAR Scores by Ethnic Classification - All Grades - Meets or Above.qmd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29-Years-of-Data-SCUC/2023 Avg STAAR Scores by Ethnic Classification - All Grades - Meets or Above.qmd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Users/D/R Working Directory/29-Years-of-Data-SCUC/2023 Avg STAAR Scores by Other Classification - All Grades - Approaches or Above.qmd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29-Years-of-Data-SCUC/2023 Avg STAAR Scores by Other Classification - All Grades - Approaches or Above.qmd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Users/D/R Working Directory/29-Years-of-Data-SCUC/2023 Avg STAAR Scores by Other Classification - All Grades - Failing.qmd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29-Years-of-Data-SCUC/2023 Avg STAAR Scores by Other Classification - All Grades - Failing.qmd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Users/D/R Working Directory/29-Years-of-Data-SCUC/2023 Avg STAAR Scores by Other Classification - All Grades - Masters.qmd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29-Years-of-Data-SCUC/2023 Avg STAAR Scores by Other Classification - All Grades - Masters.qmd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Users/D/R Working Directory/29-Years-of-Data-SCUC/2023 Avg STAAR Scores by Other Classification - All Grades - Meets or Above.qmd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29-Years-of-Data-SCUC/2023 Avg STAAR Scores by Other Classification - All Grades - Meets or Above.qmd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#                                   "SSCUC_Snapshots_1995_to_2023_LONG_CANONICAL.csv"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Users/D/R Working Directory/29-Years-of-Data-SCUC/2023 district_perform.qmd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29-Years-of-Data-SCUC/2023 district_perform.qmd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Users/D/R Working Directory/29-Years-of-Data-SCUC/2023 expenses.qmd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29-Years-of-Data-SCUC/2023 expenses.qmd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Users/D/R Working Directory/29-Years-of-Data-SCUC/2023 sat_act.qmd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29-Years-of-Data-SCUC/2023 sat_act.qmd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Users/D/R Working Directory/29-Years-of-Data-SCUC/2023 staff.qmd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29-Years-of-Data-SCUC/2023 staff.qmd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Users/D/R Working Directory/29-Years-of-Data-SCUC/2023 student_demo.qmd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29-Years-of-Data-SCUC/2023 student_demo.qmd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#                                    "SCUC_Snapshots_1995_to_2023_LONG_CANONICAL.csv")</t>
+  </si>
+  <si>
+    <t xml:space="preserve"># df2 &lt;- read_csv(file = here::here("data", "SCUC_Snapshots_1995_to_2023_LONG_CANONICAL.csv"))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Users/D/R Working Directory/29-Years-of-Data-SCUC/2023 taxes_and_revenues.qmd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29-Years-of-Data-SCUC/2023 taxes_and_revenues.qmd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Users/D/R Working Directory/29-Years-of-Data-SCUC/2023 teachers.qmd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29-Years-of-Data-SCUC/2023 teachers.qmd</t>
+  </si>
+  <si>
     <t xml:space="preserve">/Users/D/R Working Directory/How to Build Plotly Plots/MULTIPLE PLOTLY PLOTS AT ONCE.qmd</t>
   </si>
   <si>
@@ -526,12 +664,6 @@
   </si>
   <si>
     <t xml:space="preserve">How to Build Plotly Plots</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ambiguous</t>
-  </si>
-  <si>
-    <t xml:space="preserve">filename only</t>
   </si>
   <si>
     <t xml:space="preserve">df2 &lt;- read_csv(file = here::here("data", "SCUC Snapshots 1995 to 2022-LONG.csv"), show_col_types = FALSE)</t>
@@ -1842,7 +1974,7 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -3850,19 +3982,19 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="B2" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="D2" t="s">
         <v>37</v>
       </c>
       <c r="E2" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="F2" t="s">
         <v>168</v>
@@ -3871,35 +4003,37 @@
         <v>169</v>
       </c>
       <c r="H2" t="s">
-        <v>170</v>
+        <v>85</v>
       </c>
       <c r="I2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J2" t="s">
+        <v>171</v>
+      </c>
+      <c r="K2" t="n">
+        <v>92</v>
+      </c>
+      <c r="L2" t="s">
         <v>172</v>
-      </c>
-      <c r="K2" t="n">
-        <v>38</v>
-      </c>
-      <c r="L2" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>119</v>
+        <v>64</v>
       </c>
       <c r="B3" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="D3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E3"/>
+        <v>37</v>
+      </c>
+      <c r="E3" t="s">
+        <v>65</v>
+      </c>
       <c r="F3" t="s">
         <v>168</v>
       </c>
@@ -3907,16 +4041,16 @@
         <v>169</v>
       </c>
       <c r="H3" t="s">
-        <v>170</v>
+        <v>85</v>
       </c>
       <c r="I3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K3" t="n">
-        <v>38</v>
+        <v>453</v>
       </c>
       <c r="L3" t="s">
         <v>173</v>
@@ -3924,46 +4058,48 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>121</v>
+        <v>64</v>
       </c>
       <c r="B4" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="C4" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="D4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E4"/>
+        <v>37</v>
+      </c>
+      <c r="E4" t="s">
+        <v>65</v>
+      </c>
       <c r="F4" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="G4" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="H4" t="s">
-        <v>170</v>
+        <v>85</v>
       </c>
       <c r="I4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K4" t="n">
-        <v>38</v>
+        <v>89</v>
       </c>
       <c r="L4" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="B5" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="C5" t="s">
         <v>40</v>
@@ -3972,7 +4108,7 @@
         <v>37</v>
       </c>
       <c r="E5" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="F5" t="s">
         <v>174</v>
@@ -3981,135 +4117,141 @@
         <v>175</v>
       </c>
       <c r="H5" t="s">
-        <v>25</v>
+        <v>85</v>
       </c>
       <c r="I5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K5" t="n">
-        <v>61</v>
+        <v>443</v>
       </c>
       <c r="L5" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>103</v>
+        <v>64</v>
       </c>
       <c r="B6" t="s">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="C6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6" t="s">
+        <v>65</v>
+      </c>
+      <c r="F6" t="s">
+        <v>177</v>
+      </c>
+      <c r="G6" t="s">
+        <v>178</v>
+      </c>
+      <c r="H6" t="s">
         <v>85</v>
       </c>
-      <c r="D6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6"/>
-      <c r="F6" t="s">
-        <v>174</v>
-      </c>
-      <c r="G6" t="s">
-        <v>175</v>
-      </c>
-      <c r="H6" t="s">
-        <v>25</v>
-      </c>
       <c r="I6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K6" t="n">
-        <v>59</v>
+        <v>92</v>
       </c>
       <c r="L6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>64</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="D7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E7"/>
+        <v>37</v>
+      </c>
+      <c r="E7" t="s">
+        <v>65</v>
+      </c>
       <c r="F7" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="G7" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="H7" t="s">
-        <v>25</v>
+        <v>85</v>
       </c>
       <c r="I7" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="J7" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K7" t="n">
-        <v>59</v>
+        <v>460</v>
       </c>
       <c r="L7" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>34</v>
+        <v>64</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="C8" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="D8" t="s">
-        <v>22</v>
-      </c>
-      <c r="E8"/>
+        <v>37</v>
+      </c>
+      <c r="E8" t="s">
+        <v>65</v>
+      </c>
       <c r="F8" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="G8" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="H8" t="s">
-        <v>25</v>
+        <v>85</v>
       </c>
       <c r="I8" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J8" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K8" t="n">
-        <v>59</v>
+        <v>93</v>
       </c>
       <c r="L8" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="B9" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="C9" t="s">
         <v>40</v>
@@ -4118,7 +4260,7 @@
         <v>37</v>
       </c>
       <c r="E9" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="F9" t="s">
         <v>179</v>
@@ -4127,27 +4269,27 @@
         <v>180</v>
       </c>
       <c r="H9" t="s">
-        <v>25</v>
+        <v>85</v>
       </c>
       <c r="I9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K9" t="n">
-        <v>50</v>
+        <v>449</v>
       </c>
       <c r="L9" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="B10" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="C10" t="s">
         <v>40</v>
@@ -4156,25 +4298,25 @@
         <v>37</v>
       </c>
       <c r="E10" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="F10" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="G10" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="H10" t="s">
-        <v>25</v>
+        <v>85</v>
       </c>
       <c r="I10" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J10" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K10" t="n">
-        <v>261</v>
+        <v>91</v>
       </c>
       <c r="L10" t="s">
         <v>176</v>
@@ -4182,10 +4324,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="B11" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="C11" t="s">
         <v>40</v>
@@ -4194,432 +4336,454 @@
         <v>37</v>
       </c>
       <c r="E11" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="F11" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="G11" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="H11" t="s">
-        <v>25</v>
+        <v>85</v>
       </c>
       <c r="I11" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J11" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K11" t="n">
-        <v>418</v>
+        <v>474</v>
       </c>
       <c r="L11" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>103</v>
+        <v>64</v>
       </c>
       <c r="B12" t="s">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="C12" t="s">
+        <v>40</v>
+      </c>
+      <c r="D12" t="s">
+        <v>37</v>
+      </c>
+      <c r="E12" t="s">
+        <v>65</v>
+      </c>
+      <c r="F12" t="s">
+        <v>183</v>
+      </c>
+      <c r="G12" t="s">
+        <v>184</v>
+      </c>
+      <c r="H12" t="s">
         <v>85</v>
       </c>
-      <c r="D12" t="s">
-        <v>22</v>
-      </c>
-      <c r="E12"/>
-      <c r="F12" t="s">
-        <v>179</v>
-      </c>
-      <c r="G12" t="s">
-        <v>180</v>
-      </c>
-      <c r="H12" t="s">
-        <v>25</v>
-      </c>
       <c r="I12" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J12" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K12" t="n">
-        <v>48</v>
+        <v>91</v>
       </c>
       <c r="L12" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>103</v>
+        <v>64</v>
       </c>
       <c r="B13" t="s">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="C13" t="s">
+        <v>40</v>
+      </c>
+      <c r="D13" t="s">
+        <v>37</v>
+      </c>
+      <c r="E13" t="s">
+        <v>65</v>
+      </c>
+      <c r="F13" t="s">
+        <v>183</v>
+      </c>
+      <c r="G13" t="s">
+        <v>184</v>
+      </c>
+      <c r="H13" t="s">
         <v>85</v>
       </c>
-      <c r="D13" t="s">
-        <v>22</v>
-      </c>
-      <c r="E13"/>
-      <c r="F13" t="s">
-        <v>179</v>
-      </c>
-      <c r="G13" t="s">
-        <v>180</v>
-      </c>
-      <c r="H13" t="s">
-        <v>25</v>
-      </c>
       <c r="I13" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J13" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K13" t="n">
-        <v>75</v>
+        <v>448</v>
       </c>
       <c r="L13" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>103</v>
+        <v>64</v>
       </c>
       <c r="B14" t="s">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="C14" t="s">
+        <v>40</v>
+      </c>
+      <c r="D14" t="s">
+        <v>37</v>
+      </c>
+      <c r="E14" t="s">
+        <v>65</v>
+      </c>
+      <c r="F14" t="s">
+        <v>185</v>
+      </c>
+      <c r="G14" t="s">
+        <v>186</v>
+      </c>
+      <c r="H14" t="s">
         <v>85</v>
       </c>
-      <c r="D14" t="s">
-        <v>22</v>
-      </c>
-      <c r="E14"/>
-      <c r="F14" t="s">
-        <v>179</v>
-      </c>
-      <c r="G14" t="s">
-        <v>180</v>
-      </c>
-      <c r="H14" t="s">
-        <v>25</v>
-      </c>
       <c r="I14" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K14" t="n">
-        <v>108</v>
+        <v>88</v>
       </c>
       <c r="L14" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>23</v>
+        <v>64</v>
       </c>
       <c r="B15" t="s">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="C15" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="D15" t="s">
-        <v>22</v>
-      </c>
-      <c r="E15"/>
+        <v>37</v>
+      </c>
+      <c r="E15" t="s">
+        <v>65</v>
+      </c>
       <c r="F15" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="G15" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="H15" t="s">
-        <v>25</v>
+        <v>85</v>
       </c>
       <c r="I15" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="J15" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K15" t="n">
-        <v>48</v>
+        <v>445</v>
       </c>
       <c r="L15" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>23</v>
+        <v>64</v>
       </c>
       <c r="B16" t="s">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="C16" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="D16" t="s">
-        <v>22</v>
-      </c>
-      <c r="E16"/>
+        <v>37</v>
+      </c>
+      <c r="E16" t="s">
+        <v>65</v>
+      </c>
       <c r="F16" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="G16" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="H16" t="s">
-        <v>25</v>
+        <v>85</v>
       </c>
       <c r="I16" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="J16" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K16" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="L16" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>23</v>
+        <v>64</v>
       </c>
       <c r="B17" t="s">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="C17" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="D17" t="s">
-        <v>22</v>
-      </c>
-      <c r="E17"/>
+        <v>37</v>
+      </c>
+      <c r="E17" t="s">
+        <v>65</v>
+      </c>
       <c r="F17" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="G17" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="H17" t="s">
-        <v>25</v>
+        <v>85</v>
       </c>
       <c r="I17" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="J17" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K17" t="n">
-        <v>108</v>
+        <v>444</v>
       </c>
       <c r="L17" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>34</v>
+        <v>64</v>
       </c>
       <c r="B18" t="s">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="C18" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="D18" t="s">
-        <v>22</v>
-      </c>
-      <c r="E18"/>
+        <v>37</v>
+      </c>
+      <c r="E18" t="s">
+        <v>65</v>
+      </c>
       <c r="F18" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="G18" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="H18" t="s">
-        <v>25</v>
+        <v>85</v>
       </c>
       <c r="I18" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J18" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K18" t="n">
-        <v>48</v>
+        <v>90</v>
       </c>
       <c r="L18" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>34</v>
+        <v>64</v>
       </c>
       <c r="B19" t="s">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="C19" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="D19" t="s">
-        <v>22</v>
-      </c>
-      <c r="E19"/>
+        <v>37</v>
+      </c>
+      <c r="E19" t="s">
+        <v>65</v>
+      </c>
       <c r="F19" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="G19" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="H19" t="s">
-        <v>25</v>
+        <v>85</v>
       </c>
       <c r="I19" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J19" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K19" t="n">
-        <v>75</v>
+        <v>443</v>
       </c>
       <c r="L19" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>34</v>
+        <v>64</v>
       </c>
       <c r="B20" t="s">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="C20" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="D20" t="s">
-        <v>22</v>
-      </c>
-      <c r="E20"/>
+        <v>37</v>
+      </c>
+      <c r="E20" t="s">
+        <v>65</v>
+      </c>
       <c r="F20" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G20" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H20" t="s">
-        <v>25</v>
+        <v>85</v>
       </c>
       <c r="I20" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J20" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K20" t="n">
-        <v>108</v>
+        <v>88</v>
       </c>
       <c r="L20" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>31</v>
+        <v>64</v>
       </c>
       <c r="B21" t="s">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="C21" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="D21" t="s">
-        <v>22</v>
-      </c>
-      <c r="E21"/>
+        <v>37</v>
+      </c>
+      <c r="E21" t="s">
+        <v>65</v>
+      </c>
       <c r="F21" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="G21" t="s">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="H21" t="s">
-        <v>25</v>
+        <v>85</v>
       </c>
       <c r="I21" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="J21" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K21" t="n">
-        <v>39</v>
+        <v>442</v>
       </c>
       <c r="L21" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>31</v>
+        <v>64</v>
       </c>
       <c r="B22" t="s">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="C22" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="D22" t="s">
-        <v>22</v>
-      </c>
-      <c r="E22"/>
+        <v>37</v>
+      </c>
+      <c r="E22" t="s">
+        <v>65</v>
+      </c>
       <c r="F22" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="G22" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="H22" t="s">
-        <v>25</v>
+        <v>85</v>
       </c>
       <c r="I22" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="J22" t="s">
+        <v>171</v>
+      </c>
+      <c r="K22" t="n">
+        <v>89</v>
+      </c>
+      <c r="L22" t="s">
         <v>172</v>
-      </c>
-      <c r="K22" t="n">
-        <v>176</v>
-      </c>
-      <c r="L22" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="B23" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="C23" t="s">
         <v>40</v>
@@ -4628,36 +4792,36 @@
         <v>37</v>
       </c>
       <c r="E23" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="F23" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="G23" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="H23" t="s">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="I23" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J23" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K23" t="n">
-        <v>90</v>
+        <v>451</v>
       </c>
       <c r="L23" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="B24" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="C24" t="s">
         <v>40</v>
@@ -4666,36 +4830,36 @@
         <v>37</v>
       </c>
       <c r="E24" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="F24" t="s">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="G24" t="s">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="H24" t="s">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="I24" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J24" t="s">
+        <v>171</v>
+      </c>
+      <c r="K24" t="n">
+        <v>89</v>
+      </c>
+      <c r="L24" t="s">
         <v>172</v>
-      </c>
-      <c r="K24" t="n">
-        <v>374</v>
-      </c>
-      <c r="L24" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="B25" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="C25" t="s">
         <v>40</v>
@@ -4704,36 +4868,36 @@
         <v>37</v>
       </c>
       <c r="E25" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="F25" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="G25" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="H25" t="s">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="I25" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J25" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K25" t="n">
-        <v>85</v>
+        <v>452</v>
       </c>
       <c r="L25" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="B26" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="C26" t="s">
         <v>40</v>
@@ -4742,36 +4906,36 @@
         <v>37</v>
       </c>
       <c r="E26" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="F26" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="G26" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="H26" t="s">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="I26" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J26" t="s">
+        <v>171</v>
+      </c>
+      <c r="K26" t="n">
+        <v>77</v>
+      </c>
+      <c r="L26" t="s">
         <v>172</v>
-      </c>
-      <c r="K26" t="n">
-        <v>370</v>
-      </c>
-      <c r="L26" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="B27" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="C27" t="s">
         <v>40</v>
@@ -4780,36 +4944,36 @@
         <v>37</v>
       </c>
       <c r="E27" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="F27" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="G27" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="H27" t="s">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="I27" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J27" t="s">
+        <v>171</v>
+      </c>
+      <c r="K27" t="n">
+        <v>424</v>
+      </c>
+      <c r="L27" t="s">
         <v>172</v>
-      </c>
-      <c r="K27" t="n">
-        <v>91</v>
-      </c>
-      <c r="L27" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="B28" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="C28" t="s">
         <v>40</v>
@@ -4818,36 +4982,36 @@
         <v>37</v>
       </c>
       <c r="E28" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="F28" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="G28" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="H28" t="s">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="I28" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J28" t="s">
+        <v>171</v>
+      </c>
+      <c r="K28" t="n">
+        <v>73</v>
+      </c>
+      <c r="L28" t="s">
         <v>172</v>
-      </c>
-      <c r="K28" t="n">
-        <v>381</v>
-      </c>
-      <c r="L28" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="B29" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="C29" t="s">
         <v>40</v>
@@ -4856,36 +5020,36 @@
         <v>37</v>
       </c>
       <c r="E29" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="F29" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="G29" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="H29" t="s">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="I29" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J29" t="s">
+        <v>171</v>
+      </c>
+      <c r="K29" t="n">
+        <v>427</v>
+      </c>
+      <c r="L29" t="s">
         <v>172</v>
-      </c>
-      <c r="K29" t="n">
-        <v>90</v>
-      </c>
-      <c r="L29" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="B30" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="C30" t="s">
         <v>40</v>
@@ -4894,36 +5058,36 @@
         <v>37</v>
       </c>
       <c r="E30" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="F30" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="G30" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="H30" t="s">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="I30" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J30" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K30" t="n">
-        <v>374</v>
+        <v>74</v>
       </c>
       <c r="L30" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="B31" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="C31" t="s">
         <v>40</v>
@@ -4932,36 +5096,36 @@
         <v>37</v>
       </c>
       <c r="E31" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="F31" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="G31" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="H31" t="s">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="I31" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J31" t="s">
+        <v>171</v>
+      </c>
+      <c r="K31" t="n">
+        <v>422</v>
+      </c>
+      <c r="L31" t="s">
         <v>172</v>
-      </c>
-      <c r="K31" t="n">
-        <v>85</v>
-      </c>
-      <c r="L31" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="B32" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="C32" t="s">
         <v>40</v>
@@ -4970,36 +5134,36 @@
         <v>37</v>
       </c>
       <c r="E32" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="F32" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="G32" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="H32" t="s">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="I32" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J32" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K32" t="n">
-        <v>387</v>
+        <v>80</v>
       </c>
       <c r="L32" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="B33" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="C33" t="s">
         <v>40</v>
@@ -5008,36 +5172,36 @@
         <v>37</v>
       </c>
       <c r="E33" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="F33" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="G33" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="H33" t="s">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="I33" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J33" t="s">
+        <v>171</v>
+      </c>
+      <c r="K33" t="n">
+        <v>439</v>
+      </c>
+      <c r="L33" t="s">
         <v>172</v>
-      </c>
-      <c r="K33" t="n">
-        <v>88</v>
-      </c>
-      <c r="L33" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="B34" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="C34" t="s">
         <v>40</v>
@@ -5046,36 +5210,36 @@
         <v>37</v>
       </c>
       <c r="E34" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="F34" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="G34" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="H34" t="s">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="I34" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J34" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K34" t="n">
-        <v>375</v>
+        <v>44</v>
       </c>
       <c r="L34" t="s">
-        <v>188</v>
+        <v>208</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="B35" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="C35" t="s">
         <v>40</v>
@@ -5084,36 +5248,36 @@
         <v>37</v>
       </c>
       <c r="E35" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="F35" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="G35" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="H35" t="s">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="I35" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J35" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K35" t="n">
-        <v>85</v>
+        <v>332</v>
       </c>
       <c r="L35" t="s">
-        <v>187</v>
+        <v>209</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="B36" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="C36" t="s">
         <v>40</v>
@@ -5122,36 +5286,36 @@
         <v>37</v>
       </c>
       <c r="E36" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="F36" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="G36" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="H36" t="s">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="I36" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J36" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K36" t="n">
-        <v>370</v>
+        <v>514</v>
       </c>
       <c r="L36" t="s">
-        <v>188</v>
+        <v>209</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="B37" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="C37" t="s">
         <v>40</v>
@@ -5160,36 +5324,36 @@
         <v>37</v>
       </c>
       <c r="E37" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="F37" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="G37" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="H37" t="s">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="I37" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J37" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K37" t="n">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="L37" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="B38" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="C38" t="s">
         <v>40</v>
@@ -5198,36 +5362,36 @@
         <v>37</v>
       </c>
       <c r="E38" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="F38" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="G38" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="H38" t="s">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="I38" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J38" t="s">
+        <v>171</v>
+      </c>
+      <c r="K38" t="n">
+        <v>416</v>
+      </c>
+      <c r="L38" t="s">
         <v>172</v>
-      </c>
-      <c r="K38" t="n">
-        <v>370</v>
-      </c>
-      <c r="L38" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="B39" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="C39" t="s">
         <v>40</v>
@@ -5236,36 +5400,36 @@
         <v>37</v>
       </c>
       <c r="E39" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="F39" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="G39" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="H39" t="s">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="I39" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J39" t="s">
+        <v>171</v>
+      </c>
+      <c r="K39" t="n">
+        <v>72</v>
+      </c>
+      <c r="L39" t="s">
         <v>172</v>
-      </c>
-      <c r="K39" t="n">
-        <v>84</v>
-      </c>
-      <c r="L39" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="B40" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="C40" t="s">
         <v>40</v>
@@ -5274,39 +5438,39 @@
         <v>37</v>
       </c>
       <c r="E40" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="F40" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="G40" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="H40" t="s">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="I40" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J40" t="s">
+        <v>171</v>
+      </c>
+      <c r="K40" t="n">
+        <v>419</v>
+      </c>
+      <c r="L40" t="s">
         <v>172</v>
-      </c>
-      <c r="K40" t="n">
-        <v>369</v>
-      </c>
-      <c r="L40" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="B41" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="C41" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="D41" t="s">
         <v>37</v>
@@ -5315,101 +5479,97 @@
         <v>49</v>
       </c>
       <c r="F41" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="G41" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="H41" t="s">
-        <v>35</v>
+        <v>216</v>
       </c>
       <c r="I41" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J41" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K41" t="n">
-        <v>84</v>
+        <v>38</v>
       </c>
       <c r="L41" t="s">
-        <v>187</v>
+        <v>217</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>48</v>
+        <v>119</v>
       </c>
       <c r="B42" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="C42" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="D42" t="s">
-        <v>37</v>
-      </c>
-      <c r="E42" t="s">
-        <v>49</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="E42"/>
       <c r="F42" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="G42" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="H42" t="s">
-        <v>35</v>
+        <v>216</v>
       </c>
       <c r="I42" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J42" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K42" t="n">
-        <v>370</v>
+        <v>38</v>
       </c>
       <c r="L42" t="s">
-        <v>188</v>
+        <v>217</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>48</v>
+        <v>121</v>
       </c>
       <c r="B43" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="C43" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="D43" t="s">
-        <v>37</v>
-      </c>
-      <c r="E43" t="s">
-        <v>49</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="E43"/>
       <c r="F43" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="G43" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="H43" t="s">
-        <v>35</v>
+        <v>216</v>
       </c>
       <c r="I43" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J43" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K43" t="n">
-        <v>84</v>
+        <v>38</v>
       </c>
       <c r="L43" t="s">
-        <v>187</v>
+        <v>217</v>
       </c>
     </row>
     <row r="44">
@@ -5429,139 +5589,133 @@
         <v>49</v>
       </c>
       <c r="F44" t="s">
-        <v>208</v>
+        <v>218</v>
       </c>
       <c r="G44" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="H44" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="I44" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J44" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K44" t="n">
-        <v>370</v>
+        <v>61</v>
       </c>
       <c r="L44" t="s">
-        <v>188</v>
+        <v>220</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>48</v>
+        <v>103</v>
       </c>
       <c r="B45" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="C45" t="s">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="D45" t="s">
-        <v>37</v>
-      </c>
-      <c r="E45" t="s">
-        <v>49</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="E45"/>
       <c r="F45" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="G45" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="H45" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="I45" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J45" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K45" t="n">
-        <v>84</v>
+        <v>59</v>
       </c>
       <c r="L45" t="s">
-        <v>187</v>
+        <v>221</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="B46" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="C46" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="D46" t="s">
-        <v>37</v>
-      </c>
-      <c r="E46" t="s">
-        <v>49</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="E46"/>
       <c r="F46" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="G46" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="H46" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="I46" t="s">
-        <v>171</v>
+        <v>222</v>
       </c>
       <c r="J46" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K46" t="n">
-        <v>370</v>
+        <v>59</v>
       </c>
       <c r="L46" t="s">
-        <v>188</v>
+        <v>221</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="B47" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="C47" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="D47" t="s">
-        <v>37</v>
-      </c>
-      <c r="E47" t="s">
-        <v>49</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="E47"/>
       <c r="F47" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="G47" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="H47" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="I47" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J47" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K47" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="L47" t="s">
-        <v>187</v>
+        <v>221</v>
       </c>
     </row>
     <row r="48">
@@ -5581,25 +5735,25 @@
         <v>49</v>
       </c>
       <c r="F48" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="G48" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="H48" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="I48" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J48" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K48" t="n">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="L48" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="49">
@@ -5619,25 +5773,25 @@
         <v>49</v>
       </c>
       <c r="F49" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="G49" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="H49" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="I49" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J49" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K49" t="n">
-        <v>322</v>
+        <v>261</v>
       </c>
       <c r="L49" t="s">
-        <v>193</v>
+        <v>220</v>
       </c>
     </row>
     <row r="50">
@@ -5657,443 +5811,421 @@
         <v>49</v>
       </c>
       <c r="F50" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="G50" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="H50" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="I50" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J50" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K50" t="n">
-        <v>38</v>
+        <v>418</v>
       </c>
       <c r="L50" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
+        <v>103</v>
+      </c>
+      <c r="B51" t="s">
+        <v>24</v>
+      </c>
+      <c r="C51" t="s">
+        <v>85</v>
+      </c>
+      <c r="D51" t="s">
+        <v>22</v>
+      </c>
+      <c r="E51"/>
+      <c r="F51" t="s">
+        <v>223</v>
+      </c>
+      <c r="G51" t="s">
+        <v>224</v>
+      </c>
+      <c r="H51" t="s">
+        <v>25</v>
+      </c>
+      <c r="I51" t="s">
+        <v>170</v>
+      </c>
+      <c r="J51" t="s">
+        <v>171</v>
+      </c>
+      <c r="K51" t="n">
         <v>48</v>
       </c>
-      <c r="B51" t="s">
-        <v>49</v>
-      </c>
-      <c r="C51" t="s">
-        <v>40</v>
-      </c>
-      <c r="D51" t="s">
-        <v>37</v>
-      </c>
-      <c r="E51" t="s">
-        <v>49</v>
-      </c>
-      <c r="F51" t="s">
-        <v>220</v>
-      </c>
-      <c r="G51" t="s">
+      <c r="L51" t="s">
         <v>221</v>
-      </c>
-      <c r="H51" t="s">
-        <v>35</v>
-      </c>
-      <c r="I51" t="s">
-        <v>171</v>
-      </c>
-      <c r="J51" t="s">
-        <v>172</v>
-      </c>
-      <c r="K51" t="n">
-        <v>53</v>
-      </c>
-      <c r="L51" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>48</v>
+        <v>103</v>
       </c>
       <c r="B52" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="C52" t="s">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="D52" t="s">
-        <v>37</v>
-      </c>
-      <c r="E52" t="s">
-        <v>49</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="E52"/>
       <c r="F52" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="G52" t="s">
+        <v>224</v>
+      </c>
+      <c r="H52" t="s">
+        <v>25</v>
+      </c>
+      <c r="I52" t="s">
+        <v>170</v>
+      </c>
+      <c r="J52" t="s">
+        <v>171</v>
+      </c>
+      <c r="K52" t="n">
+        <v>75</v>
+      </c>
+      <c r="L52" t="s">
         <v>221</v>
-      </c>
-      <c r="H52" t="s">
-        <v>35</v>
-      </c>
-      <c r="I52" t="s">
-        <v>171</v>
-      </c>
-      <c r="J52" t="s">
-        <v>172</v>
-      </c>
-      <c r="K52" t="n">
-        <v>247</v>
-      </c>
-      <c r="L52" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>48</v>
+        <v>103</v>
       </c>
       <c r="B53" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="C53" t="s">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="D53" t="s">
-        <v>37</v>
-      </c>
-      <c r="E53" t="s">
-        <v>49</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="E53"/>
       <c r="F53" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="G53" t="s">
+        <v>224</v>
+      </c>
+      <c r="H53" t="s">
+        <v>25</v>
+      </c>
+      <c r="I53" t="s">
+        <v>170</v>
+      </c>
+      <c r="J53" t="s">
+        <v>171</v>
+      </c>
+      <c r="K53" t="n">
+        <v>108</v>
+      </c>
+      <c r="L53" t="s">
         <v>221</v>
-      </c>
-      <c r="H53" t="s">
-        <v>35</v>
-      </c>
-      <c r="I53" t="s">
-        <v>171</v>
-      </c>
-      <c r="J53" t="s">
-        <v>172</v>
-      </c>
-      <c r="K53" t="n">
-        <v>427</v>
-      </c>
-      <c r="L53" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
+        <v>23</v>
+      </c>
+      <c r="B54" t="s">
+        <v>24</v>
+      </c>
+      <c r="C54" t="s">
+        <v>25</v>
+      </c>
+      <c r="D54" t="s">
+        <v>22</v>
+      </c>
+      <c r="E54"/>
+      <c r="F54" t="s">
+        <v>223</v>
+      </c>
+      <c r="G54" t="s">
+        <v>224</v>
+      </c>
+      <c r="H54" t="s">
+        <v>25</v>
+      </c>
+      <c r="I54" t="s">
+        <v>222</v>
+      </c>
+      <c r="J54" t="s">
+        <v>171</v>
+      </c>
+      <c r="K54" t="n">
         <v>48</v>
       </c>
-      <c r="B54" t="s">
-        <v>49</v>
-      </c>
-      <c r="C54" t="s">
-        <v>40</v>
-      </c>
-      <c r="D54" t="s">
-        <v>37</v>
-      </c>
-      <c r="E54" t="s">
-        <v>49</v>
-      </c>
-      <c r="F54" t="s">
-        <v>220</v>
-      </c>
-      <c r="G54" t="s">
+      <c r="L54" t="s">
         <v>221</v>
-      </c>
-      <c r="H54" t="s">
-        <v>35</v>
-      </c>
-      <c r="I54" t="s">
-        <v>171</v>
-      </c>
-      <c r="J54" t="s">
-        <v>172</v>
-      </c>
-      <c r="K54" t="n">
-        <v>603</v>
-      </c>
-      <c r="L54" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="B55" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="C55" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="D55" t="s">
-        <v>37</v>
-      </c>
-      <c r="E55" t="s">
-        <v>49</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="E55"/>
       <c r="F55" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="G55" t="s">
+        <v>224</v>
+      </c>
+      <c r="H55" t="s">
+        <v>25</v>
+      </c>
+      <c r="I55" t="s">
+        <v>222</v>
+      </c>
+      <c r="J55" t="s">
+        <v>171</v>
+      </c>
+      <c r="K55" t="n">
+        <v>75</v>
+      </c>
+      <c r="L55" t="s">
         <v>221</v>
-      </c>
-      <c r="H55" t="s">
-        <v>35</v>
-      </c>
-      <c r="I55" t="s">
-        <v>171</v>
-      </c>
-      <c r="J55" t="s">
-        <v>172</v>
-      </c>
-      <c r="K55" t="n">
-        <v>787</v>
-      </c>
-      <c r="L55" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="B56" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="C56" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="D56" t="s">
-        <v>37</v>
-      </c>
-      <c r="E56" t="s">
-        <v>49</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="E56"/>
       <c r="F56" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="G56" t="s">
+        <v>224</v>
+      </c>
+      <c r="H56" t="s">
+        <v>25</v>
+      </c>
+      <c r="I56" t="s">
+        <v>222</v>
+      </c>
+      <c r="J56" t="s">
+        <v>171</v>
+      </c>
+      <c r="K56" t="n">
+        <v>108</v>
+      </c>
+      <c r="L56" t="s">
         <v>221</v>
-      </c>
-      <c r="H56" t="s">
-        <v>35</v>
-      </c>
-      <c r="I56" t="s">
-        <v>171</v>
-      </c>
-      <c r="J56" t="s">
-        <v>172</v>
-      </c>
-      <c r="K56" t="n">
-        <v>969</v>
-      </c>
-      <c r="L56" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
+        <v>34</v>
+      </c>
+      <c r="B57" t="s">
+        <v>24</v>
+      </c>
+      <c r="C57" t="s">
+        <v>35</v>
+      </c>
+      <c r="D57" t="s">
+        <v>22</v>
+      </c>
+      <c r="E57"/>
+      <c r="F57" t="s">
+        <v>223</v>
+      </c>
+      <c r="G57" t="s">
+        <v>224</v>
+      </c>
+      <c r="H57" t="s">
+        <v>25</v>
+      </c>
+      <c r="I57" t="s">
+        <v>170</v>
+      </c>
+      <c r="J57" t="s">
+        <v>171</v>
+      </c>
+      <c r="K57" t="n">
         <v>48</v>
       </c>
-      <c r="B57" t="s">
-        <v>49</v>
-      </c>
-      <c r="C57" t="s">
-        <v>40</v>
-      </c>
-      <c r="D57" t="s">
-        <v>37</v>
-      </c>
-      <c r="E57" t="s">
-        <v>49</v>
-      </c>
-      <c r="F57" t="s">
-        <v>220</v>
-      </c>
-      <c r="G57" t="s">
+      <c r="L57" t="s">
         <v>221</v>
-      </c>
-      <c r="H57" t="s">
-        <v>35</v>
-      </c>
-      <c r="I57" t="s">
-        <v>171</v>
-      </c>
-      <c r="J57" t="s">
-        <v>172</v>
-      </c>
-      <c r="K57" t="n">
-        <v>1157</v>
-      </c>
-      <c r="L57" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="B58" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="C58" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="D58" t="s">
-        <v>37</v>
-      </c>
-      <c r="E58" t="s">
-        <v>49</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="E58"/>
       <c r="F58" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="G58" t="s">
+        <v>224</v>
+      </c>
+      <c r="H58" t="s">
+        <v>25</v>
+      </c>
+      <c r="I58" t="s">
+        <v>170</v>
+      </c>
+      <c r="J58" t="s">
+        <v>171</v>
+      </c>
+      <c r="K58" t="n">
+        <v>75</v>
+      </c>
+      <c r="L58" t="s">
         <v>221</v>
-      </c>
-      <c r="H58" t="s">
-        <v>35</v>
-      </c>
-      <c r="I58" t="s">
-        <v>171</v>
-      </c>
-      <c r="J58" t="s">
-        <v>172</v>
-      </c>
-      <c r="K58" t="n">
-        <v>1302</v>
-      </c>
-      <c r="L58" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="B59" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="C59" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="D59" t="s">
-        <v>37</v>
-      </c>
-      <c r="E59" t="s">
-        <v>49</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="E59"/>
       <c r="F59" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="G59" t="s">
+        <v>224</v>
+      </c>
+      <c r="H59" t="s">
+        <v>25</v>
+      </c>
+      <c r="I59" t="s">
+        <v>170</v>
+      </c>
+      <c r="J59" t="s">
+        <v>171</v>
+      </c>
+      <c r="K59" t="n">
+        <v>108</v>
+      </c>
+      <c r="L59" t="s">
         <v>221</v>
-      </c>
-      <c r="H59" t="s">
-        <v>35</v>
-      </c>
-      <c r="I59" t="s">
-        <v>171</v>
-      </c>
-      <c r="J59" t="s">
-        <v>172</v>
-      </c>
-      <c r="K59" t="n">
-        <v>1447</v>
-      </c>
-      <c r="L59" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="B60" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="C60" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="D60" t="s">
-        <v>37</v>
-      </c>
-      <c r="E60" t="s">
-        <v>49</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="E60"/>
       <c r="F60" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="G60" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="H60" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="I60" t="s">
-        <v>171</v>
+        <v>222</v>
       </c>
       <c r="J60" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K60" t="n">
-        <v>1594</v>
+        <v>39</v>
       </c>
       <c r="L60" t="s">
-        <v>193</v>
+        <v>227</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="B61" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="C61" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="D61" t="s">
-        <v>37</v>
-      </c>
-      <c r="E61" t="s">
-        <v>49</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="E61"/>
       <c r="F61" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="G61" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="H61" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="I61" t="s">
-        <v>171</v>
+        <v>222</v>
       </c>
       <c r="J61" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K61" t="n">
-        <v>1739</v>
+        <v>176</v>
       </c>
       <c r="L61" t="s">
-        <v>193</v>
+        <v>228</v>
       </c>
     </row>
     <row r="62">
@@ -6113,25 +6245,25 @@
         <v>49</v>
       </c>
       <c r="F62" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="G62" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="H62" t="s">
         <v>35</v>
       </c>
       <c r="I62" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J62" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K62" t="n">
-        <v>1888</v>
+        <v>90</v>
       </c>
       <c r="L62" t="s">
-        <v>193</v>
+        <v>231</v>
       </c>
     </row>
     <row r="63">
@@ -6151,25 +6283,25 @@
         <v>49</v>
       </c>
       <c r="F63" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="G63" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="H63" t="s">
         <v>35</v>
       </c>
       <c r="I63" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J63" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K63" t="n">
-        <v>2029</v>
+        <v>374</v>
       </c>
       <c r="L63" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
     </row>
     <row r="64">
@@ -6189,133 +6321,139 @@
         <v>49</v>
       </c>
       <c r="F64" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="G64" t="s">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="H64" t="s">
         <v>35</v>
       </c>
       <c r="I64" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J64" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K64" t="n">
-        <v>47</v>
+        <v>85</v>
       </c>
       <c r="L64" t="s">
-        <v>187</v>
+        <v>231</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>103</v>
+        <v>48</v>
       </c>
       <c r="B65" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="C65" t="s">
-        <v>85</v>
+        <v>40</v>
       </c>
       <c r="D65" t="s">
-        <v>22</v>
-      </c>
-      <c r="E65"/>
+        <v>37</v>
+      </c>
+      <c r="E65" t="s">
+        <v>49</v>
+      </c>
       <c r="F65" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="G65" t="s">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="H65" t="s">
         <v>35</v>
       </c>
       <c r="I65" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J65" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K65" t="n">
-        <v>186</v>
+        <v>370</v>
       </c>
       <c r="L65" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="B66" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="C66" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="D66" t="s">
-        <v>22</v>
-      </c>
-      <c r="E66"/>
+        <v>37</v>
+      </c>
+      <c r="E66" t="s">
+        <v>49</v>
+      </c>
       <c r="F66" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
       <c r="G66" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="H66" t="s">
         <v>35</v>
       </c>
       <c r="I66" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J66" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K66" t="n">
-        <v>186</v>
+        <v>91</v>
       </c>
       <c r="L66" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="B67" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="C67" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="D67" t="s">
-        <v>22</v>
-      </c>
-      <c r="E67"/>
+        <v>37</v>
+      </c>
+      <c r="E67" t="s">
+        <v>49</v>
+      </c>
       <c r="F67" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
       <c r="G67" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="H67" t="s">
         <v>35</v>
       </c>
       <c r="I67" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="J67" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K67" t="n">
-        <v>186</v>
+        <v>381</v>
       </c>
       <c r="L67" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
     </row>
     <row r="68">
@@ -6335,25 +6473,25 @@
         <v>49</v>
       </c>
       <c r="F68" t="s">
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="G68" t="s">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="H68" t="s">
         <v>35</v>
       </c>
       <c r="I68" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J68" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K68" t="n">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="L68" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
     <row r="69">
@@ -6373,25 +6511,25 @@
         <v>49</v>
       </c>
       <c r="F69" t="s">
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="G69" t="s">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="H69" t="s">
         <v>35</v>
       </c>
       <c r="I69" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J69" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K69" t="n">
-        <v>331</v>
+        <v>374</v>
       </c>
       <c r="L69" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="70">
@@ -6411,25 +6549,25 @@
         <v>49</v>
       </c>
       <c r="F70" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="G70" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="H70" t="s">
         <v>35</v>
       </c>
       <c r="I70" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J70" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K70" t="n">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="L70" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="71">
@@ -6449,25 +6587,25 @@
         <v>49</v>
       </c>
       <c r="F71" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="G71" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="H71" t="s">
         <v>35</v>
       </c>
       <c r="I71" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J71" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K71" t="n">
-        <v>241</v>
+        <v>387</v>
       </c>
       <c r="L71" t="s">
-        <v>188</v>
+        <v>232</v>
       </c>
     </row>
     <row r="72">
@@ -6487,25 +6625,25 @@
         <v>49</v>
       </c>
       <c r="F72" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="G72" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="H72" t="s">
         <v>35</v>
       </c>
       <c r="I72" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J72" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K72" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="L72" t="s">
-        <v>193</v>
+        <v>231</v>
       </c>
     </row>
     <row r="73">
@@ -6525,25 +6663,25 @@
         <v>49</v>
       </c>
       <c r="F73" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="G73" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="H73" t="s">
         <v>35</v>
       </c>
       <c r="I73" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J73" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K73" t="n">
-        <v>100</v>
+        <v>375</v>
       </c>
       <c r="L73" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
     </row>
     <row r="74">
@@ -6563,25 +6701,25 @@
         <v>49</v>
       </c>
       <c r="F74" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="G74" t="s">
-        <v>234</v>
+        <v>245</v>
       </c>
       <c r="H74" t="s">
         <v>35</v>
       </c>
       <c r="I74" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J74" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K74" t="n">
-        <v>393</v>
+        <v>85</v>
       </c>
       <c r="L74" t="s">
-        <v>193</v>
+        <v>231</v>
       </c>
     </row>
     <row r="75">
@@ -6601,25 +6739,25 @@
         <v>49</v>
       </c>
       <c r="F75" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="G75" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="H75" t="s">
         <v>35</v>
       </c>
       <c r="I75" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J75" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K75" t="n">
-        <v>76</v>
+        <v>370</v>
       </c>
       <c r="L75" t="s">
-        <v>193</v>
+        <v>232</v>
       </c>
     </row>
     <row r="76">
@@ -6639,25 +6777,25 @@
         <v>49</v>
       </c>
       <c r="F76" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="G76" t="s">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="H76" t="s">
         <v>35</v>
       </c>
       <c r="I76" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J76" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K76" t="n">
-        <v>370</v>
+        <v>85</v>
       </c>
       <c r="L76" t="s">
-        <v>193</v>
+        <v>231</v>
       </c>
     </row>
     <row r="77">
@@ -6677,25 +6815,25 @@
         <v>49</v>
       </c>
       <c r="F77" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="G77" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="H77" t="s">
         <v>35</v>
       </c>
       <c r="I77" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J77" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K77" t="n">
-        <v>69</v>
+        <v>370</v>
       </c>
       <c r="L77" t="s">
-        <v>193</v>
+        <v>232</v>
       </c>
     </row>
     <row r="78">
@@ -6715,25 +6853,25 @@
         <v>49</v>
       </c>
       <c r="F78" t="s">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="G78" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="H78" t="s">
         <v>35</v>
       </c>
       <c r="I78" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J78" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K78" t="n">
-        <v>363</v>
+        <v>84</v>
       </c>
       <c r="L78" t="s">
-        <v>193</v>
+        <v>231</v>
       </c>
     </row>
     <row r="79">
@@ -6753,25 +6891,25 @@
         <v>49</v>
       </c>
       <c r="F79" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="G79" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="H79" t="s">
         <v>35</v>
       </c>
       <c r="I79" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J79" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K79" t="n">
-        <v>77</v>
+        <v>369</v>
       </c>
       <c r="L79" t="s">
-        <v>193</v>
+        <v>232</v>
       </c>
     </row>
     <row r="80">
@@ -6791,25 +6929,25 @@
         <v>49</v>
       </c>
       <c r="F80" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="G80" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
       <c r="H80" t="s">
         <v>35</v>
       </c>
       <c r="I80" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J80" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K80" t="n">
-        <v>376</v>
+        <v>84</v>
       </c>
       <c r="L80" t="s">
-        <v>193</v>
+        <v>231</v>
       </c>
     </row>
     <row r="81">
@@ -6829,25 +6967,25 @@
         <v>49</v>
       </c>
       <c r="F81" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="G81" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="H81" t="s">
         <v>35</v>
       </c>
       <c r="I81" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J81" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K81" t="n">
-        <v>49</v>
+        <v>370</v>
       </c>
       <c r="L81" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
     </row>
     <row r="82">
@@ -6867,25 +7005,25 @@
         <v>49</v>
       </c>
       <c r="F82" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="G82" t="s">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="H82" t="s">
         <v>35</v>
       </c>
       <c r="I82" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J82" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K82" t="n">
-        <v>357</v>
+        <v>84</v>
       </c>
       <c r="L82" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
     </row>
     <row r="83">
@@ -6905,25 +7043,25 @@
         <v>49</v>
       </c>
       <c r="F83" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="G83" t="s">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="H83" t="s">
         <v>35</v>
       </c>
       <c r="I83" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J83" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K83" t="n">
-        <v>522</v>
+        <v>370</v>
       </c>
       <c r="L83" t="s">
-        <v>245</v>
+        <v>232</v>
       </c>
     </row>
     <row r="84">
@@ -6943,25 +7081,25 @@
         <v>49</v>
       </c>
       <c r="F84" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="G84" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="H84" t="s">
         <v>35</v>
       </c>
       <c r="I84" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J84" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K84" t="n">
-        <v>37</v>
+        <v>84</v>
       </c>
       <c r="L84" t="s">
-        <v>187</v>
+        <v>231</v>
       </c>
     </row>
     <row r="85">
@@ -6981,25 +7119,25 @@
         <v>49</v>
       </c>
       <c r="F85" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="G85" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="H85" t="s">
         <v>35</v>
       </c>
       <c r="I85" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J85" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K85" t="n">
-        <v>87</v>
+        <v>370</v>
       </c>
       <c r="L85" t="s">
-        <v>193</v>
+        <v>232</v>
       </c>
     </row>
     <row r="86">
@@ -7019,25 +7157,25 @@
         <v>49</v>
       </c>
       <c r="F86" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="G86" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="H86" t="s">
         <v>35</v>
       </c>
       <c r="I86" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J86" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K86" t="n">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="L86" t="s">
-        <v>193</v>
+        <v>231</v>
       </c>
     </row>
     <row r="87">
@@ -7057,25 +7195,25 @@
         <v>49</v>
       </c>
       <c r="F87" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="G87" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="H87" t="s">
         <v>35</v>
       </c>
       <c r="I87" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J87" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K87" t="n">
-        <v>371</v>
+        <v>73</v>
       </c>
       <c r="L87" t="s">
-        <v>193</v>
+        <v>260</v>
       </c>
     </row>
     <row r="88">
@@ -7095,25 +7233,25 @@
         <v>49</v>
       </c>
       <c r="F88" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="G88" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="H88" t="s">
         <v>35</v>
       </c>
       <c r="I88" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J88" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K88" t="n">
-        <v>77</v>
+        <v>322</v>
       </c>
       <c r="L88" t="s">
-        <v>193</v>
+        <v>237</v>
       </c>
     </row>
     <row r="89">
@@ -7133,25 +7271,25 @@
         <v>49</v>
       </c>
       <c r="F89" t="s">
-        <v>250</v>
+        <v>261</v>
       </c>
       <c r="G89" t="s">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="H89" t="s">
         <v>35</v>
       </c>
       <c r="I89" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J89" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K89" t="n">
-        <v>371</v>
+        <v>38</v>
       </c>
       <c r="L89" t="s">
-        <v>193</v>
+        <v>263</v>
       </c>
     </row>
     <row r="90">
@@ -7171,25 +7309,25 @@
         <v>49</v>
       </c>
       <c r="F90" t="s">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="G90" t="s">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="H90" t="s">
         <v>35</v>
       </c>
       <c r="I90" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J90" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K90" t="n">
-        <v>85</v>
+        <v>53</v>
       </c>
       <c r="L90" t="s">
-        <v>216</v>
+        <v>237</v>
       </c>
     </row>
     <row r="91">
@@ -7209,25 +7347,1501 @@
         <v>49</v>
       </c>
       <c r="F91" t="s">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="G91" t="s">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="H91" t="s">
         <v>35</v>
       </c>
       <c r="I91" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J91" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K91" t="n">
+        <v>247</v>
+      </c>
+      <c r="L91" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s">
+        <v>48</v>
+      </c>
+      <c r="B92" t="s">
+        <v>49</v>
+      </c>
+      <c r="C92" t="s">
+        <v>40</v>
+      </c>
+      <c r="D92" t="s">
+        <v>37</v>
+      </c>
+      <c r="E92" t="s">
+        <v>49</v>
+      </c>
+      <c r="F92" t="s">
+        <v>264</v>
+      </c>
+      <c r="G92" t="s">
+        <v>265</v>
+      </c>
+      <c r="H92" t="s">
+        <v>35</v>
+      </c>
+      <c r="I92" t="s">
+        <v>170</v>
+      </c>
+      <c r="J92" t="s">
+        <v>171</v>
+      </c>
+      <c r="K92" t="n">
+        <v>427</v>
+      </c>
+      <c r="L92" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s">
+        <v>48</v>
+      </c>
+      <c r="B93" t="s">
+        <v>49</v>
+      </c>
+      <c r="C93" t="s">
+        <v>40</v>
+      </c>
+      <c r="D93" t="s">
+        <v>37</v>
+      </c>
+      <c r="E93" t="s">
+        <v>49</v>
+      </c>
+      <c r="F93" t="s">
+        <v>264</v>
+      </c>
+      <c r="G93" t="s">
+        <v>265</v>
+      </c>
+      <c r="H93" t="s">
+        <v>35</v>
+      </c>
+      <c r="I93" t="s">
+        <v>170</v>
+      </c>
+      <c r="J93" t="s">
+        <v>171</v>
+      </c>
+      <c r="K93" t="n">
+        <v>603</v>
+      </c>
+      <c r="L93" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s">
+        <v>48</v>
+      </c>
+      <c r="B94" t="s">
+        <v>49</v>
+      </c>
+      <c r="C94" t="s">
+        <v>40</v>
+      </c>
+      <c r="D94" t="s">
+        <v>37</v>
+      </c>
+      <c r="E94" t="s">
+        <v>49</v>
+      </c>
+      <c r="F94" t="s">
+        <v>264</v>
+      </c>
+      <c r="G94" t="s">
+        <v>265</v>
+      </c>
+      <c r="H94" t="s">
+        <v>35</v>
+      </c>
+      <c r="I94" t="s">
+        <v>170</v>
+      </c>
+      <c r="J94" t="s">
+        <v>171</v>
+      </c>
+      <c r="K94" t="n">
+        <v>787</v>
+      </c>
+      <c r="L94" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s">
+        <v>48</v>
+      </c>
+      <c r="B95" t="s">
+        <v>49</v>
+      </c>
+      <c r="C95" t="s">
+        <v>40</v>
+      </c>
+      <c r="D95" t="s">
+        <v>37</v>
+      </c>
+      <c r="E95" t="s">
+        <v>49</v>
+      </c>
+      <c r="F95" t="s">
+        <v>264</v>
+      </c>
+      <c r="G95" t="s">
+        <v>265</v>
+      </c>
+      <c r="H95" t="s">
+        <v>35</v>
+      </c>
+      <c r="I95" t="s">
+        <v>170</v>
+      </c>
+      <c r="J95" t="s">
+        <v>171</v>
+      </c>
+      <c r="K95" t="n">
+        <v>969</v>
+      </c>
+      <c r="L95" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s">
+        <v>48</v>
+      </c>
+      <c r="B96" t="s">
+        <v>49</v>
+      </c>
+      <c r="C96" t="s">
+        <v>40</v>
+      </c>
+      <c r="D96" t="s">
+        <v>37</v>
+      </c>
+      <c r="E96" t="s">
+        <v>49</v>
+      </c>
+      <c r="F96" t="s">
+        <v>264</v>
+      </c>
+      <c r="G96" t="s">
+        <v>265</v>
+      </c>
+      <c r="H96" t="s">
+        <v>35</v>
+      </c>
+      <c r="I96" t="s">
+        <v>170</v>
+      </c>
+      <c r="J96" t="s">
+        <v>171</v>
+      </c>
+      <c r="K96" t="n">
+        <v>1157</v>
+      </c>
+      <c r="L96" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s">
+        <v>48</v>
+      </c>
+      <c r="B97" t="s">
+        <v>49</v>
+      </c>
+      <c r="C97" t="s">
+        <v>40</v>
+      </c>
+      <c r="D97" t="s">
+        <v>37</v>
+      </c>
+      <c r="E97" t="s">
+        <v>49</v>
+      </c>
+      <c r="F97" t="s">
+        <v>264</v>
+      </c>
+      <c r="G97" t="s">
+        <v>265</v>
+      </c>
+      <c r="H97" t="s">
+        <v>35</v>
+      </c>
+      <c r="I97" t="s">
+        <v>170</v>
+      </c>
+      <c r="J97" t="s">
+        <v>171</v>
+      </c>
+      <c r="K97" t="n">
+        <v>1302</v>
+      </c>
+      <c r="L97" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s">
+        <v>48</v>
+      </c>
+      <c r="B98" t="s">
+        <v>49</v>
+      </c>
+      <c r="C98" t="s">
+        <v>40</v>
+      </c>
+      <c r="D98" t="s">
+        <v>37</v>
+      </c>
+      <c r="E98" t="s">
+        <v>49</v>
+      </c>
+      <c r="F98" t="s">
+        <v>264</v>
+      </c>
+      <c r="G98" t="s">
+        <v>265</v>
+      </c>
+      <c r="H98" t="s">
+        <v>35</v>
+      </c>
+      <c r="I98" t="s">
+        <v>170</v>
+      </c>
+      <c r="J98" t="s">
+        <v>171</v>
+      </c>
+      <c r="K98" t="n">
+        <v>1447</v>
+      </c>
+      <c r="L98" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s">
+        <v>48</v>
+      </c>
+      <c r="B99" t="s">
+        <v>49</v>
+      </c>
+      <c r="C99" t="s">
+        <v>40</v>
+      </c>
+      <c r="D99" t="s">
+        <v>37</v>
+      </c>
+      <c r="E99" t="s">
+        <v>49</v>
+      </c>
+      <c r="F99" t="s">
+        <v>264</v>
+      </c>
+      <c r="G99" t="s">
+        <v>265</v>
+      </c>
+      <c r="H99" t="s">
+        <v>35</v>
+      </c>
+      <c r="I99" t="s">
+        <v>170</v>
+      </c>
+      <c r="J99" t="s">
+        <v>171</v>
+      </c>
+      <c r="K99" t="n">
+        <v>1594</v>
+      </c>
+      <c r="L99" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s">
+        <v>48</v>
+      </c>
+      <c r="B100" t="s">
+        <v>49</v>
+      </c>
+      <c r="C100" t="s">
+        <v>40</v>
+      </c>
+      <c r="D100" t="s">
+        <v>37</v>
+      </c>
+      <c r="E100" t="s">
+        <v>49</v>
+      </c>
+      <c r="F100" t="s">
+        <v>264</v>
+      </c>
+      <c r="G100" t="s">
+        <v>265</v>
+      </c>
+      <c r="H100" t="s">
+        <v>35</v>
+      </c>
+      <c r="I100" t="s">
+        <v>170</v>
+      </c>
+      <c r="J100" t="s">
+        <v>171</v>
+      </c>
+      <c r="K100" t="n">
+        <v>1739</v>
+      </c>
+      <c r="L100" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s">
+        <v>48</v>
+      </c>
+      <c r="B101" t="s">
+        <v>49</v>
+      </c>
+      <c r="C101" t="s">
+        <v>40</v>
+      </c>
+      <c r="D101" t="s">
+        <v>37</v>
+      </c>
+      <c r="E101" t="s">
+        <v>49</v>
+      </c>
+      <c r="F101" t="s">
+        <v>264</v>
+      </c>
+      <c r="G101" t="s">
+        <v>265</v>
+      </c>
+      <c r="H101" t="s">
+        <v>35</v>
+      </c>
+      <c r="I101" t="s">
+        <v>170</v>
+      </c>
+      <c r="J101" t="s">
+        <v>171</v>
+      </c>
+      <c r="K101" t="n">
+        <v>1888</v>
+      </c>
+      <c r="L101" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s">
+        <v>48</v>
+      </c>
+      <c r="B102" t="s">
+        <v>49</v>
+      </c>
+      <c r="C102" t="s">
+        <v>40</v>
+      </c>
+      <c r="D102" t="s">
+        <v>37</v>
+      </c>
+      <c r="E102" t="s">
+        <v>49</v>
+      </c>
+      <c r="F102" t="s">
+        <v>264</v>
+      </c>
+      <c r="G102" t="s">
+        <v>265</v>
+      </c>
+      <c r="H102" t="s">
+        <v>35</v>
+      </c>
+      <c r="I102" t="s">
+        <v>170</v>
+      </c>
+      <c r="J102" t="s">
+        <v>171</v>
+      </c>
+      <c r="K102" t="n">
+        <v>2029</v>
+      </c>
+      <c r="L102" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s">
+        <v>48</v>
+      </c>
+      <c r="B103" t="s">
+        <v>49</v>
+      </c>
+      <c r="C103" t="s">
+        <v>40</v>
+      </c>
+      <c r="D103" t="s">
+        <v>37</v>
+      </c>
+      <c r="E103" t="s">
+        <v>49</v>
+      </c>
+      <c r="F103" t="s">
+        <v>267</v>
+      </c>
+      <c r="G103" t="s">
+        <v>268</v>
+      </c>
+      <c r="H103" t="s">
+        <v>35</v>
+      </c>
+      <c r="I103" t="s">
+        <v>170</v>
+      </c>
+      <c r="J103" t="s">
+        <v>171</v>
+      </c>
+      <c r="K103" t="n">
+        <v>47</v>
+      </c>
+      <c r="L103" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s">
+        <v>103</v>
+      </c>
+      <c r="B104" t="s">
+        <v>24</v>
+      </c>
+      <c r="C104" t="s">
+        <v>85</v>
+      </c>
+      <c r="D104" t="s">
+        <v>22</v>
+      </c>
+      <c r="E104"/>
+      <c r="F104" t="s">
+        <v>267</v>
+      </c>
+      <c r="G104" t="s">
+        <v>268</v>
+      </c>
+      <c r="H104" t="s">
+        <v>35</v>
+      </c>
+      <c r="I104" t="s">
+        <v>170</v>
+      </c>
+      <c r="J104" t="s">
+        <v>171</v>
+      </c>
+      <c r="K104" t="n">
+        <v>186</v>
+      </c>
+      <c r="L104" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s">
+        <v>23</v>
+      </c>
+      <c r="B105" t="s">
+        <v>24</v>
+      </c>
+      <c r="C105" t="s">
+        <v>25</v>
+      </c>
+      <c r="D105" t="s">
+        <v>22</v>
+      </c>
+      <c r="E105"/>
+      <c r="F105" t="s">
+        <v>267</v>
+      </c>
+      <c r="G105" t="s">
+        <v>268</v>
+      </c>
+      <c r="H105" t="s">
+        <v>35</v>
+      </c>
+      <c r="I105" t="s">
+        <v>170</v>
+      </c>
+      <c r="J105" t="s">
+        <v>171</v>
+      </c>
+      <c r="K105" t="n">
+        <v>186</v>
+      </c>
+      <c r="L105" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s">
+        <v>34</v>
+      </c>
+      <c r="B106" t="s">
+        <v>24</v>
+      </c>
+      <c r="C106" t="s">
+        <v>35</v>
+      </c>
+      <c r="D106" t="s">
+        <v>22</v>
+      </c>
+      <c r="E106"/>
+      <c r="F106" t="s">
+        <v>267</v>
+      </c>
+      <c r="G106" t="s">
+        <v>268</v>
+      </c>
+      <c r="H106" t="s">
+        <v>35</v>
+      </c>
+      <c r="I106" t="s">
+        <v>222</v>
+      </c>
+      <c r="J106" t="s">
+        <v>171</v>
+      </c>
+      <c r="K106" t="n">
+        <v>186</v>
+      </c>
+      <c r="L106" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s">
+        <v>48</v>
+      </c>
+      <c r="B107" t="s">
+        <v>49</v>
+      </c>
+      <c r="C107" t="s">
+        <v>40</v>
+      </c>
+      <c r="D107" t="s">
+        <v>37</v>
+      </c>
+      <c r="E107" t="s">
+        <v>49</v>
+      </c>
+      <c r="F107" t="s">
+        <v>270</v>
+      </c>
+      <c r="G107" t="s">
+        <v>271</v>
+      </c>
+      <c r="H107" t="s">
+        <v>35</v>
+      </c>
+      <c r="I107" t="s">
+        <v>170</v>
+      </c>
+      <c r="J107" t="s">
+        <v>171</v>
+      </c>
+      <c r="K107" t="n">
+        <v>180</v>
+      </c>
+      <c r="L107" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s">
+        <v>48</v>
+      </c>
+      <c r="B108" t="s">
+        <v>49</v>
+      </c>
+      <c r="C108" t="s">
+        <v>40</v>
+      </c>
+      <c r="D108" t="s">
+        <v>37</v>
+      </c>
+      <c r="E108" t="s">
+        <v>49</v>
+      </c>
+      <c r="F108" t="s">
+        <v>270</v>
+      </c>
+      <c r="G108" t="s">
+        <v>271</v>
+      </c>
+      <c r="H108" t="s">
+        <v>35</v>
+      </c>
+      <c r="I108" t="s">
+        <v>170</v>
+      </c>
+      <c r="J108" t="s">
+        <v>171</v>
+      </c>
+      <c r="K108" t="n">
+        <v>331</v>
+      </c>
+      <c r="L108" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s">
+        <v>48</v>
+      </c>
+      <c r="B109" t="s">
+        <v>49</v>
+      </c>
+      <c r="C109" t="s">
+        <v>40</v>
+      </c>
+      <c r="D109" t="s">
+        <v>37</v>
+      </c>
+      <c r="E109" t="s">
+        <v>49</v>
+      </c>
+      <c r="F109" t="s">
+        <v>274</v>
+      </c>
+      <c r="G109" t="s">
+        <v>275</v>
+      </c>
+      <c r="H109" t="s">
+        <v>35</v>
+      </c>
+      <c r="I109" t="s">
+        <v>170</v>
+      </c>
+      <c r="J109" t="s">
+        <v>171</v>
+      </c>
+      <c r="K109" t="n">
+        <v>68</v>
+      </c>
+      <c r="L109" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s">
+        <v>48</v>
+      </c>
+      <c r="B110" t="s">
+        <v>49</v>
+      </c>
+      <c r="C110" t="s">
+        <v>40</v>
+      </c>
+      <c r="D110" t="s">
+        <v>37</v>
+      </c>
+      <c r="E110" t="s">
+        <v>49</v>
+      </c>
+      <c r="F110" t="s">
+        <v>274</v>
+      </c>
+      <c r="G110" t="s">
+        <v>275</v>
+      </c>
+      <c r="H110" t="s">
+        <v>35</v>
+      </c>
+      <c r="I110" t="s">
+        <v>170</v>
+      </c>
+      <c r="J110" t="s">
+        <v>171</v>
+      </c>
+      <c r="K110" t="n">
+        <v>241</v>
+      </c>
+      <c r="L110" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s">
+        <v>48</v>
+      </c>
+      <c r="B111" t="s">
+        <v>49</v>
+      </c>
+      <c r="C111" t="s">
+        <v>40</v>
+      </c>
+      <c r="D111" t="s">
+        <v>37</v>
+      </c>
+      <c r="E111" t="s">
+        <v>49</v>
+      </c>
+      <c r="F111" t="s">
+        <v>277</v>
+      </c>
+      <c r="G111" t="s">
+        <v>278</v>
+      </c>
+      <c r="H111" t="s">
+        <v>35</v>
+      </c>
+      <c r="I111" t="s">
+        <v>170</v>
+      </c>
+      <c r="J111" t="s">
+        <v>171</v>
+      </c>
+      <c r="K111" t="n">
+        <v>84</v>
+      </c>
+      <c r="L111" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s">
+        <v>48</v>
+      </c>
+      <c r="B112" t="s">
+        <v>49</v>
+      </c>
+      <c r="C112" t="s">
+        <v>40</v>
+      </c>
+      <c r="D112" t="s">
+        <v>37</v>
+      </c>
+      <c r="E112" t="s">
+        <v>49</v>
+      </c>
+      <c r="F112" t="s">
+        <v>277</v>
+      </c>
+      <c r="G112" t="s">
+        <v>278</v>
+      </c>
+      <c r="H112" t="s">
+        <v>35</v>
+      </c>
+      <c r="I112" t="s">
+        <v>170</v>
+      </c>
+      <c r="J112" t="s">
+        <v>171</v>
+      </c>
+      <c r="K112" t="n">
+        <v>100</v>
+      </c>
+      <c r="L112" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s">
+        <v>48</v>
+      </c>
+      <c r="B113" t="s">
+        <v>49</v>
+      </c>
+      <c r="C113" t="s">
+        <v>40</v>
+      </c>
+      <c r="D113" t="s">
+        <v>37</v>
+      </c>
+      <c r="E113" t="s">
+        <v>49</v>
+      </c>
+      <c r="F113" t="s">
+        <v>277</v>
+      </c>
+      <c r="G113" t="s">
+        <v>278</v>
+      </c>
+      <c r="H113" t="s">
+        <v>35</v>
+      </c>
+      <c r="I113" t="s">
+        <v>170</v>
+      </c>
+      <c r="J113" t="s">
+        <v>171</v>
+      </c>
+      <c r="K113" t="n">
+        <v>393</v>
+      </c>
+      <c r="L113" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s">
+        <v>48</v>
+      </c>
+      <c r="B114" t="s">
+        <v>49</v>
+      </c>
+      <c r="C114" t="s">
+        <v>40</v>
+      </c>
+      <c r="D114" t="s">
+        <v>37</v>
+      </c>
+      <c r="E114" t="s">
+        <v>49</v>
+      </c>
+      <c r="F114" t="s">
+        <v>280</v>
+      </c>
+      <c r="G114" t="s">
+        <v>281</v>
+      </c>
+      <c r="H114" t="s">
+        <v>35</v>
+      </c>
+      <c r="I114" t="s">
+        <v>170</v>
+      </c>
+      <c r="J114" t="s">
+        <v>171</v>
+      </c>
+      <c r="K114" t="n">
+        <v>76</v>
+      </c>
+      <c r="L114" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s">
+        <v>48</v>
+      </c>
+      <c r="B115" t="s">
+        <v>49</v>
+      </c>
+      <c r="C115" t="s">
+        <v>40</v>
+      </c>
+      <c r="D115" t="s">
+        <v>37</v>
+      </c>
+      <c r="E115" t="s">
+        <v>49</v>
+      </c>
+      <c r="F115" t="s">
+        <v>280</v>
+      </c>
+      <c r="G115" t="s">
+        <v>281</v>
+      </c>
+      <c r="H115" t="s">
+        <v>35</v>
+      </c>
+      <c r="I115" t="s">
+        <v>170</v>
+      </c>
+      <c r="J115" t="s">
+        <v>171</v>
+      </c>
+      <c r="K115" t="n">
+        <v>370</v>
+      </c>
+      <c r="L115" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s">
+        <v>48</v>
+      </c>
+      <c r="B116" t="s">
+        <v>49</v>
+      </c>
+      <c r="C116" t="s">
+        <v>40</v>
+      </c>
+      <c r="D116" t="s">
+        <v>37</v>
+      </c>
+      <c r="E116" t="s">
+        <v>49</v>
+      </c>
+      <c r="F116" t="s">
+        <v>282</v>
+      </c>
+      <c r="G116" t="s">
+        <v>283</v>
+      </c>
+      <c r="H116" t="s">
+        <v>35</v>
+      </c>
+      <c r="I116" t="s">
+        <v>170</v>
+      </c>
+      <c r="J116" t="s">
+        <v>171</v>
+      </c>
+      <c r="K116" t="n">
+        <v>69</v>
+      </c>
+      <c r="L116" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s">
+        <v>48</v>
+      </c>
+      <c r="B117" t="s">
+        <v>49</v>
+      </c>
+      <c r="C117" t="s">
+        <v>40</v>
+      </c>
+      <c r="D117" t="s">
+        <v>37</v>
+      </c>
+      <c r="E117" t="s">
+        <v>49</v>
+      </c>
+      <c r="F117" t="s">
+        <v>282</v>
+      </c>
+      <c r="G117" t="s">
+        <v>283</v>
+      </c>
+      <c r="H117" t="s">
+        <v>35</v>
+      </c>
+      <c r="I117" t="s">
+        <v>170</v>
+      </c>
+      <c r="J117" t="s">
+        <v>171</v>
+      </c>
+      <c r="K117" t="n">
+        <v>363</v>
+      </c>
+      <c r="L117" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s">
+        <v>48</v>
+      </c>
+      <c r="B118" t="s">
+        <v>49</v>
+      </c>
+      <c r="C118" t="s">
+        <v>40</v>
+      </c>
+      <c r="D118" t="s">
+        <v>37</v>
+      </c>
+      <c r="E118" t="s">
+        <v>49</v>
+      </c>
+      <c r="F118" t="s">
+        <v>284</v>
+      </c>
+      <c r="G118" t="s">
+        <v>285</v>
+      </c>
+      <c r="H118" t="s">
+        <v>35</v>
+      </c>
+      <c r="I118" t="s">
+        <v>170</v>
+      </c>
+      <c r="J118" t="s">
+        <v>171</v>
+      </c>
+      <c r="K118" t="n">
+        <v>77</v>
+      </c>
+      <c r="L118" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s">
+        <v>48</v>
+      </c>
+      <c r="B119" t="s">
+        <v>49</v>
+      </c>
+      <c r="C119" t="s">
+        <v>40</v>
+      </c>
+      <c r="D119" t="s">
+        <v>37</v>
+      </c>
+      <c r="E119" t="s">
+        <v>49</v>
+      </c>
+      <c r="F119" t="s">
+        <v>284</v>
+      </c>
+      <c r="G119" t="s">
+        <v>285</v>
+      </c>
+      <c r="H119" t="s">
+        <v>35</v>
+      </c>
+      <c r="I119" t="s">
+        <v>170</v>
+      </c>
+      <c r="J119" t="s">
+        <v>171</v>
+      </c>
+      <c r="K119" t="n">
+        <v>376</v>
+      </c>
+      <c r="L119" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s">
+        <v>48</v>
+      </c>
+      <c r="B120" t="s">
+        <v>49</v>
+      </c>
+      <c r="C120" t="s">
+        <v>40</v>
+      </c>
+      <c r="D120" t="s">
+        <v>37</v>
+      </c>
+      <c r="E120" t="s">
+        <v>49</v>
+      </c>
+      <c r="F120" t="s">
+        <v>286</v>
+      </c>
+      <c r="G120" t="s">
+        <v>287</v>
+      </c>
+      <c r="H120" t="s">
+        <v>35</v>
+      </c>
+      <c r="I120" t="s">
+        <v>170</v>
+      </c>
+      <c r="J120" t="s">
+        <v>171</v>
+      </c>
+      <c r="K120" t="n">
+        <v>49</v>
+      </c>
+      <c r="L120" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s">
+        <v>48</v>
+      </c>
+      <c r="B121" t="s">
+        <v>49</v>
+      </c>
+      <c r="C121" t="s">
+        <v>40</v>
+      </c>
+      <c r="D121" t="s">
+        <v>37</v>
+      </c>
+      <c r="E121" t="s">
+        <v>49</v>
+      </c>
+      <c r="F121" t="s">
+        <v>286</v>
+      </c>
+      <c r="G121" t="s">
+        <v>287</v>
+      </c>
+      <c r="H121" t="s">
+        <v>35</v>
+      </c>
+      <c r="I121" t="s">
+        <v>170</v>
+      </c>
+      <c r="J121" t="s">
+        <v>171</v>
+      </c>
+      <c r="K121" t="n">
+        <v>357</v>
+      </c>
+      <c r="L121" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s">
+        <v>48</v>
+      </c>
+      <c r="B122" t="s">
+        <v>49</v>
+      </c>
+      <c r="C122" t="s">
+        <v>40</v>
+      </c>
+      <c r="D122" t="s">
+        <v>37</v>
+      </c>
+      <c r="E122" t="s">
+        <v>49</v>
+      </c>
+      <c r="F122" t="s">
+        <v>286</v>
+      </c>
+      <c r="G122" t="s">
+        <v>287</v>
+      </c>
+      <c r="H122" t="s">
+        <v>35</v>
+      </c>
+      <c r="I122" t="s">
+        <v>170</v>
+      </c>
+      <c r="J122" t="s">
+        <v>171</v>
+      </c>
+      <c r="K122" t="n">
+        <v>522</v>
+      </c>
+      <c r="L122" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s">
+        <v>48</v>
+      </c>
+      <c r="B123" t="s">
+        <v>49</v>
+      </c>
+      <c r="C123" t="s">
+        <v>40</v>
+      </c>
+      <c r="D123" t="s">
+        <v>37</v>
+      </c>
+      <c r="E123" t="s">
+        <v>49</v>
+      </c>
+      <c r="F123" t="s">
+        <v>290</v>
+      </c>
+      <c r="G123" t="s">
+        <v>291</v>
+      </c>
+      <c r="H123" t="s">
+        <v>35</v>
+      </c>
+      <c r="I123" t="s">
+        <v>170</v>
+      </c>
+      <c r="J123" t="s">
+        <v>171</v>
+      </c>
+      <c r="K123" t="n">
+        <v>37</v>
+      </c>
+      <c r="L123" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="s">
+        <v>48</v>
+      </c>
+      <c r="B124" t="s">
+        <v>49</v>
+      </c>
+      <c r="C124" t="s">
+        <v>40</v>
+      </c>
+      <c r="D124" t="s">
+        <v>37</v>
+      </c>
+      <c r="E124" t="s">
+        <v>49</v>
+      </c>
+      <c r="F124" t="s">
+        <v>290</v>
+      </c>
+      <c r="G124" t="s">
+        <v>291</v>
+      </c>
+      <c r="H124" t="s">
+        <v>35</v>
+      </c>
+      <c r="I124" t="s">
+        <v>170</v>
+      </c>
+      <c r="J124" t="s">
+        <v>171</v>
+      </c>
+      <c r="K124" t="n">
+        <v>87</v>
+      </c>
+      <c r="L124" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s">
+        <v>48</v>
+      </c>
+      <c r="B125" t="s">
+        <v>49</v>
+      </c>
+      <c r="C125" t="s">
+        <v>40</v>
+      </c>
+      <c r="D125" t="s">
+        <v>37</v>
+      </c>
+      <c r="E125" t="s">
+        <v>49</v>
+      </c>
+      <c r="F125" t="s">
+        <v>292</v>
+      </c>
+      <c r="G125" t="s">
+        <v>293</v>
+      </c>
+      <c r="H125" t="s">
+        <v>35</v>
+      </c>
+      <c r="I125" t="s">
+        <v>170</v>
+      </c>
+      <c r="J125" t="s">
+        <v>171</v>
+      </c>
+      <c r="K125" t="n">
+        <v>77</v>
+      </c>
+      <c r="L125" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="s">
+        <v>48</v>
+      </c>
+      <c r="B126" t="s">
+        <v>49</v>
+      </c>
+      <c r="C126" t="s">
+        <v>40</v>
+      </c>
+      <c r="D126" t="s">
+        <v>37</v>
+      </c>
+      <c r="E126" t="s">
+        <v>49</v>
+      </c>
+      <c r="F126" t="s">
+        <v>292</v>
+      </c>
+      <c r="G126" t="s">
+        <v>293</v>
+      </c>
+      <c r="H126" t="s">
+        <v>35</v>
+      </c>
+      <c r="I126" t="s">
+        <v>170</v>
+      </c>
+      <c r="J126" t="s">
+        <v>171</v>
+      </c>
+      <c r="K126" t="n">
+        <v>371</v>
+      </c>
+      <c r="L126" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="s">
+        <v>48</v>
+      </c>
+      <c r="B127" t="s">
+        <v>49</v>
+      </c>
+      <c r="C127" t="s">
+        <v>40</v>
+      </c>
+      <c r="D127" t="s">
+        <v>37</v>
+      </c>
+      <c r="E127" t="s">
+        <v>49</v>
+      </c>
+      <c r="F127" t="s">
+        <v>294</v>
+      </c>
+      <c r="G127" t="s">
+        <v>295</v>
+      </c>
+      <c r="H127" t="s">
+        <v>35</v>
+      </c>
+      <c r="I127" t="s">
+        <v>170</v>
+      </c>
+      <c r="J127" t="s">
+        <v>171</v>
+      </c>
+      <c r="K127" t="n">
+        <v>77</v>
+      </c>
+      <c r="L127" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="s">
+        <v>48</v>
+      </c>
+      <c r="B128" t="s">
+        <v>49</v>
+      </c>
+      <c r="C128" t="s">
+        <v>40</v>
+      </c>
+      <c r="D128" t="s">
+        <v>37</v>
+      </c>
+      <c r="E128" t="s">
+        <v>49</v>
+      </c>
+      <c r="F128" t="s">
+        <v>294</v>
+      </c>
+      <c r="G128" t="s">
+        <v>295</v>
+      </c>
+      <c r="H128" t="s">
+        <v>35</v>
+      </c>
+      <c r="I128" t="s">
+        <v>170</v>
+      </c>
+      <c r="J128" t="s">
+        <v>171</v>
+      </c>
+      <c r="K128" t="n">
+        <v>371</v>
+      </c>
+      <c r="L128" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="s">
+        <v>48</v>
+      </c>
+      <c r="B129" t="s">
+        <v>49</v>
+      </c>
+      <c r="C129" t="s">
+        <v>40</v>
+      </c>
+      <c r="D129" t="s">
+        <v>37</v>
+      </c>
+      <c r="E129" t="s">
+        <v>49</v>
+      </c>
+      <c r="F129" t="s">
+        <v>296</v>
+      </c>
+      <c r="G129" t="s">
+        <v>297</v>
+      </c>
+      <c r="H129" t="s">
+        <v>35</v>
+      </c>
+      <c r="I129" t="s">
+        <v>170</v>
+      </c>
+      <c r="J129" t="s">
+        <v>171</v>
+      </c>
+      <c r="K129" t="n">
+        <v>85</v>
+      </c>
+      <c r="L129" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s">
+        <v>48</v>
+      </c>
+      <c r="B130" t="s">
+        <v>49</v>
+      </c>
+      <c r="C130" t="s">
+        <v>40</v>
+      </c>
+      <c r="D130" t="s">
+        <v>37</v>
+      </c>
+      <c r="E130" t="s">
+        <v>49</v>
+      </c>
+      <c r="F130" t="s">
+        <v>296</v>
+      </c>
+      <c r="G130" t="s">
+        <v>297</v>
+      </c>
+      <c r="H130" t="s">
+        <v>35</v>
+      </c>
+      <c r="I130" t="s">
+        <v>170</v>
+      </c>
+      <c r="J130" t="s">
+        <v>171</v>
+      </c>
+      <c r="K130" t="n">
         <v>360</v>
       </c>
-      <c r="L91" t="s">
-        <v>188</v>
+      <c r="L130" t="s">
+        <v>232</v>
       </c>
     </row>
   </sheetData>
